--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6F58F0-613B-478D-8370-802AAB5C9938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F2288A-0B3F-4CB8-9371-0A1943D8DCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3876,29 +3876,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4314,7 +4314,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>10.51</v>
+        <v>10.49</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14661.68444657</v>
+        <v>14633.78400043</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4372,13 +4372,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="350" t="s">
         <v>363</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="350"/>
+      <c r="D18" s="350"/>
+      <c r="E18" s="350"/>
+      <c r="F18" s="350"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10675080829126316</v>
+        <v>0.10747795197530263</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4499,7 +4499,7 @@
         <v>428</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4574,22 +4574,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="350" t="s">
         <v>364</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="350"/>
+      <c r="D36" s="350"/>
+      <c r="E36" s="350"/>
+      <c r="F36" s="350"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="353" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="353"/>
+      <c r="D37" s="353"/>
+      <c r="E37" s="353"/>
+      <c r="F37" s="353"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4601,13 +4601,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="351" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="351"/>
+      <c r="D40" s="351"/>
+      <c r="E40" s="351"/>
+      <c r="F40" s="351"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4627,13 +4627,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="351" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="351"/>
+      <c r="D43" s="351"/>
+      <c r="E43" s="351"/>
+      <c r="F43" s="351"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4662,13 +4662,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="351" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="351"/>
+      <c r="D47" s="351"/>
+      <c r="E47" s="351"/>
+      <c r="F47" s="351"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4684,13 +4684,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="351" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="351"/>
+      <c r="D50" s="351"/>
+      <c r="E50" s="351"/>
+      <c r="F50" s="351"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4754,13 +4754,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="351" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="351"/>
+      <c r="D58" s="351"/>
+      <c r="E58" s="351"/>
+      <c r="F58" s="351"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4776,7 +4776,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="351" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="352"/>
@@ -4798,22 +4798,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="350" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="350"/>
+      <c r="D64" s="350"/>
+      <c r="E64" s="350"/>
+      <c r="F64" s="350"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="350" t="s">
         <v>365</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="350"/>
+      <c r="D65" s="350"/>
+      <c r="E65" s="350"/>
+      <c r="F65" s="350"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.3569400417418821E-2</v>
+        <v>3.3633403087423429E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8058991436726933E-2</v>
+        <v>3.8131553860819831E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>452</v>
@@ -4948,22 +4948,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="350" t="s">
         <v>366</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="350"/>
+      <c r="D80" s="350"/>
+      <c r="E80" s="350"/>
+      <c r="F80" s="350"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="353" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="353"/>
+      <c r="D81" s="353"/>
+      <c r="E81" s="353"/>
+      <c r="F81" s="353"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5007,22 +5007,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="350" t="s">
         <v>367</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="350"/>
+      <c r="D89" s="350"/>
+      <c r="E89" s="350"/>
+      <c r="F89" s="350"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="350"/>
+      <c r="D90" s="350"/>
+      <c r="E90" s="350"/>
+      <c r="F90" s="350"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5059,13 +5059,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="350"/>
+      <c r="D97" s="350"/>
+      <c r="E97" s="350"/>
+      <c r="F97" s="350"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="350" t="s">
         <v>347</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="350"/>
+      <c r="D101" s="350"/>
+      <c r="E101" s="350"/>
+      <c r="F101" s="350"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5206,13 +5206,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="350" t="s">
         <v>370</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="350"/>
+      <c r="D116" s="350"/>
+      <c r="E116" s="350"/>
+      <c r="F116" s="350"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5251,13 +5251,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="351"/>
+      <c r="D123" s="351"/>
+      <c r="E123" s="351"/>
+      <c r="F123" s="351"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5400,13 +5400,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="354" t="s">
         <v>374</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="354"/>
+      <c r="D134" s="354"/>
+      <c r="E134" s="354"/>
+      <c r="F134" s="354"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5419,22 +5419,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="355" t="s">
         <v>372</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="355"/>
+      <c r="D138" s="355"/>
+      <c r="E138" s="355"/>
+      <c r="F138" s="355"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="350" t="s">
         <v>373</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="350"/>
+      <c r="D139" s="350"/>
+      <c r="E139" s="350"/>
+      <c r="F139" s="350"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5767,13 +5767,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="349" t="s">
         <v>380</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="350"/>
+      <c r="D179" s="350"/>
+      <c r="E179" s="350"/>
+      <c r="F179" s="350"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="351" t="s">
         <v>385</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="351"/>
+      <c r="D188" s="351"/>
+      <c r="E188" s="351"/>
+      <c r="F188" s="351"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5824,22 +5824,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="348" t="s">
         <v>386</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="348"/>
+      <c r="D191" s="348"/>
+      <c r="E191" s="348"/>
+      <c r="F191" s="348"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="348" t="s">
         <v>387</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="348"/>
+      <c r="D192" s="348"/>
+      <c r="E192" s="348"/>
+      <c r="F192" s="348"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5863,17 +5863,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5890,6 +5879,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13456,24 +13456,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8058991436726933E-2</v>
+        <v>3.8131553860819831E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8058991436726933E-2</v>
+        <v>3.8131553860819831E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4215033301617508E-2</v>
+        <v>7.4356530028598669E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1360608943862994E-2</v>
+        <v>7.1496663489037174E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4700285442435765E-2</v>
+        <v>6.4823641563393708E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14655,50 +14655,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3569400417418821E-2</v>
+        <v>3.3633403087423429E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>2.2913937294196982E-2</v>
+        <v>2.2957624495901836E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11465164308150533</v>
+        <v>0.11487023534667502</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.9109669339599939E-2</v>
+        <v>7.9260498070466673E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.5807243160326018E-2</v>
+        <v>6.5932709782176024E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.1081841890218723</v>
+        <v>0.10839045058340112</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10237559964371633</v>
+        <v>0.10257078667830873</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.8435089485863186E-2</v>
+        <v>9.8622763631689411E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.1098837417263404</v>
+        <v>0.11009324361714372</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.1391700038495477E-2</v>
+        <v>9.1565945415117964E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.4549148154372094E-2</v>
+        <v>7.469128189727843E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14712,43 +14712,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3420070378286638E-2</v>
+        <v>5.3521919892830561E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13328576618337809</v>
+        <v>0.13353988585198318</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13071804109440938</v>
+        <v>0.13096726519563798</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13984073702252225</v>
+        <v>0.1401073542523078</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1248235936102243</v>
+        <v>0.12506157948936675</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11808726952959619</v>
+        <v>0.11831241208351344</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11091852910396326</v>
+        <v>0.1111300038972978</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.903682604079618E-2</v>
+        <v>9.9225647444115134E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7284593913040207E-2</v>
+        <v>8.7451008772740937E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9251445237032939E-2</v>
+        <v>7.9402544274663131E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18468,7 +18468,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.51</v>
+        <v>-10.49</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.51</v>
+        <v>10.49</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19247,7 +19247,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19256,7 +19256,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.51</v>
+        <v>10.49</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19319,7 +19319,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10675080829126316</v>
+        <v>0.10747795197530263</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F2288A-0B3F-4CB8-9371-0A1943D8DCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499B1BD8-3FD0-4C8B-91B8-9BAAFBD6E9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1405,10 +1405,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Play</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1554,10 +1550,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1765,10 +1757,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2458,26 +2446,44 @@
     <t>Latest</t>
   </si>
   <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>中文传媒</t>
+  </si>
+  <si>
     <t>600373.SS</t>
   </si>
   <si>
-    <t>中文传媒</t>
+    <t/>
   </si>
   <si>
     <t>TMT_02</t>
   </si>
   <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>DCF</t>
   </si>
   <si>
-    <t>CN</t>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2495,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3143,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3815,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3859,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3876,29 +3856,71 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4220,13 +4242,13 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>285</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4245,7 +4267,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4254,10 +4276,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4271,7 +4293,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4294,19 +4316,21 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C11" s="49" t="s">
         <v>458</v>
       </c>
-      <c r="D11" s="49"/>
+      <c r="D11" s="49" t="s">
+        <v>459</v>
+      </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
@@ -4321,17 +4345,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4345,7 +4369,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4372,34 +4396,34 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
-        <v>363</v>
-      </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="B18" s="357" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4409,30 +4433,34 @@
       <c r="C22" s="48" t="s">
         <v>460</v>
       </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
       <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>323</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>323</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4453,7 +4481,7 @@
         <v>12.91528670453229</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4466,7 +4494,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4477,7 +4505,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4485,7 +4513,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4496,15 +4524,15 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4515,7 +4543,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F30" s="312">
         <v>0.187</v>
@@ -4523,7 +4551,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4534,7 +4562,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F31" s="312">
         <v>0.06</v>
@@ -4542,7 +4570,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4553,7 +4581,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4565,7 +4593,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4574,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
-        <v>364</v>
-      </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="B36" s="357" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="B37" s="359" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4601,19 +4629,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>805173862.5</v>
       </c>
@@ -4627,19 +4655,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>304213708</v>
       </c>
@@ -4652,7 +4680,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-304213708</v>
       </c>
@@ -4662,19 +4690,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4684,19 +4712,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="340">
+        <v>341</v>
+      </c>
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>30189572.474333331</v>
       </c>
@@ -4709,9 +4737,9 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="340">
+        <v>342</v>
+      </c>
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-127330087.00000001</v>
       </c>
@@ -4726,7 +4754,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-97140514.525666684</v>
       </c>
@@ -4744,7 +4772,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-38841055</v>
       </c>
@@ -4754,19 +4782,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-177008336.99358332</v>
       </c>
@@ -4776,19 +4804,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="358" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4798,28 +4826,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="B64" s="357" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
-        <v>365</v>
-      </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="B65" s="357" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>335956918.03600812</v>
       </c>
@@ -4832,7 +4860,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>492183955.98074996</v>
       </c>
@@ -4843,7 +4871,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4853,14 +4881,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>3.8131553860819831E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4869,18 +4897,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>451</v>
+      </c>
+      <c r="C72" s="329" t="s">
+        <v>453</v>
+      </c>
+      <c r="D72" s="329" t="s">
         <v>454</v>
-      </c>
-      <c r="C72" s="344" t="s">
-        <v>456</v>
-      </c>
-      <c r="D72" s="344" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C120</f>
@@ -4896,11 +4924,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>7.6099586896956867E-2</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>8.3218084848475898E-2</v>
       </c>
@@ -4910,11 +4938,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.30413488760323032</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.30413488760323026</v>
       </c>
@@ -4924,18 +4952,18 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.6800075256655485</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.6800075256655487</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4948,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
-        <v>366</v>
-      </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="B80" s="357" t="s">
+        <v>363</v>
+      </c>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -4972,7 +5000,7 @@
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -4981,7 +5009,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5002,27 +5030,27 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
-        <v>367</v>
-      </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="B89" s="357" t="s">
+        <v>364</v>
+      </c>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
-        <v>368</v>
-      </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="B90" s="357" t="s">
+        <v>365</v>
+      </c>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5047,7 +5075,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5059,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
-        <v>369</v>
-      </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="B97" s="357" t="s">
+        <v>366</v>
+      </c>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5078,19 +5106,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
-        <v>347</v>
-      </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="B101" s="357" t="s">
+        <v>345</v>
+      </c>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>1685959940.8299999</v>
       </c>
@@ -5114,18 +5142,18 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>408</v>
-      </c>
-      <c r="C104" s="346">
+        <v>405</v>
+      </c>
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>9.2587702159681276E-2</v>
       </c>
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>410</v>
-      </c>
-      <c r="C105" s="347">
+        <v>407</v>
+      </c>
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>2.0939079363495856</v>
       </c>
@@ -5139,7 +5167,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>10570865213.440001</v>
       </c>
@@ -5152,7 +5180,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>7551907966.0066681</v>
       </c>
@@ -5183,7 +5211,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>3684979983.197</v>
       </c>
@@ -5206,17 +5234,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
-        <v>370</v>
-      </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="B116" s="357" t="s">
+        <v>367</v>
+      </c>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5229,7 +5257,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5242,7 +5270,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5251,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="B123" s="358" t="s">
+        <v>368</v>
+      </c>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5400,17 +5428,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
-        <v>374</v>
-      </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="B134" s="362" t="s">
+        <v>371</v>
+      </c>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5419,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
-        <v>372</v>
-      </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="B138" s="360" t="s">
+        <v>369</v>
+      </c>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
-        <v>373</v>
-      </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="B139" s="357" t="s">
+        <v>370</v>
+      </c>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5456,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5474,7 +5502,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5487,11 +5515,11 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5501,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322296</v>
+        <v>0.69031028314322285</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5529,7 +5557,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5551,12 +5579,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5598,7 +5626,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5620,12 +5648,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5654,7 +5682,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5667,7 +5695,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5689,12 +5717,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5723,7 +5751,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5736,7 +5764,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5758,7 +5786,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5767,102 +5795,113 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
-        <v>380</v>
-      </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="B179" s="364" t="s">
+        <v>377</v>
+      </c>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
-        <v>384</v>
-      </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="B182" s="361" t="s">
+        <v>381</v>
+      </c>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
-        <v>385</v>
-      </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="B188" s="358" t="s">
+        <v>382</v>
+      </c>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
-        <v>386</v>
-      </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="B191" s="363" t="s">
+        <v>383</v>
+      </c>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
-        <v>387</v>
-      </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="B192" s="363" t="s">
+        <v>384</v>
+      </c>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5879,17 +5918,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6005,391 +6033,391 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>9304036682</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>10083626566</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>10236379917</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>10714557474</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>10339544971</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>11258180127</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>11512673967</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>13306047614</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>12775837643</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>11601620038</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>5676944377</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>5916816097</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>6311388363</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>6550446555</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>6394029156</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>7367488537</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>7224602455</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>8540494147</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>7781713253</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>7483557979</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>2587076947</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>2472052826</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>2474489551</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>2654508105</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>1974885174</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>1837469000</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>1855864520</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>3107662903</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>3565289873</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>2862797189</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>775878829</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>812050107</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>922966476</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>1146157898</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>634916493</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>595595416</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>678292721</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>1085064842</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>1910926978</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>1707428207</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>218971112</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>230826900</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>251189350</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>238378620</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>208413520</v>
       </c>
-      <c r="H8" s="334">
+      <c r="H8" s="321">
         <v>390411956</v>
       </c>
-      <c r="I8" s="334">
+      <c r="I8" s="321">
         <v>833049901</v>
       </c>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>127330087</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>145285501</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>161564792</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>169466694</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>139996345</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>156549769</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>87319034</v>
       </c>
-      <c r="J12" s="334"/>
-      <c r="K12" s="334"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>282045305</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>408337182</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>577191429</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>441101398</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>264423586</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>197905422</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>115750108</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>399466141</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>-245723033</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>42708255</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>256010400</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>87059787</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>55904457</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>94528010</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>46504665</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>88878250</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>58244331</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>783228215</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>1954193845</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>1916546670</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>2050300759</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>1830124141</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>1731358283</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>1626252473</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>1452046692</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>1279739173</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>1161959682</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>38841055</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>-12469089</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>-13791461</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>6877210</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>24515876</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>5877927</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>7143161</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>305152</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>-14934895</v>
       </c>
-      <c r="L16" s="334">
+      <c r="L16" s="321">
         <v>104004453</v>
       </c>
-      <c r="M16" s="334"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6401,171 +6429,171 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>304213708</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>284765003</v>
       </c>
-      <c r="E19" s="334">
+      <c r="E19" s="321">
         <v>280160892</v>
       </c>
-      <c r="F19" s="334">
+      <c r="F19" s="321">
         <v>262044527</v>
       </c>
-      <c r="G19" s="334">
+      <c r="G19" s="321">
         <v>233520143</v>
       </c>
-      <c r="H19" s="334">
+      <c r="H19" s="321">
         <v>241901529</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="321">
         <v>213366792</v>
       </c>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>375</v>
-      </c>
-      <c r="C22" s="334">
+        <v>372</v>
+      </c>
+      <c r="C22" s="321">
         <v>401377348</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>1956255182</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>2083950094</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>1804027448</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>2770158153</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>2326723445</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>2605766691</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>1503187129</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>2357234262</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>1011750597</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="C23" s="334">
+        <v>374</v>
+      </c>
+      <c r="C23" s="321">
         <v>-5702735165</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-2481866338</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>474401567</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>1138014522</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-2480713998</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>1129192930</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-2458554273</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-2519375006</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-1120642674</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-922976904</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="C24" s="334">
+        <v>373</v>
+      </c>
+      <c r="C24" s="321">
         <v>-1440890089</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-859747503</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-291365390</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-848504375</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-215048943</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-2175532336</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>1191203049</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>571517672</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-353867404</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>1755067231</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6601,193 +6629,193 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>220</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>1910217201.7599998</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>834568719</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>1061824178</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>925201481</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>854194501</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>1181367947</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>1188191051</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>1801027889</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>1423555374</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>2019329272</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>1152244678.0699999</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>959867234</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>1086298738</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>1224714311</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>1118318039</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>1167338551</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>1312102814</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>1053507533</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>1025018847</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>940108789</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>12382480837.01</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>10670434743</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>11040803287</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>9869570784</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>9001654126</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>8576109791</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>10230716015</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>8088092587</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>7643685931</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>7296360629</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>18209329117.190002</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>18619255819</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>17690189005</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>16697566222</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>15368696907</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>14238226833</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>13494814071</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>12392566731</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>11212733584</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>10310906068</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>337582462.13999999</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>183358225</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>204627353</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>244147889</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>209715743</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>206701848</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>205332329</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>199184480</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>205687459</v>
       </c>
-      <c r="L32" s="334">
+      <c r="L32" s="321">
         <v>551331945</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6814,47 +6842,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>9304036682</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>10083626566</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>10236379917</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>10714557474</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>10339544971</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>11258180127</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>11512673967</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>13306047614</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>12775837643</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>11601620038</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6863,47 +6891,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-5676944377</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-5916816097</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-6311388363</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-6550446555</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-6394029156</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-7367488537</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-7224602455</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-8540494147</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-7781713253</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-7483557979</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6912,47 +6940,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>3627092305</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>4166810469</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>3924991554</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>4164110919</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>3945515815</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>3890691590</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>4288071512</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>4765553467</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>4994124390</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>4118062059</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6961,47 +6989,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-2587076947</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-2472052826</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-2474489551</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-2654508105</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-1974885174</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-1837469000</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-1855864520</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-3107662903</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-3565289873</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-2862797189</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7010,47 +7038,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-775878829</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-812050107</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-922966476</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-1146157898</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-634916493</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-595595416</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-678292721</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-1085064842</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-1910926978</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-1707428207</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7059,47 +7087,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-1811198118</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-1660002719</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-1551523075</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-1508350207</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-1339968681</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-1241873584</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-1177571799</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-2022598061</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-1654362895</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-1155368982</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7108,47 +7136,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-218971112</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-230826900</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-251189350</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-238378620</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-208413520</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>-390411956</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>-833049901</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7157,47 +7185,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>821044246</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>1463930743</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>1199312653</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>1271224194</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>1762217121</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>1662810634</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>1599157091</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>1657890564</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>1428834517</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>1255264870</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7304,47 +7332,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-399466141</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>245723033</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-42708255</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-256010400</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-87059787</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-55904457</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-94528010</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-46504665</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-88878250</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-58244331</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7353,47 +7381,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>783228215</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>1954193845</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>1916546670</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>2050300759</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>1830124141</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>1731358283</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>1626252473</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>1452046692</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>1279739173</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>1161959682</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7402,47 +7430,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-38841055</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>-6877210</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>-24515876</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>-5877927</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>-7143161</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>-305152</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>-104004453</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7456,47 +7484,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-127330087</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-145285501</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-161564792</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-169466694</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-139996345</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-156549769</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-87319034</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7505,47 +7533,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>282045305</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>408337182</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>577191429</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>441101398</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>264423586</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>197905422</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>115750108</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7761,47 +7789,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-304213708</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-284765003</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>-280160892</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>-262044527</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>-233520143</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>-241901529</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>-213366792</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7810,47 +7838,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-304213708</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-284765003</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-280160892</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-262044527</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-233520143</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>-241901529</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>-213366792</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7859,96 +7887,96 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>397</v>
-      </c>
-      <c r="C64" s="323">
+        <v>394</v>
+      </c>
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-6742247906</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>-1385358659</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>2266986271</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>2093537595</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>74395212</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>1280384039</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>1338415467</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>-444670205</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>882724184</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>1843840924</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8330,115 +8358,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>1910217201.7599998</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>834568719</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>1061824178</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>925201481</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>854194501</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>1181367947</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>1152244678.0699999</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>959867234</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>1086298738</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>1224714311</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>1118318039</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>1167338551</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>12382480837.01</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>10670434743</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>11040803287</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>9869570784</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>9001654126</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>8576109791</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>10230716015</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>8088092587</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>7643685931</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>7296360629</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8447,47 +8475,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>18209329117.190002</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>18619255819</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>17690189005</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>16697566222</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>15368696907</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>14238226833</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>13494814071</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>12392566731</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>11212733584</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>10310906068</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9286,7 +9314,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9492,7 +9520,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9559,7 +9587,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>96</v>
@@ -9571,23 +9599,23 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>319</v>
-      </c>
-      <c r="C73" s="76">
+        <v>318</v>
+      </c>
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-753416779.89999998</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-754739311.85833323</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9598,25 +9626,25 @@
         <v>14.005981995839356</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>322</v>
-      </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+        <v>321</v>
+      </c>
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>3018957247.4333329</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9624,7 +9652,7 @@
         <v>4</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9700,7 +9728,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9711,15 +9739,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>291</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9736,7 +9764,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9770,7 +9798,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9910,54 +9938,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>G4</f>
         <v>9304036682</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>9304036682</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>10083626566</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>10236379917</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>10714557474</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>10339544971</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>11258180127</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>11512673967</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>13306047614</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>12775837643</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>11601620038</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9967,52 +9995,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-6452823206</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-6452823206</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-6728866204</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-7234354839</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-7696604453</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-7028945649</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-7963083953</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-7902895176</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-9625558989</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-9692640231</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-9190986186</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10022,52 +10050,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>2851213476</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>2851213476</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>3354760362</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>3002025078</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>3017953021</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>3310599322</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>3295096174</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>3609778791</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>3680488625</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>3083197412</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>2410633852</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10077,52 +10105,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-2046039613.5</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-2030169230</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-1890829619</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-1802712425</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-1746728827</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-1548382201</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-1632285540</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-2010621700</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-2022598061</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-1654362895</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-1155368982</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10132,54 +10160,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>805173862.5</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>821044246</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>1463930743</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>1199312653</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>1271224194</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>1762217121</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>1662810634</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>1599157091</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>1657890564</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>1428834517</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>1255264870</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10189,52 +10217,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>304213708</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>304213708</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>284765003</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>280160892</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>262044527</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>233520143</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>241901529</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>213366792</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10244,52 +10272,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-304213708</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-304213708</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-284765003</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-280160892</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-262044527</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-233520143</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>-241901529</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>-213366792</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10299,54 +10327,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10356,52 +10384,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-97140514.525666684</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>-46780131.963991836</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>-28667563.858198315</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>3276610.5297081172</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-43491550.484597951</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>-64479016.453226149</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-100029512.99544704</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-54261699.488393471</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10411,52 +10439,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>708033347.97433329</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>774264114.03600812</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>1435263179.1418016</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>1202589263.5297081</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>1227732643.5154021</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>1697738104.5467739</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>1562781121.0045528</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>1544895391.5116065</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>1657890564</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>1428834517</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>1255264870</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10466,52 +10494,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-177008336.99358332</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-399466141</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>245723033</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-42708255</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-256010400</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-87059787</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-55904457</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-94528010</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-46504665</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-88878250</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-58244331</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10521,54 +10549,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-38841055</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-38841055</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>0</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>-6877210</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>-24515876</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>-5877927</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>-7143161</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>-305152</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>0</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>-104004453</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10578,54 +10606,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>492183955.98074996</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>335956918.03600812</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>1680986212.1418016</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>1159881008.5297081</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>964845033.51540208</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>1586162441.5467739</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>1500998737.0045528</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>1443224220.5116065</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>1611080747</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>1339956267</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>1093016086</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10635,105 +10663,105 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>492183955.98074996</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>335956918.03600812</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>1680986212.1418016</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>1159881008.5297081</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>964845033.51540208</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>1586162441.5467739</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>1500998737.0045528</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>1443224220.5116065</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>1611080747</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>1339956267</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>1093016086</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10806,54 +10834,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-5676944377</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-5676944377</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-5916816097</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-6311388363</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-6550446555</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-6394029156</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-7367488537</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-7224602455</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-8540494147</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-7781713253</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-7483557979</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10863,54 +10891,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-775878829</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-775878829</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-812050107</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-922966476</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-1146157898</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-634916493</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-595595416</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-678292721</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-1085064842</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-1910926978</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-1707428207</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10920,54 +10948,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-6452823206</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-6452823206</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-6728866204</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-7234354839</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-7696604453</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-7028945649</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-7963083953</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-7902895176</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-9625558989</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-9692640231</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-9190986186</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -10994,7 +11022,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11054,7 +11082,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11173,54 +11201,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>G33</f>
         <v>-1811198118</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>336</v>
-      </c>
-      <c r="G33" s="318">
+        <v>334</v>
+      </c>
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-1811198118</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-1660002719</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-1551523075</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-1508350207</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-1339968681</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-1241873584</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-1177571799</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-2022598061</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-1654362895</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-1155368982</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11230,56 +11258,56 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>-234841495.5</v>
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-218971112</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-230826900</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-251189350</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-238378620</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-208413520</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>-390411956</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>-833049901</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11289,54 +11317,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-2046039613.5</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-2030169230</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-1890829619</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-1802712425</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-1746728827</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-1548382201</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-1632285540</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-2010621700</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-2022598061</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-1654362895</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-1155368982</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11544,7 +11572,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11630,52 +11658,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-127330087.00000001</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-127330087</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-145285501</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-161564792</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-169466694</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-139996345</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-156549769</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-87319034</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11683,54 +11711,54 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C48" s="318">
+        <v>346</v>
+      </c>
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>30189572.474333331</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>80549955.036008164</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>116617937.14180169</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>164841402.52970812</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>125975143.51540205</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>75517328.546773851</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>56520256.00455296</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>33057334.511606529</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11738,56 +11766,56 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="329">
+        <v>343</v>
+      </c>
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>105708652.13440001</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>282045305</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>408337182</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>577191429</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>441101398</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>264423586</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>197905422</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>115750108</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11797,52 +11825,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-97140514.525666684</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-46780131.963991836</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>-28667563.858198315</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>3276610.5297081172</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-43491550.484597951</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>-64479016.453226149</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-100029512.99544704</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-54261699.488393471</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11870,7 +11898,7 @@
         <v>0.01</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11897,7 +11925,7 @@
         <v>7.5523791471175328E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11988,52 +12016,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12043,52 +12071,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12098,52 +12126,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12153,52 +12181,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12208,53 +12236,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>340</v>
-      </c>
-      <c r="G62" s="318">
+        <v>338</v>
+      </c>
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>206934892</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>-18511612</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>344315635</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>763452261</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>30539566</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>83096453</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>93192318</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-159339207</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>-60217094</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>-35060857</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12264,52 +12292,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>206934892</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>-18511612</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>344315635</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>763452261</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>30539566</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>83096453</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>93192318</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-159339207</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>-60217094</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>-35060857</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -12441,7 +12469,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>464</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12773,7 +12801,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>357</v>
+        <v>465</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13452,7 +13480,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13684,54 +13712,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>30591809954.200001</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>30591809954.200005</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>29289690562</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>28730992292</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>26567137006</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>24370351033</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>22814336624</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>23725530086</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>20480659318</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>18856419515</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>17607266697</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13741,54 +13769,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>1910217201.7599998</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>834568719</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>1061824178</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>925201481</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>854194501</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>1181367947</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13798,54 +13826,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>1152244678.0699999</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>959867234</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>1086298738</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1224714311</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>1118318039</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>1167338551</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13855,54 +13883,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>12382480837.01</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>12382480837.01</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>10670434743</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>11040803287</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>9869570784</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>9001654126</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>8576109791</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>10230716015</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>8088092587</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>7643685931</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>7296360629</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13912,54 +13940,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>18209329117.190002</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>18209329117.190002</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>18619255819</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>17690189005</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>16697566222</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>15368696907</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>14238226833</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>13494814071</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>12392566731</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>11212733584</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>10310906068</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -14146,7 +14174,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C113" s="169"/>
       <c r="E113" s="268"/>
@@ -14198,7 +14226,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -14707,7 +14735,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
@@ -15457,7 +15485,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15496,7 +15524,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>492183955.98074996</v>
       </c>
@@ -15528,7 +15556,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>8203065933.0124998</v>
       </c>
@@ -15536,17 +15564,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>1685959940.8299999</v>
       </c>
@@ -15554,15 +15582,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>7551907966.0066681</v>
       </c>
@@ -15570,15 +15598,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>3684979983.197</v>
       </c>
@@ -15586,15 +15614,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>17753993941.386166</v>
       </c>
@@ -15657,11 +15685,11 @@
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15671,7 +15699,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15685,10 +15713,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15706,7 +15734,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15716,7 +15744,7 @@
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15728,7 +15756,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15738,7 +15766,7 @@
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
@@ -15750,7 +15778,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15760,7 +15788,7 @@
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
@@ -15770,9 +15798,19 @@
         <f t="shared" si="1"/>
         <v>442596229.3744846</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15782,7 +15820,7 @@
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
@@ -15792,9 +15830,19 @@
         <f t="shared" si="1"/>
         <v>427203165.48600757</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15804,7 +15852,7 @@
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
@@ -15814,9 +15862,19 @@
         <f t="shared" si="1"/>
         <v>412345457.30132753</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15838,7 +15896,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15860,7 +15918,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15882,7 +15940,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15904,7 +15962,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15926,7 +15984,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15948,7 +16006,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15970,11 +16028,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15990,13 +16048,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16012,13 +16080,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16034,9 +16112,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16058,7 +16146,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16080,7 +16168,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16102,7 +16190,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16124,7 +16212,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16146,7 +16234,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16168,7 +16256,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16190,7 +16278,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16212,7 +16300,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16234,7 +16322,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16256,7 +16344,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16278,11 +16366,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16298,13 +16386,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16320,13 +16418,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16342,13 +16450,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16364,9 +16482,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16388,7 +16516,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16399,11 +16527,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16413,7 +16541,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>8487371563.7394762</v>
@@ -16440,7 +16568,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16462,7 +16590,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16483,14 +16611,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>8203065933.0124931</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>8203065933.0124931</v>
       </c>
       <c r="D58" s="123">
@@ -16502,16 +16630,26 @@
       <c r="F58" s="123">
         <v>10443360379.329018</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>8203065933.0124931</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>8203065933.0124931</v>
       </c>
       <c r="D59" s="123">
@@ -16523,16 +16661,26 @@
       <c r="F59" s="123">
         <v>11610103840.277256</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>8203065933.0124912</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>8203065933.0124912</v>
       </c>
       <c r="D60" s="123">
@@ -16544,16 +16692,26 @@
       <c r="F60" s="123">
         <v>12910373672.111689</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>8203065933.0124912</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>8203065933.0124912</v>
       </c>
       <c r="D61" s="123">
@@ -16565,26 +16723,56 @@
       <c r="F61" s="123">
         <v>14290591802.684071</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16932,7 +17120,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>106</v>
@@ -16956,6 +17144,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16999,7 +17257,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17011,7 +17269,7 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -17024,7 +17282,7 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91</f>
@@ -17056,9 +17314,9 @@
     </row>
     <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>445</v>
-      </c>
-      <c r="C6" s="338">
+        <v>442</v>
+      </c>
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>9300148713.333334</v>
       </c>
@@ -17066,13 +17324,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17109,7 +17367,7 @@
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="H11" s="120"/>
     </row>
@@ -17145,7 +17403,7 @@
         <v>108</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D15" s="128" t="s">
         <v>119</v>
@@ -17154,7 +17412,7 @@
         <v>110</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17168,7 +17426,7 @@
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
@@ -17190,7 +17448,7 @@
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
@@ -17212,7 +17470,7 @@
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
@@ -17234,7 +17492,7 @@
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
@@ -17256,7 +17514,7 @@
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
@@ -18384,7 +18642,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>106</v>
@@ -18455,7 +18713,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I2" s="249"/>
     </row>
@@ -18524,7 +18782,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>821044246</v>
       </c>
@@ -18532,11 +18790,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中文传媒(600373.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18549,7 +18807,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>335956918.03600812</v>
       </c>
@@ -18557,8 +18815,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18571,7 +18829,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>492183955.98074996</v>
       </c>
@@ -18579,8 +18837,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18590,8 +18848,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18602,10 +18860,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>451</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+        <v>448</v>
+      </c>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18623,8 +18881,8 @@
         <v>-4.5961886297537391E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18641,8 +18899,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.135599908831609</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18659,8 +18917,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.29648179377498129</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18676,7 +18934,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -18686,21 +18944,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="367" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>305</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18714,8 +18972,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18729,8 +18987,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18750,8 +19008,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18761,8 +19019,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18776,8 +19034,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18787,8 +19045,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18808,8 +19066,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18819,8 +19077,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18834,8 +19092,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18845,8 +19103,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18866,8 +19124,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18877,8 +19135,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18892,8 +19150,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18904,8 +19162,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18967,8 +19225,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18978,8 +19236,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18993,8 +19251,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19004,12 +19262,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E54" s="159" t="s">
         <v>150</v>
@@ -19025,8 +19283,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19036,8 +19294,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19051,8 +19309,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19062,8 +19320,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19078,7 +19336,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19087,7 +19345,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19096,10 +19354,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -19112,7 +19370,7 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -19120,11 +19378,11 @@
         <v>135</v>
       </c>
       <c r="C65" s="151">
-        <v>2.3134236943577698E-2</v>
+        <v>2.3134236943577701E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19140,20 +19398,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19163,19 +19421,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19185,14 +19443,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19215,7 +19473,7 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19238,16 +19496,16 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19256,7 +19514,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322296</v>
+        <v>0.69031028314322285</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19297,12 +19555,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19315,7 +19573,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19327,12 +19585,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19383,14 +19641,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19425,14 +19683,14 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>11.913128542800674</v>
       </c>
       <c r="D99" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E99" s="146" t="s">
         <v>127</v>
@@ -19447,12 +19705,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19481,14 +19739,14 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>11.073728055846336</v>
       </c>
       <c r="D105" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E105" s="146" t="s">
         <v>127</v>
@@ -19503,32 +19761,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="283" t="s">
         <v>328</v>
-      </c>
-      <c r="F109" s="283" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499B1BD8-3FD0-4C8B-91B8-9BAAFBD6E9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBA79F7-93DC-42C5-9042-C48D1334AFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>10.49</v>
+        <v>10.42</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14633.78400043</v>
+        <v>14536.13243894</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4396,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10747795197530263</v>
+        <v>0.11003791920656925</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4527,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.3633403087423429E-2</v>
+        <v>3.3859347254037601E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8131553860819831E-2</v>
+        <v>3.8387715930902115E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,24 +13484,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8131553860819831E-2</v>
+        <v>3.8387715930902115E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8131553860819831E-2</v>
+        <v>3.8387715930902115E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4356530028598669E-2</v>
+        <v>7.4856046065259127E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1496663489037174E-2</v>
+        <v>7.1976967370441458E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4823641563393708E-2</v>
+        <v>6.5259117082533583E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3633403087423429E-2</v>
+        <v>3.3859347254037601E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>2.2957624495901836E-2</v>
+        <v>2.3111850380231311E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11487023534667502</v>
+        <v>0.11564191639027073</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.9260498070466673E-2</v>
+        <v>7.9792958230249081E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.5932709782176024E-2</v>
+        <v>6.6375635855568757E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10839045058340112</v>
+        <v>0.10911860140305929</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10257078667830873</v>
+        <v>0.10325984186712654</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.8622763631689411E-2</v>
+        <v>9.9285296592746833E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.11009324361714372</v>
+        <v>0.11083283354547387</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.1565945415117964E-2</v>
+        <v>9.2181071727887476E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.469128189727843E-2</v>
+        <v>7.5193046746876269E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3521919892830561E-2</v>
+        <v>5.3881472137791993E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13353988585198318</v>
+        <v>0.13443698681260111</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13096726519563798</v>
+        <v>0.131847083675839</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1401073542523078</v>
+        <v>0.14104857448240968</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12506157948936675</v>
+        <v>0.12590172445714562</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11831241208351344</v>
+        <v>0.11910721715509175</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1111300038972978</v>
+        <v>0.11187655862597445</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9225647444115134E-2</v>
+        <v>9.989223048836543E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7451008772740937E-2</v>
+        <v>8.8038491557202739E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9402544274663131E-2</v>
+        <v>7.9935958679579283E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.49</v>
+        <v>-10.42</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.49</v>
+        <v>10.42</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.49</v>
+        <v>10.42</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10747795197530263</v>
+        <v>0.11003791920656925</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E73A71-CEFA-4645-B4EB-8A29240A9091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778CC860-2855-654A-A284-92B41A90B81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,17 +4340,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.53</v>
+        <v>10.48</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4349,13 +4360,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14689.58489271</v>
+        <v>14619.833777360001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4377,7 +4388,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4387,27 +4398,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4435,7 +4446,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4443,7 +4454,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4451,7 +4462,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4467,7 +4478,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4481,14 +4492,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10602554910062834</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.10784223317227548</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4507,7 +4518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4523,10 +4534,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4545,7 +4556,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4564,7 +4575,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4583,11 +4594,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4597,25 +4608,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4624,16 +4635,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4646,20 +4657,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4672,7 +4683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4685,16 +4696,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4707,16 +4718,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4731,7 +4742,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4746,7 +4757,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4759,12 +4770,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4777,16 +4788,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4799,8 +4810,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4808,7 +4819,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4821,25 +4832,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4852,7 +4863,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4865,23 +4876,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.3505640872466456E-2</v>
+        <v>3.3665496029300739E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7986704653371325E-2</v>
+        <v>3.8167938931297711E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4891,7 +4902,7 @@
         <v>1.1337405781301506</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4902,7 +4913,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4915,7 +4926,7 @@
         <v>4.2520188912675866E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4929,7 +4940,7 @@
         <v>8.3218084848475898E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4943,7 +4954,7 @@
         <v>0.30413488760323026</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4957,7 +4968,7 @@
         <v>1.6800075256655487</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4967,34 +4978,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5003,7 +5014,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5012,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5021,34 +5032,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5056,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5069,7 +5080,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5079,38 +5090,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5123,7 +5134,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5136,7 +5147,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5145,7 +5156,7 @@
         <v>9.2587702159681276E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5154,12 +5165,12 @@
         <v>2.0939079363495856</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5172,7 +5183,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5185,7 +5196,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5198,12 +5209,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5216,7 +5227,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5229,16 +5240,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5251,7 +5262,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5264,7 +5275,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5274,16 +5285,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5300,7 +5311,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5322,7 +5333,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5344,7 +5355,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5366,7 +5377,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5388,7 +5399,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5410,7 +5421,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5423,16 +5434,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5442,30 +5453,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5474,16 +5485,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5496,7 +5507,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5509,26 +5520,26 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322285</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+        <v>0.69031028314322296</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5538,7 +5549,7 @@
         <v>5.4039314300970522</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5551,7 +5562,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5573,12 +5584,12 @@
         <v>0.52813732651388556</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5587,7 +5598,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5597,7 +5608,7 @@
         <v>0.86005014536183588</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5607,7 +5618,7 @@
         <v>7.7223929124686403</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5620,7 +5631,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5633,7 +5644,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5642,12 +5653,12 @@
         <v>0.33548180120394178</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5656,7 +5667,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5666,7 +5677,7 @@
         <v>1.069204779784656</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5676,7 +5687,7 @@
         <v>10.843923763016019</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5689,7 +5700,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5702,7 +5713,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5711,12 +5722,12 @@
         <v>7.7594728220778397E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5735,7 +5746,7 @@
         <v>1.0179560233797402</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5745,7 +5756,7 @@
         <v>10.055772032466596</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5758,7 +5769,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5771,7 +5782,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5780,7 +5791,7 @@
         <v>0.14359457232654926</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5790,21 +5801,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5813,80 +5824,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5925,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5944,15 +5955,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6001,7 +6012,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6017,7 +6028,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6025,7 +6036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6061,7 +6072,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6097,7 +6108,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6133,7 +6144,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6169,7 +6180,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6199,7 +6210,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6215,7 +6226,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6231,7 +6242,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6247,7 +6258,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6277,7 +6288,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6307,7 +6318,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6343,7 +6354,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6379,7 +6390,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6415,13 +6426,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6451,7 +6462,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6467,7 +6478,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6483,7 +6494,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6519,7 +6530,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6555,7 +6566,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6591,7 +6602,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6620,7 +6631,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6628,7 +6639,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6665,7 +6676,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6702,7 +6713,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6739,7 +6750,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6776,7 +6787,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6813,7 +6824,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6829,12 +6840,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6883,7 +6894,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6932,7 +6943,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6981,7 +6992,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7030,7 +7041,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7079,7 +7090,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7128,7 +7139,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7177,7 +7188,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7226,7 +7237,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7275,7 +7286,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7324,7 +7335,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7373,7 +7384,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7422,7 +7433,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7471,12 +7482,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7525,7 +7536,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7574,12 +7585,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7628,7 +7639,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7677,7 +7688,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7726,7 +7737,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7775,13 +7786,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7830,7 +7841,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7879,7 +7890,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7928,7 +7939,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7977,7 +7988,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8026,12 +8037,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8081,7 +8092,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8130,7 +8141,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8180,7 +8191,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8229,7 +8240,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8279,7 +8290,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8295,13 +8306,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8350,7 +8361,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8384,7 +8395,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8418,7 +8429,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8467,7 +8478,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8548,18 +8559,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8575,7 +8586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8586,7 +8597,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8606,7 +8617,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8628,7 +8639,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8649,7 +8660,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8670,7 +8681,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8691,7 +8702,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8712,7 +8723,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8733,7 +8744,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8745,7 +8756,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8758,7 +8769,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8782,12 +8793,12 @@
         <v>12999518734.206001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8807,7 +8818,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8828,7 +8839,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8849,7 +8860,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8869,7 +8880,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8889,7 +8900,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8910,7 +8921,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8930,7 +8941,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8950,7 +8961,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8962,7 +8973,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8975,7 +8986,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8999,7 +9010,7 @@
         <v>199239941.08700001</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9016,7 +9027,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9035,7 +9046,7 @@
         <v>4020530411.1730003</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9050,7 +9061,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9069,7 +9080,7 @@
         <v>3682947949.0330005</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9085,7 +9096,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9102,7 +9113,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9122,7 +9133,7 @@
         <v>16403011248.183001</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9133,7 +9144,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9146,7 +9157,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9165,7 +9176,7 @@
         <v>3204252572.8899999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9181,7 +9192,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9197,7 +9208,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9213,7 +9224,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9232,7 +9243,7 @@
         <v>643531523.5710001</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9252,7 +9263,7 @@
         <v>13198758675.293001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9272,7 +9283,7 @@
         <v>9513778692.0960007</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9291,7 +9302,7 @@
         <v>3684979983.197</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9302,7 +9313,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9316,7 +9327,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9330,7 +9341,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9345,10 +9356,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9361,7 +9372,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9375,7 +9386,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9386,10 +9397,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9401,7 +9412,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9415,7 +9426,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9429,10 +9440,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9444,7 +9455,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9455,7 +9466,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9466,10 +9477,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9481,7 +9492,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9497,7 +9508,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9508,7 +9519,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9522,7 +9533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9538,7 +9549,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9548,7 +9559,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9558,7 +9569,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9568,7 +9579,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9578,10 +9589,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9593,7 +9604,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9609,7 +9620,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9625,7 +9636,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9638,7 +9649,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9651,10 +9662,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9666,7 +9677,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9680,7 +9691,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9694,7 +9705,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9708,7 +9719,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9722,7 +9733,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9733,7 +9744,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9741,7 +9752,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9758,7 +9769,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9775,7 +9786,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9792,7 +9803,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9823,19 +9834,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9892,7 +9903,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9915,7 +9926,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9929,7 +9940,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9986,7 +9997,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10041,7 +10052,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10096,7 +10107,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10151,7 +10162,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10208,7 +10219,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10263,7 +10274,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10318,7 +10329,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10375,7 +10386,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10430,7 +10441,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10485,7 +10496,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10540,7 +10551,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10597,7 +10608,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10654,7 +10665,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10680,7 +10691,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10705,7 +10716,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10762,7 +10773,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10781,7 +10792,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10804,7 +10815,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10825,7 +10836,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10882,7 +10893,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10939,7 +10950,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10996,18 +11007,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11066,7 +11077,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11126,7 +11137,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11181,18 +11192,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11249,7 +11260,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11308,7 +11319,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11365,18 +11376,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11434,7 +11445,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11492,7 +11503,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11547,18 +11558,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11616,10 +11627,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11642,14 +11653,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11704,7 +11715,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11759,7 +11770,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11816,7 +11827,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11871,11 +11882,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11885,7 +11896,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11911,7 +11922,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11938,7 +11949,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11993,11 +12004,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12007,7 +12018,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12062,7 +12073,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12117,7 +12128,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12172,7 +12183,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12227,7 +12238,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12283,7 +12294,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12338,11 +12349,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12352,7 +12363,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12377,7 +12388,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12402,7 +12413,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12427,7 +12438,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12454,10 +12465,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12480,7 +12491,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12501,7 +12512,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12558,7 +12569,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12615,7 +12626,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12672,7 +12683,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12729,7 +12740,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12786,7 +12797,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12845,7 +12856,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12902,7 +12913,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12959,7 +12970,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13016,7 +13027,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13073,7 +13084,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13131,7 +13142,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13188,7 +13199,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13214,7 +13225,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13238,7 +13249,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13295,18 +13306,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13362,7 +13373,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13418,7 +13429,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13473,31 +13484,31 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7986704653371325E-2</v>
+        <v>3.8167938931297711E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7986704653371325E-2</v>
+        <v>3.8167938931297711E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4074074074074084E-2</v>
+        <v>7.4427480916030533E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1225071225071226E-2</v>
+        <v>7.15648854961832E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4577397910731249E-2</v>
+        <v>6.4885496183206104E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -13528,11 +13539,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13553,7 +13564,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13610,7 +13621,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13667,10 +13678,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13693,7 +13704,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13703,7 +13714,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13760,7 +13771,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13817,7 +13828,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13874,7 +13885,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13931,7 +13942,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13988,11 +13999,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14015,7 +14026,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14072,7 +14083,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14129,7 +14140,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14156,18 +14167,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14219,7 +14230,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14271,11 +14282,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14329,7 +14340,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14384,7 +14395,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14438,7 +14449,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14494,7 +14505,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14551,7 +14562,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14570,7 +14581,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14593,7 +14604,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14614,7 +14625,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14672,795 +14683,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3505640872466456E-2</v>
+        <v>3.3665496029300739E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>2.2870416045774954E-2</v>
+        <v>2.2979530626146015E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1144338811763173</v>
+        <v>0.11497984434986841</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.8959413557378483E-2</v>
+        <v>7.9336128316717117E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.5682253144826827E-2</v>
+        <v>6.599562267318955E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10797871098004538</v>
+        <v>0.10849387658586619</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10218115406034745</v>
+        <v>0.10266865956636055</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.8248128252271805E-2</v>
+        <v>9.8716869322177672E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10967503566418212</v>
+        <v>0.11019829442212191</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.1218116562638882E-2</v>
+        <v>9.1653317500437731E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.4407554330717079E-2</v>
+        <v>7.4762552204432314E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3318607756485531E-2</v>
+        <v>5.3572990427079442E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13303261183165277</v>
+        <v>0.13366730940718544</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13046976371341334</v>
+        <v>0.13109223396013764</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13957513258373305</v>
+        <v>0.14024104447583099</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1245865117610121</v>
+        <v>0.12518091305758181</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11786298221804901</v>
+        <v>0.11842530560649389</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11070785763368034</v>
+        <v>0.11123604397735247</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8848721907765225E-2</v>
+        <v>9.9320328405416769E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7118811208551999E-2</v>
+        <v>8.7534454391798897E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9100920174854344E-2</v>
+        <v>7.9478310061184748E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15482,16 +15493,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15503,7 +15514,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15516,7 +15527,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15537,7 +15548,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15548,7 +15559,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15566,7 +15577,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15582,7 +15593,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15598,7 +15609,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15614,7 +15625,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15628,7 +15639,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15642,7 +15653,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15656,10 +15667,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15669,13 +15680,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15685,7 +15696,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15695,7 +15706,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15709,10 +15720,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15730,7 +15741,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15752,7 +15763,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15774,7 +15785,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15806,7 +15817,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15838,7 +15849,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15870,7 +15881,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15892,7 +15903,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15914,7 +15925,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15936,7 +15947,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15958,7 +15969,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15980,7 +15991,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16002,7 +16013,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16024,7 +16035,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16056,7 +16067,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16088,7 +16099,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16120,7 +16131,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16142,7 +16153,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16164,7 +16175,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16186,7 +16197,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16208,7 +16219,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16230,7 +16241,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16252,7 +16263,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16274,7 +16285,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16296,7 +16307,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16318,7 +16329,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16340,7 +16351,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16362,7 +16373,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16394,7 +16405,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16426,7 +16437,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16458,7 +16469,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16490,7 +16501,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16512,7 +16523,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16523,11 +16534,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16537,7 +16548,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>8487371563.7394762</v>
@@ -16564,7 +16575,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16586,7 +16597,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16607,7 +16618,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16638,7 +16649,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16669,7 +16680,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16700,7 +16711,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16731,7 +16742,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16748,7 +16759,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16768,7 +16779,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16791,7 +16802,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16817,7 +16828,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16844,7 +16855,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16871,7 +16882,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16898,7 +16909,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16925,7 +16936,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16951,7 +16962,7 @@
         <v>16.101034060730154</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16977,7 +16988,7 @@
         <v>17.090421917574211</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16994,7 +17005,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17016,7 +17027,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17039,7 +17050,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17062,7 +17073,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17085,7 +17096,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17107,14 +17118,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17122,26 +17133,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17155,7 +17166,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17169,7 +17180,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17183,7 +17194,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17197,7 +17208,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17242,16 +17253,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17263,7 +17274,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17276,7 +17287,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17297,7 +17308,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17308,7 +17319,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17324,7 +17335,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17338,10 +17349,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17351,13 +17362,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17367,7 +17378,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17377,7 +17388,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17391,10 +17402,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17412,7 +17423,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17434,7 +17445,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17456,7 +17467,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17478,7 +17489,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17500,7 +17511,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17522,7 +17533,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17544,7 +17555,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17566,7 +17577,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17588,7 +17599,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17610,7 +17621,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17632,7 +17643,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17654,7 +17665,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17676,7 +17687,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17698,7 +17709,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17720,7 +17731,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17742,7 +17753,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17764,7 +17775,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17786,7 +17797,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17808,7 +17819,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17830,7 +17841,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17852,7 +17863,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17874,7 +17885,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17896,7 +17907,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17918,7 +17929,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17940,7 +17951,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17962,7 +17973,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17984,7 +17995,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18006,7 +18017,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18028,7 +18039,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18050,7 +18061,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18072,7 +18083,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18094,7 +18105,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18105,11 +18116,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18119,7 +18130,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>9622477543.4793949</v>
@@ -18146,7 +18157,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18168,7 +18179,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18189,7 +18200,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18210,7 +18221,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18231,7 +18242,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18252,7 +18263,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18273,14 +18284,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18290,7 +18301,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18313,7 +18324,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18339,7 +18350,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18366,7 +18377,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18393,7 +18404,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18420,7 +18431,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18447,7 +18458,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18473,7 +18484,7 @@
         <v>10.492315741081677</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18499,7 +18510,7 @@
         <v>11.614024901895009</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18516,7 +18527,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18538,7 +18549,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18561,7 +18572,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18584,7 +18595,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18607,7 +18618,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18629,14 +18640,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18644,23 +18655,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18690,17 +18701,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18713,7 +18724,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18722,10 +18733,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.53</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-10.48</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18745,7 +18756,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18754,7 +18765,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18774,7 +18785,7 @@
         <v>13.315286704532291</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18799,7 +18810,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18821,7 +18832,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18843,7 +18854,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18854,7 +18865,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18868,7 +18879,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18887,7 +18898,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18905,7 +18916,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18916,7 +18927,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18925,7 +18936,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18933,7 +18944,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18945,24 +18956,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.53</v>
+        <v>10.48</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18971,7 +18982,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18986,7 +18997,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18995,7 +19006,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19007,7 +19018,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19018,7 +19029,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19033,7 +19044,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19044,7 +19055,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19053,7 +19064,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19065,7 +19076,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19076,7 +19087,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19091,7 +19102,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19102,7 +19113,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19111,7 +19122,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19123,7 +19134,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19134,7 +19145,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19149,7 +19160,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19161,7 +19172,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19174,7 +19185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19183,12 +19194,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19198,12 +19209,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19212,7 +19223,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19224,7 +19235,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19235,7 +19246,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19250,7 +19261,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19261,7 +19272,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19270,7 +19281,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19282,7 +19293,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19293,7 +19304,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19308,7 +19319,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19319,7 +19330,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19339,7 +19350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19348,7 +19359,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19356,7 +19367,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19369,7 +19380,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19381,7 +19392,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19397,7 +19408,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19405,7 +19416,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19415,7 +19426,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19427,7 +19438,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19437,7 +19448,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19453,7 +19464,7 @@
         <v>0.53010312915742175</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19462,12 +19473,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19477,7 +19488,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19490,33 +19501,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19526,7 +19537,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19546,45 +19557,45 @@
         <v>0.52813732651388556</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.53</v>
+        <v>10.48</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10602554910062834</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>0.10784223317227548</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19593,7 +19604,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19605,7 +19616,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19615,7 +19626,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19635,14 +19646,14 @@
         <v>0.33548180120394178</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19653,7 +19664,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19665,7 +19676,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19677,7 +19688,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19696,15 +19707,15 @@
         <v>7.7594728220778397E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19713,7 +19724,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19723,7 +19734,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19733,7 +19744,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19752,16 +19763,16 @@
         <v>0.14359457232654926</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19769,7 +19780,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19777,7 +19788,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778CC860-2855-654A-A284-92B41A90B81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAB34F1-EE5D-4D00-A4CB-DF01DFE5FEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2513,7 +2502,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3905,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3943,7 +3932,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4232,7 +4221,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4241,7 +4230,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4272,7 +4261,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4281,7 +4270,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +4287,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4308,7 +4297,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4318,17 +4307,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4340,17 +4329,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4360,13 +4349,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14619.833777360001</v>
+        <v>14647.7342235</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4388,7 +4377,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4398,27 +4387,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4433,7 +4422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4446,7 +4435,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4454,7 +4443,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4462,7 +4451,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4478,7 +4467,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4492,14 +4481,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10784223317227548</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.10711414403848307</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4518,7 +4507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4537,7 +4526,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4556,7 +4545,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4575,7 +4564,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4594,11 +4583,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4608,25 +4597,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4635,16 +4624,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4657,20 +4646,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4683,7 +4672,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4696,16 +4685,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4718,16 +4707,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4742,7 +4731,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4757,7 +4746,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4770,12 +4759,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4788,16 +4777,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4810,8 +4799,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,7 +4808,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4832,25 +4821,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4863,7 +4852,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4876,23 +4865,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.3665496029300739E-2</v>
+        <v>3.360137127495922E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8167938931297711E-2</v>
+        <v>3.8095238095238099E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4902,7 +4891,7 @@
         <v>1.1337405781301506</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4913,7 +4902,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4926,7 +4915,7 @@
         <v>4.2520188912675866E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4940,7 +4929,7 @@
         <v>8.3218084848475898E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4954,7 +4943,7 @@
         <v>0.30413488760323026</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4968,7 +4957,7 @@
         <v>1.6800075256655487</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4978,34 +4967,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5014,7 +5003,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5023,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5032,34 +5021,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5067,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5080,7 +5069,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5090,38 +5079,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5134,7 +5123,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5147,7 +5136,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5156,7 +5145,7 @@
         <v>9.2587702159681276E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5165,12 +5154,12 @@
         <v>2.0939079363495856</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5183,7 +5172,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5196,7 +5185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5209,12 +5198,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5227,7 +5216,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5240,16 +5229,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5262,7 +5251,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5275,7 +5264,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5285,16 +5274,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5311,7 +5300,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5333,7 +5322,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5355,7 +5344,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5377,7 +5366,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5399,7 +5388,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5421,7 +5410,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5434,16 +5423,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5453,30 +5442,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5485,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5494,7 +5483,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5507,7 +5496,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5520,7 +5509,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5529,7 +5518,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5539,7 +5528,7 @@
         <v>0.69031028314322296</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5549,7 +5538,7 @@
         <v>5.4039314300970522</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5562,7 +5551,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5584,12 +5573,12 @@
         <v>0.52813732651388556</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5598,7 +5587,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5608,7 +5597,7 @@
         <v>0.86005014536183588</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5618,7 +5607,7 @@
         <v>7.7223929124686403</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5631,7 +5620,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5644,7 +5633,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5653,12 +5642,12 @@
         <v>0.33548180120394178</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5667,7 +5656,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5677,7 +5666,7 @@
         <v>1.069204779784656</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5687,7 +5676,7 @@
         <v>10.843923763016019</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5700,7 +5689,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5713,7 +5702,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5722,12 +5711,12 @@
         <v>7.7594728220778397E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5736,7 +5725,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5746,7 +5735,7 @@
         <v>1.0179560233797402</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5756,7 +5745,7 @@
         <v>10.055772032466596</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5769,7 +5758,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5782,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5791,7 +5780,7 @@
         <v>0.14359457232654926</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5801,21 +5790,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5824,91 +5813,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5925,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5955,15 +5944,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6012,7 +6001,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6028,7 +6017,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6036,7 +6025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6072,7 +6061,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6108,7 +6097,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6144,7 +6133,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6180,7 +6169,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6210,7 +6199,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6226,7 +6215,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6242,7 +6231,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6258,7 +6247,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6288,7 +6277,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6318,7 +6307,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6354,7 +6343,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6390,7 +6379,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6426,13 +6415,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6462,7 +6451,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6478,7 +6467,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6494,7 +6483,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6530,7 +6519,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6566,7 +6555,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6602,7 +6591,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6631,7 +6620,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6639,7 +6628,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6676,7 +6665,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6713,7 +6702,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6750,7 +6739,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6787,7 +6776,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6824,7 +6813,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6840,12 +6829,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6894,7 +6883,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6943,7 +6932,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6992,7 +6981,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7041,7 +7030,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7090,7 +7079,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7139,7 +7128,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7188,7 +7177,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7237,7 +7226,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7286,7 +7275,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7335,7 +7324,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7384,7 +7373,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7433,7 +7422,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7482,12 +7471,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7536,7 +7525,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7585,12 +7574,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7639,7 +7628,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7688,7 +7677,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7737,7 +7726,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7786,13 +7775,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7841,7 +7830,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7890,7 +7879,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7939,7 +7928,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7988,7 +7977,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8037,12 +8026,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8092,7 +8081,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8141,7 +8130,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8191,7 +8180,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8240,7 +8229,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8290,7 +8279,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8306,13 +8295,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8361,7 +8350,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8395,7 +8384,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8429,7 +8418,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8478,7 +8467,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8559,7 +8548,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8570,7 +8559,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8586,7 +8575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8597,7 +8586,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8617,7 +8606,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8639,7 +8628,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8660,7 +8649,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8681,7 +8670,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8702,7 +8691,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8723,7 +8712,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8744,7 +8733,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8756,7 +8745,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8769,7 +8758,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8793,12 +8782,12 @@
         <v>12999518734.206001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8818,7 +8807,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8839,7 +8828,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8860,7 +8849,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8880,7 +8869,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8900,7 +8889,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8921,7 +8910,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8941,7 +8930,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8961,7 +8950,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8973,7 +8962,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8986,7 +8975,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9010,7 +8999,7 @@
         <v>199239941.08700001</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9027,7 +9016,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9046,7 +9035,7 @@
         <v>4020530411.1730003</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9061,7 +9050,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9080,7 +9069,7 @@
         <v>3682947949.0330005</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9096,7 +9085,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9113,7 +9102,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9133,7 +9122,7 @@
         <v>16403011248.183001</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9144,7 +9133,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9157,7 +9146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9176,7 +9165,7 @@
         <v>3204252572.8899999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9192,7 +9181,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9208,7 +9197,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9224,7 +9213,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9243,7 +9232,7 @@
         <v>643531523.5710001</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9263,7 +9252,7 @@
         <v>13198758675.293001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9283,7 +9272,7 @@
         <v>9513778692.0960007</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9302,7 +9291,7 @@
         <v>3684979983.197</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9313,7 +9302,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9327,7 +9316,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9341,7 +9330,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9356,10 +9345,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9372,7 +9361,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9386,7 +9375,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9397,10 +9386,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9412,7 +9401,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9426,7 +9415,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9440,10 +9429,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9455,7 +9444,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9466,7 +9455,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9477,10 +9466,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9492,7 +9481,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9508,7 +9497,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9519,7 +9508,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9533,7 +9522,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9549,7 +9538,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9559,7 +9548,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9569,7 +9558,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9579,7 +9568,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9589,10 +9578,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9604,7 +9593,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9620,7 +9609,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9636,7 +9625,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9649,7 +9638,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9662,10 +9651,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9677,7 +9666,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9691,7 +9680,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9705,7 +9694,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9719,7 +9708,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9733,7 +9722,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9744,7 +9733,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9752,7 +9741,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9769,7 +9758,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9786,7 +9775,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9803,7 +9792,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9834,19 +9823,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9903,7 +9892,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9926,7 +9915,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9940,7 +9929,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9997,7 +9986,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10052,7 +10041,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10107,7 +10096,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10162,7 +10151,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10219,7 +10208,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10274,7 +10263,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10329,7 +10318,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10386,7 +10375,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10441,7 +10430,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10496,7 +10485,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10551,7 +10540,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10608,7 +10597,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10665,7 +10654,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10691,7 +10680,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10716,7 +10705,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10773,7 +10762,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10792,7 +10781,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10815,7 +10804,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10836,7 +10825,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10893,7 +10882,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10950,7 +10939,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11007,18 +10996,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11077,7 +11066,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11137,7 +11126,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11192,18 +11181,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11260,7 +11249,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11319,7 +11308,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11376,18 +11365,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11445,7 +11434,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11503,7 +11492,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11558,18 +11547,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11627,10 +11616,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11653,14 +11642,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11715,7 +11704,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11770,7 +11759,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11827,7 +11816,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11882,11 +11871,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11896,7 +11885,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11922,7 +11911,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11949,7 +11938,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -12004,11 +11993,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12018,7 +12007,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12073,7 +12062,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12128,7 +12117,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12183,7 +12172,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12238,7 +12227,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12294,7 +12283,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12349,11 +12338,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12363,7 +12352,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12388,7 +12377,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12413,7 +12402,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12438,7 +12427,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12465,10 +12454,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12491,7 +12480,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12512,7 +12501,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12569,7 +12558,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12626,7 +12615,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12683,7 +12672,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12740,7 +12729,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12797,7 +12786,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12856,7 +12845,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12913,7 +12902,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12970,7 +12959,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13027,7 +13016,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13084,7 +13073,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13142,7 +13131,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13199,7 +13188,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13225,7 +13214,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13249,7 +13238,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13306,18 +13295,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13373,7 +13362,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13429,7 +13418,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13484,31 +13473,31 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8167938931297711E-2</v>
+        <v>3.8095238095238099E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8167938931297711E-2</v>
+        <v>3.8095238095238099E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4427480916030533E-2</v>
+        <v>7.4285714285714288E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.15648854961832E-2</v>
+        <v>7.1428571428571425E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4885496183206104E-2</v>
+        <v>6.4761904761904757E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -13539,11 +13528,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13564,7 +13553,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13621,7 +13610,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13678,10 +13667,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13704,7 +13693,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13714,7 +13703,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13771,7 +13760,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13828,7 +13817,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13885,7 +13874,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13942,7 +13931,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13999,11 +13988,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14026,7 +14015,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14083,7 +14072,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14140,7 +14129,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14167,18 +14156,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14230,7 +14219,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14282,11 +14271,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14340,7 +14329,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14395,7 +14384,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14449,7 +14438,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14505,7 +14494,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14562,7 +14551,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14581,7 +14570,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14604,7 +14593,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14625,7 +14614,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14683,795 +14672,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3665496029300739E-2</v>
+        <v>3.360137127495922E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>2.2979530626146015E-2</v>
+        <v>2.2935760091620024E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11497984434986841</v>
+        <v>0.11476083512253533</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.9336128316717117E-2</v>
+        <v>7.9185011881828138E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.599562267318955E-2</v>
+        <v>6.5869916725240618E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10849387658586619</v>
+        <v>0.1082872215828455</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10266865956636055</v>
+        <v>0.10247310021480557</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.8716869322177672E-2</v>
+        <v>9.8528837190135429E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.11019829442212191</v>
+        <v>0.10998839290893692</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.1653317500437731E-2</v>
+        <v>9.1478739752817853E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.4762552204432314E-2</v>
+        <v>7.4620147343090554E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3572990427079442E-2</v>
+        <v>5.3470946635789766E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13366730940718544</v>
+        <v>0.13341270500831462</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13109223396013764</v>
+        <v>0.13084253446688024</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14024104447583099</v>
+        <v>0.1399739186768294</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12518091305758181</v>
+        <v>0.12494247322318641</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11842530560649389</v>
+        <v>0.11819973359581486</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11123604397735247</v>
+        <v>0.11102416579834799</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9320328405416769E-2</v>
+        <v>9.9131146827501695E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7534454391798897E-2</v>
+        <v>8.7367722097719286E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9478310061184748E-2</v>
+        <v>7.9326922803925351E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15493,16 +15482,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15514,7 +15503,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15527,7 +15516,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15548,7 +15537,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15559,7 +15548,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15577,7 +15566,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15593,7 +15582,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15609,7 +15598,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15625,7 +15614,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15639,7 +15628,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15653,7 +15642,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15667,10 +15656,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15680,13 +15669,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15696,7 +15685,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15706,7 +15695,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15720,10 +15709,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15741,7 +15730,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15763,7 +15752,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15785,7 +15774,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15817,7 +15806,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15849,7 +15838,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15881,7 +15870,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15903,7 +15892,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15925,7 +15914,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15947,7 +15936,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15969,7 +15958,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15991,7 +15980,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16013,7 +16002,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16035,7 +16024,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16067,7 +16056,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16099,7 +16088,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16131,7 +16120,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16153,7 +16142,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16175,7 +16164,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16197,7 +16186,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16219,7 +16208,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16241,7 +16230,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16263,7 +16252,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16285,7 +16274,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16307,7 +16296,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16329,7 +16318,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16351,7 +16340,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16373,7 +16362,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16405,7 +16394,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16437,7 +16426,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16469,7 +16458,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16501,7 +16490,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16523,7 +16512,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16534,11 +16523,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16548,7 +16537,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>8487371563.7394762</v>
@@ -16575,7 +16564,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16597,7 +16586,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16618,7 +16607,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16649,7 +16638,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16680,7 +16669,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16711,7 +16700,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16742,7 +16731,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16759,7 +16748,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16779,7 +16768,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16802,7 +16791,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16828,7 +16817,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16855,7 +16844,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16882,7 +16871,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16909,7 +16898,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16936,7 +16925,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16962,7 +16951,7 @@
         <v>16.101034060730154</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16988,7 +16977,7 @@
         <v>17.090421917574211</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -17005,7 +16994,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17027,7 +17016,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17050,7 +17039,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17073,7 +17062,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17096,7 +17085,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17118,14 +17107,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17133,26 +17122,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17166,7 +17155,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17180,7 +17169,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17194,7 +17183,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17208,7 +17197,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17253,16 +17242,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17274,7 +17263,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17287,7 +17276,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17308,7 +17297,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17319,7 +17308,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17335,7 +17324,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17349,10 +17338,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17362,13 +17351,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17378,7 +17367,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17388,7 +17377,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17402,10 +17391,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17423,7 +17412,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17445,7 +17434,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17467,7 +17456,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17489,7 +17478,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17511,7 +17500,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17533,7 +17522,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17555,7 +17544,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17577,7 +17566,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17599,7 +17588,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17621,7 +17610,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17643,7 +17632,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17665,7 +17654,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17687,7 +17676,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17709,7 +17698,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17731,7 +17720,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17753,7 +17742,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17775,7 +17764,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17797,7 +17786,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17819,7 +17808,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17841,7 +17830,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17863,7 +17852,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17885,7 +17874,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17907,7 +17896,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17929,7 +17918,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17951,7 +17940,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17973,7 +17962,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17995,7 +17984,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18017,7 +18006,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18039,7 +18028,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18061,7 +18050,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18083,7 +18072,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18105,7 +18094,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18116,11 +18105,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18130,7 +18119,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>9622477543.4793949</v>
@@ -18157,7 +18146,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18179,7 +18168,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18200,7 +18189,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18221,7 +18210,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18242,7 +18231,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18263,7 +18252,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18284,14 +18273,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18301,7 +18290,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18324,7 +18313,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18350,7 +18339,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18377,7 +18366,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18404,7 +18393,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18431,7 +18420,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18458,7 +18447,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18484,7 +18473,7 @@
         <v>10.492315741081677</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18510,7 +18499,7 @@
         <v>11.614024901895009</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18527,7 +18516,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18549,7 +18538,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18572,7 +18561,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18595,7 +18584,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18618,7 +18607,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18640,14 +18629,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18655,23 +18644,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18701,7 +18690,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18711,7 +18700,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18724,7 +18713,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18733,10 +18722,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.48</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-10.5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18756,7 +18745,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18765,7 +18754,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18785,7 +18774,7 @@
         <v>13.315286704532291</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18810,7 +18799,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18832,7 +18821,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18854,7 +18843,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18865,7 +18854,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18879,7 +18868,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18898,7 +18887,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18916,7 +18905,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18927,7 +18916,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18936,7 +18925,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18944,7 +18933,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18956,24 +18945,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18982,7 +18971,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18997,7 +18986,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -19006,7 +18995,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19018,7 +19007,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19029,7 +19018,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19044,7 +19033,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19055,7 +19044,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19064,7 +19053,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19076,7 +19065,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19087,7 +19076,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19102,7 +19091,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19113,7 +19102,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19122,7 +19111,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19134,7 +19123,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19145,7 +19134,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19160,7 +19149,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19172,7 +19161,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19185,7 +19174,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19194,12 +19183,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19209,12 +19198,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19223,7 +19212,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19235,7 +19224,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19246,7 +19235,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19261,7 +19250,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19272,7 +19261,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19281,7 +19270,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19293,7 +19282,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19304,7 +19293,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19319,7 +19308,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19330,7 +19319,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19350,7 +19339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19359,7 +19348,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19367,7 +19356,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19380,7 +19369,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19392,7 +19381,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19408,7 +19397,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19416,7 +19405,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19426,7 +19415,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19438,7 +19427,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19448,7 +19437,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19464,7 +19453,7 @@
         <v>0.53010312915742175</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19473,12 +19462,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19488,7 +19477,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19501,12 +19490,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19515,7 +19504,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19527,7 +19516,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19537,7 +19526,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19557,45 +19546,45 @@
         <v>0.52813732651388556</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10784223317227548</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.10711414403848307</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19604,7 +19593,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19616,7 +19605,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19626,7 +19615,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19646,14 +19635,14 @@
         <v>0.33548180120394178</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19664,7 +19653,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19676,7 +19665,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19688,7 +19677,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19707,15 +19696,15 @@
         <v>7.7594728220778397E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19724,7 +19713,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19734,7 +19723,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19744,7 +19733,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19763,16 +19752,16 @@
         <v>0.14359457232654926</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19780,7 +19769,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19788,7 +19777,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAB34F1-EE5D-4D00-A4CB-DF01DFE5FEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2B38DA-0ECD-4C67-80AA-2F24A841B2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.5</v>
+        <v>10.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14647.7342235</v>
+        <v>14773.28623113</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10711414403848307</v>
+        <v>0.10386099380261116</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.360137127495922E-2</v>
+        <v>3.3315807213132369E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.8095238095238099E-2</v>
+        <v>3.7771482530689335E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,24 +13480,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.8095238095238099E-2</v>
+        <v>3.7771482530689335E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.8095238095238099E-2</v>
+        <v>3.7771482530689335E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4285714285714288E-2</v>
+        <v>7.3654390934844202E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1428571428571425E-2</v>
+        <v>7.0821529745042494E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4761904761904757E-2</v>
+        <v>6.4211520302171851E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.360137127495922E-2</v>
+        <v>3.3315807213132369E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>2.2935760091620024E-2</v>
+        <v>2.2740838617753566E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11476083512253533</v>
+        <v>0.11378553057475174</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.9185011881828138E-2</v>
+        <v>7.8512051440906075E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.5869916725240618E-2</v>
+        <v>6.53101157332414E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.1082872215828455</v>
+        <v>0.10736693358072501</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10247310021480557</v>
+        <v>0.10160222400901403</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.8528837190135429E-2</v>
+        <v>9.7691481633278759E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10998839290893692</v>
+        <v>0.10905364736013576</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.1478739752817853E-2</v>
+        <v>9.0701300038204674E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.4620147343090554E-2</v>
+        <v>7.3985981784933971E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3470946635789766E-2</v>
+        <v>5.3016519327270313E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13341270500831462</v>
+        <v>0.13227888598558107</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13084253446688024</v>
+        <v>0.1297305582532807</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1399739186768294</v>
+        <v>0.13878433863141726</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12494247322318641</v>
+        <v>0.12388063917313101</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11819973359581486</v>
+        <v>0.11719520328196942</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11102416579834799</v>
+        <v>0.11008061764708725</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9131146827501695E-2</v>
+        <v>9.8288672491857215E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7367722097719286E-2</v>
+        <v>8.662522021020326E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9326922803925351E-2</v>
+        <v>7.8652756321172454E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.5</v>
+        <v>-10.59</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.5</v>
+        <v>10.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.5</v>
+        <v>10.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10711414403848307</v>
+        <v>0.10386099380261116</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2B38DA-0ECD-4C67-80AA-2F24A841B2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A844741-D472-422E-A8A7-64037B2DCDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A844741-D472-422E-A8A7-64037B2DCDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564AEEB5-3DF2-458F-9D01-4CAC6B6F22CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564AEEB5-3DF2-458F-9D01-4CAC6B6F22CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DEB6B6-6DEA-4339-99F8-6C102F244B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DEB6B6-6DEA-4339-99F8-6C102F244B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA703957-E5C9-4835-96E7-13AC5338F850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.59</v>
+        <v>10.62</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14773.28623113</v>
+        <v>14815.136900339998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10386099380261116</v>
+        <v>0.1027849768295388</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.3315807213132369E-2</v>
+        <v>3.322169476337776E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7771482530689335E-2</v>
+        <v>3.7664783427495296E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,24 +13480,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7771482530689335E-2</v>
+        <v>3.7664783427495296E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7771482530689335E-2</v>
+        <v>3.7664783427495296E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3654390934844202E-2</v>
+        <v>7.3446327683615822E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.0821529745042494E-2</v>
+        <v>7.0621468926553674E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4211520302171851E-2</v>
+        <v>6.4030131826741998E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3315807213132369E-2</v>
+        <v>3.322169476337776E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>2.2740838617753566E-2</v>
+        <v>2.2676598960641271E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11378553057475174</v>
+        <v>0.1134641025222807</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.8512051440906075E-2</v>
+        <v>7.8290265984858332E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.53101157332414E-2</v>
+        <v>6.512562388088762E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10736693358072501</v>
+        <v>0.10706363715818058</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10160222400901403</v>
+        <v>0.10131521207678519</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.7691481633278759E-2</v>
+        <v>9.7415516995896623E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10905364736013576</v>
+        <v>0.10874558620940092</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.0701300038204674E-2</v>
+        <v>9.0445081676514827E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.3985981784933971E-2</v>
+        <v>7.3776981836388963E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3016519327270313E-2</v>
+        <v>5.286675514837972E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13227888598558107</v>
+        <v>0.13190521681613029</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1297305582532807</v>
+        <v>0.12936408774974037</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13878433863141726</v>
+        <v>0.13839229247709126</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12388063917313101</v>
+        <v>0.12353069386473235</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11719520328196942</v>
+        <v>0.11686414338569268</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11008061764708725</v>
+        <v>0.10976965545034406</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8288672491857215E-2</v>
+        <v>9.801102087464858E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.662522021020326E-2</v>
+        <v>8.6380516198310039E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8652756321172454E-2</v>
+        <v>7.8430573393711525E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.59</v>
+        <v>-10.62</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.59</v>
+        <v>10.62</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.59</v>
+        <v>10.62</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10386099380261116</v>
+        <v>0.1027849768295388</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA703957-E5C9-4835-96E7-13AC5338F850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F687C7-7D29-4747-B9C3-DA6D2F8966B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.62</v>
+        <v>10.71</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14815.136900339998</v>
+        <v>14940.688907970001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1027849768295388</v>
+        <v>9.9581634565672816E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.322169476337776E-2</v>
+        <v>3.2942520857803151E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7664783427495296E-2</v>
+        <v>3.7348272642390289E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,24 +13480,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7664783427495296E-2</v>
+        <v>3.7348272642390289E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7664783427495296E-2</v>
+        <v>3.7348272642390289E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3446327683615822E-2</v>
+        <v>7.2829131652661055E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.0621468926553674E-2</v>
+        <v>7.0028011204481794E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4030131826741998E-2</v>
+        <v>6.3492063492063475E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.322169476337776E-2</v>
+        <v>3.2942520857803151E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>2.2676598960641271E-2</v>
+        <v>2.2486039305509825E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1134641025222807</v>
+        <v>0.11251062266915228</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.8290265984858332E-2</v>
+        <v>7.7632364590027578E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.512562388088762E-2</v>
+        <v>6.4578349730628051E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10706363715818058</v>
+        <v>0.10616394272827989</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10131521207678519</v>
+        <v>0.10046382374000547</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.7415516995896623E-2</v>
+        <v>9.6596899206015122E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10874558620940092</v>
+        <v>0.10783175775385971</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.0445081676514827E-2</v>
+        <v>8.9685038973350825E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.3776981836388963E-2</v>
+        <v>7.3157007199108379E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.286675514837972E-2</v>
+        <v>5.2422496701754674E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13190521681613029</v>
+        <v>0.13079676961599473</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12936408774974037</v>
+        <v>0.12827699457537278</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13839229247709126</v>
+        <v>0.13722933203610727</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12353069386473235</v>
+        <v>0.1224926208070455</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11686414338569268</v>
+        <v>0.1158820917606028</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10976965545034406</v>
+        <v>0.10884722137092939</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.801102087464858E-2</v>
+        <v>9.7187398850491852E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6380516198310039E-2</v>
+        <v>8.5654629507567914E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8430573393711525E-2</v>
+        <v>7.7771492945024848E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.62</v>
+        <v>-10.71</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.62</v>
+        <v>10.71</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.62</v>
+        <v>10.71</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1027849768295388</v>
+        <v>9.9581634565672816E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F687C7-7D29-4747-B9C3-DA6D2F8966B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C598C9D-8AD0-466B-BDCD-676DAEBFFA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.71</v>
+        <v>10.67</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14940.688907970001</v>
+        <v>14884.888015690001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.9581634565672816E-2</v>
+        <v>0.10100079374860971</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.2942520857803151E-2</v>
+        <v>3.3066016718563428E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7348272642390289E-2</v>
+        <v>3.7488284910965328E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,24 +13480,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7348272642390289E-2</v>
+        <v>3.7488284910965328E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7348272642390289E-2</v>
+        <v>3.7488284910965328E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.2829131652661055E-2</v>
+        <v>7.3102155576382388E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.0028011204481794E-2</v>
+        <v>7.0290534208059988E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.3492063492063475E-2</v>
+        <v>6.3730084348641039E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.2942520857803151E-2</v>
+        <v>3.3066016718563428E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>2.2486039305509825E-2</v>
+        <v>2.257033561031024E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11251062266915228</v>
+        <v>0.11293240569696542</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.7632364590027578E-2</v>
+        <v>7.7923395010233876E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.4578349730628051E-2</v>
+        <v>6.482044288800623E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10616394272827989</v>
+        <v>0.10656193314150682</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10046382374000547</v>
+        <v>0.10084044538476651</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.6596899206015122E-2</v>
+        <v>9.6959024413910216E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10783175775385971</v>
+        <v>0.10823600051957241</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>8.9685038973350825E-2</v>
+        <v>9.0021252802679239E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.3157007199108379E-2</v>
+        <v>7.3431260272019752E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2422496701754674E-2</v>
+        <v>5.2619019650964625E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13079676961599473</v>
+        <v>0.13128710427247456</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12827699457537278</v>
+        <v>0.12875788302738916</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13722933203610727</v>
+        <v>0.13774378126585837</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1224926208070455</v>
+        <v>0.12295182463387604</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1158820917606028</v>
+        <v>0.11631651384780281</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10884722137092939</v>
+        <v>0.10925527093558142</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7187398850491852E-2</v>
+        <v>9.7551737740278144E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5654629507567914E-2</v>
+        <v>8.5975734023060219E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7771492945024848E-2</v>
+        <v>7.8063044933572273E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.71</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.71</v>
+        <v>10.67</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.71</v>
+        <v>10.67</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.9581634565672816E-2</v>
+        <v>0.10100079374860971</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C598C9D-8AD0-466B-BDCD-676DAEBFFA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4CE0FF-6D34-4BD0-8B20-8FC1F8BD0F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14884.888015690001</v>
+        <v>14912.78846183</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10100079374860971</v>
+        <v>0.10029030917921822</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.3066016718563428E-2</v>
+        <v>3.3004153263524023E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7488284910965328E-2</v>
+        <v>3.7418147801683822E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,24 +13480,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7488284910965328E-2</v>
+        <v>3.7418147801683822E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7488284910965328E-2</v>
+        <v>3.7418147801683822E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3102155576382388E-2</v>
+        <v>7.2965388213283452E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.0290534208059988E-2</v>
+        <v>7.0159027128157164E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.3730084348641039E-2</v>
+        <v>6.3610851262862492E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3066016718563428E-2</v>
+        <v>3.3004153263524023E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>2.257033561031024E-2</v>
+        <v>2.252810860262023E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11293240569696542</v>
+        <v>0.11272111962456698</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.7923395010233876E-2</v>
+        <v>7.7777607554648784E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.482044288800623E-2</v>
+        <v>6.4699169842378529E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10656193314150682</v>
+        <v>0.10636256563329072</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10084044538476651</v>
+        <v>0.10065178225027677</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>9.6959024413910216E-2</v>
+        <v>9.6777623058598883E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10823600051957241</v>
+        <v>0.10803350098632719</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.0021252802679239E-2</v>
+        <v>8.9852831375546074E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>7.3431260272019752E-2</v>
+        <v>7.3293877184513634E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2619019650964625E-2</v>
+        <v>5.2520574338240651E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13128710427247456</v>
+        <v>0.13104147825886844</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12875788302738916</v>
+        <v>0.12851698895250163</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13774378126585837</v>
+        <v>0.13748607540754992</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12295182463387604</v>
+        <v>0.12272179315654419</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11631651384780281</v>
+        <v>0.11609889642245613</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10925527093558142</v>
+        <v>0.1090508644417824</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7551737740278144E-2</v>
+        <v>9.7369227473224296E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5975734023060219E-2</v>
+        <v>8.5814881386908556E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8063044933572273E-2</v>
+        <v>7.791699620591358E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.67</v>
+        <v>-10.69</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10100079374860971</v>
+        <v>0.10029030917921822</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4CE0FF-6D34-4BD0-8B20-8FC1F8BD0F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29CD00C-C4FC-4EA8-A6B9-954CE59F33A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2445,6 +2434,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
@@ -2470,9 +2471,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3149,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3894,6 +3892,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4223,10 +4225,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4238,18 +4240,18 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4263,7 +4265,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4272,10 +4274,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4289,7 +4291,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4299,7 +4301,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4312,20 +4314,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4341,17 +4343,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4365,7 +4367,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4391,35 +4393,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4427,7 +4429,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4437,26 +4439,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4477,11 +4479,11 @@
         <v>12.91528670453229</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10029030917921822</v>
+        <v>9.6763347097292396E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4490,7 +4492,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4501,7 +4503,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4509,37 +4511,37 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>6.0942417132402751</v>
+        <v>6.0252106849259528</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>8.582443057830476</v>
+        <v>8.4964380432942921</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F30" s="312">
         <v>0.187</v>
@@ -4547,18 +4549,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.913128542800674</v>
+        <v>11.80620806482221</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F31" s="312">
         <v>0.06</v>
@@ -4566,18 +4568,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>11.073728055846336</v>
+        <v>10.971932453508362</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4589,7 +4591,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4597,45 +4599,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4650,18 +4652,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4674,7 +4676,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4686,17 +4688,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4708,17 +4710,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4733,7 +4735,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4748,7 +4750,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4761,12 +4763,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4778,17 +4780,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4800,17 +4802,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4821,27 +4823,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4854,7 +4856,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4867,24 +4869,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>3.3004153263524023E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
-        <v>3.7418147801683822E-2</v>
+        <f>Normalized_FCF!C94</f>
+        <v>3.3676333021515438E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4893,73 +4895,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>450</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>3.888300021475994E-2</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>4.2520188912675866E-2</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>7.6099586896956867E-2</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>8.3218084848475898E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.30413488760323032</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.30413488760323026</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.6800075256655485</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.6800075256655487</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4970,33 +4972,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5005,7 +5007,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5014,7 +5016,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5026,31 +5028,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5058,7 +5060,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5071,7 +5073,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5083,36 +5085,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5125,7 +5127,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5138,7 +5140,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5147,7 +5149,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5156,12 +5158,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5174,7 +5176,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5187,7 +5189,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5200,12 +5202,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5218,7 +5220,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5229,18 +5231,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+    <row r="116" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5253,7 +5255,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5266,7 +5268,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5274,30 +5276,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+    <row r="123" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5412,7 +5414,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5423,18 +5425,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+    <row r="134" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5443,31 +5445,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5476,20 +5478,20 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.4</v>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5498,7 +5500,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5511,11 +5513,11 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5525,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322296</v>
+        <v>0.62127925482890056</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5540,11 +5542,11 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>6.0942417132402751</v>
+        <v>6.0252106849259528</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5553,7 +5555,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5566,21 +5568,21 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.52813732651388556</v>
+        <v>0.53348223521731353</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5594,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.86005014536183588</v>
+        <v>0.77404513082565229</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5609,11 +5611,11 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>8.582443057830476</v>
+        <v>8.4964380432942921</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5622,7 +5624,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5635,21 +5637,21 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.33548180120394178</v>
+        <v>0.34214096537921346</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5663,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>1.069204779784656</v>
+        <v>0.9622843018061904</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5678,11 +5680,11 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.913128542800674</v>
+        <v>11.80620806482221</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5691,7 +5693,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5704,21 +5706,21 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7594728220778397E-2</v>
+        <v>8.5873327095470353E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5732,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>1.0179560233797402</v>
+        <v>0.91616042104176609</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5747,11 +5749,11 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>11.073728055846336</v>
+        <v>10.971932453508362</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5760,7 +5762,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5773,16 +5775,16 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.14359457232654926</v>
+        <v>0.15146710684391118</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5791,98 +5793,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+    </row>
+    <row r="191" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5920,7 +5922,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -5944,12 +5946,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -6201,7 +6203,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6217,7 +6219,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6233,7 +6235,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6485,7 +6487,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>401377348</v>
@@ -6521,7 +6523,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-5702735165</v>
@@ -6557,7 +6559,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-1440890089</v>
@@ -6625,7 +6627,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6778,7 +6780,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7179,7 +7181,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7228,7 +7230,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7576,12 +7578,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7630,7 +7632,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7679,7 +7681,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7728,7 +7730,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7930,7 +7932,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8182,7 +8184,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8548,15 +8550,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8577,7 +8579,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8588,19 +8590,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8661,7 +8663,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8682,7 +8684,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>5809566736.8500004</v>
@@ -8693,7 +8695,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8703,7 +8705,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8724,7 +8726,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8789,19 +8791,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8809,7 +8811,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <f>55162498.36</f>
@@ -8840,7 +8842,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8860,7 +8862,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>11101623.65</v>
@@ -8871,7 +8873,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8880,7 +8882,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8901,7 +8903,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>1925789668.97</v>
@@ -8921,7 +8923,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8941,7 +8943,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9001,16 +9003,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -9043,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>337582462.13999999</v>
@@ -9087,7 +9089,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9137,10 +9139,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9148,10 +9150,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9173,7 +9175,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9189,7 +9191,7 @@
         <v>84443071.049999997</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9205,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9234,14 +9236,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>84443071.049999997</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9261,7 +9263,7 @@
         <v>974532871.35000002</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9280,7 +9282,7 @@
         <v>1058975942.4</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9304,13 +9306,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9318,7 +9320,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9350,7 +9352,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9377,7 +9379,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9391,7 +9393,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9403,7 +9405,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9417,7 +9419,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9434,7 +9436,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9471,10 +9473,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9483,7 +9485,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9494,12 +9496,12 @@
         <v>1.8889170076983472E-2</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9510,13 +9512,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9524,7 +9526,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9535,12 +9537,12 @@
         <v>7551907966.0066681</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9550,7 +9552,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9560,7 +9562,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9570,7 +9572,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9583,7 +9585,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9595,7 +9597,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9606,12 +9608,12 @@
         <v>-754739311.85833323</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9622,12 +9624,12 @@
         <v>14.005981995839356</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9635,12 +9637,12 @@
         <v>3018957247.4333329</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9648,7 +9650,7 @@
         <v>4</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9656,10 +9658,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9668,7 +9670,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9682,7 +9684,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9696,7 +9698,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9710,7 +9712,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9724,7 +9726,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9735,15 +9737,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>289</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9760,7 +9762,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9777,7 +9779,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9794,7 +9796,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9822,17 +9824,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Q809"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10154,7 +10156,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10321,7 +10323,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10433,7 +10435,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10543,7 +10545,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10600,7 +10602,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10665,7 +10667,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10690,7 +10692,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10784,7 +10786,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -11003,7 +11005,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -11018,7 +11020,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11078,7 +11080,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11195,14 +11197,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-1811198118</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11260,7 +11262,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11372,7 +11374,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11554,21 +11556,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11622,7 +11624,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11707,7 +11709,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11762,7 +11764,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11878,11 +11880,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11894,7 +11896,7 @@
         <v>0.01</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11921,7 +11923,7 @@
         <v>7.5523791471175328E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12000,17 +12002,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12065,7 +12067,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12120,7 +12122,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12175,7 +12177,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12230,13 +12232,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12286,7 +12288,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12345,17 +12347,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12380,7 +12382,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12405,7 +12407,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12430,7 +12432,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12460,12 +12462,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>464</v>
+        <v>59</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12483,7 +12485,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12675,7 +12677,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12848,7 +12850,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12962,7 +12964,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13134,7 +13136,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13241,7 +13243,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13302,7 +13304,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13421,7 +13423,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13476,1310 +13478,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
-        <v>3.7418147801683822E-2</v>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0.1</v>
       </c>
       <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7418147801683822E-2</v>
-      </c>
-      <c r="H93" s="23">
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
+        <v>3.3676333021515438E-2</v>
+      </c>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>3.3676333021515438E-2</v>
+      </c>
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.2965388213283452E-2</v>
-      </c>
-      <c r="I93" s="23">
+        <v>6.5668849391955109E-2</v>
+      </c>
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>7.0159027128157164E-2</v>
-      </c>
-      <c r="J93" s="23">
+        <v>6.3143124415341451E-2</v>
+      </c>
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.3610851262862492E-2</v>
-      </c>
-      <c r="K93" s="23">
+        <v>5.7249766136576244E-2</v>
+      </c>
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>0</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-7.7312450922034648E-2</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>-1.4922594925019905E-2</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>-4.4628773345081973E-2</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>3.6269729862563826E-2</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>-8.159712721213952E-2</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>-2.2105536969906581E-2</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.13477883884265496</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>4.1500994753992382E-2</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.10121152055953919</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-8.5540276064757226E-2</v>
+        <f>C4/G4-1</f>
+        <v>0</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>-7.7312450922034648E-2</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>-1.4922594925019905E-2</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>-4.4628773345081973E-2</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>3.6269729862563826E-2</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>-8.159712721213952E-2</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>-2.2105536969906581E-2</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.13477883884265496</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>4.1500994753992382E-2</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.10121152055953919</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-8.5540276064757226E-2</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>-0.46054206274631104</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>0.19347745956851004</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>-2.0479523875572947E-2</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>-0.27684214648456862</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>8.6356932348575555E-2</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>1.1577307817227656E-2</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>-6.8155989871713563E-2</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>0.16030970995922544</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>0.13827332473663501</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>30591809954.200001</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>30591809954.200005</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>29289690562</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>28730992292</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>26567137006</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>24370351033</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>22814336624</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>23725530086</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>20480659318</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>18856419515</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>17607266697</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>1910217201.7599998</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>834568719</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>1061824178</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>925201481</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>854194501</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>1181367947</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>1152244678.0699999</v>
+        <f>BS!C4</f>
+        <v>1910217201.7599998</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>834568719</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>1061824178</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>925201481</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>854194501</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>1181367947</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="346">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="346">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>1152244678.0699999</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>959867234</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>1086298738</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1224714311</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>1118318039</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>1167338551</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346">
+      <c r="N104" s="346">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="346">
+      <c r="O104" s="346">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="346">
+      <c r="P104" s="346">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>12382480837.01</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>12382480837.01</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>10670434743</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>11040803287</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>9869570784</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>9001654126</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>8576109791</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>10230716015</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>8088092587</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>7643685931</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>7296360629</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>18209329117.190002</v>
+        <f>BS!G30</f>
+        <v>12382480837.01</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>12382480837.01</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>10670434743</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>11040803287</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>9869570784</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>9001654126</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>8576109791</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>10230716015</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>8088092587</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>7643685931</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>7296360629</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>18209329117.190002</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>18209329117.190002</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>18619255819</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>17690189005</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>16697566222</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>15368696907</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>14238226833</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>13494814071</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>12392566731</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>11212733584</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>10310906068</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>0.20531058367983332</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>8.96996376437975E-2</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.10530181488277855</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>9.0383659897526641E-2</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>7.9722797985151764E-2</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.114257247326982</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0.12384352270441747</v>
+        <v>0.20531058367983332</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>0.10316675082085623</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>8.96996376437975E-2</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.10772897338967163</v>
+        <f t="shared" si="43"/>
+        <v>0.10530181488277855</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.11964330368063654</v>
+        <f t="shared" si="43"/>
+        <v>9.0383659897526641E-2</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.10437370294701542</v>
+        <f t="shared" si="43"/>
+        <v>7.9722797985151764E-2</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.11290037949195163</v>
+        <f t="shared" si="43"/>
+        <v>0.114257247326982</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>7.1640261316845921E-2</v>
+        <f>C104/C$4</f>
+        <v>0.12384352270441747</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>0.10316675082085623</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.10772897338967163</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.11964330368063654</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.10437370294701542</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.11290037949195163</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A111" s="10"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>7.1640261316845921E-2</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
         <f>BS!$G$38/G$4</f>
         <v>7.1640261316845921E-2</v>
       </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
-    </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>0.51246538405156916</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>1.0010548272911994</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>1.0873463853609158</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>0.87988429994040696</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>1.5136449440453559</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>1.3438717265200504</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>1.6023137454131331</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>1.0352195540830447</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>1.8419646063299806</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>0.87072779948659185</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>0.51246538405156916</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>1.0010548272911994</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>1.0873463853609158</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>0.87988429994040696</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>1.5136449440453559</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>1.3438717265200504</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>1.6023137454131331</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>1.0352195540830447</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>1.8419646063299806</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>0.87072779948659185</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.1947286287373908</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.1637544483529516</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.7966930044329832</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.8697587543432195</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>1.746452999037496</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.5501168572888298</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.8055175723674355</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.93303028529084642</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.759187460108353</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.92565023512380407</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>7.6099586896956867E-2</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>8.3218084848475898E-2</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.14233601073459284</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.11748189040273076</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.11458547368798239</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.16419853188012928</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.1388129434220548</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.13419084010716401</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>0.12459677073871622</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>0.11183881299422052</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>0.10819737811516837</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.30413488760323032</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.30413488760323026</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.34427221225349319</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.35628354958872299</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.40330117135241905</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.42426737953011739</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.49346953683311268</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.4852441199530213</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>0.6496884405623411</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>0.67753253118053569</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>0.65891090523304974</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.6800075256655485</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.6800075256655487</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.5730859947749021</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>1.6241201427457559</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>1.5910784034499756</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>1.5857135566191045</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>1.6023299032659821</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.7581220431176996</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>1.6526567709954421</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>1.6816969183952744</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>1.7076352534763486</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>3.888300021475994E-2</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>4.2520188912675866E-2</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>7.7084884223846836E-2</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>6.7980577437007889E-2</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>7.3527640327474428E-2</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>0.11046727740290739</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>0.10975953251302951</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>0.11448067260382237</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>0.13378104794487711</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>0.12742963223873205</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>0.12174147080010039</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (CNY)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.35281439838707179</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.24082548096201026</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.204988768786621</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.83144262475919539</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.69163412561502646</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.1370158266198778</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.0759675522554586</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.034552790496422</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.1548781255438376</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.96052676740458742</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.78351154710245074</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3004153263524023E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (CNY)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>0.35281439838707179</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.24082548096201026</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.204988768786621</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.83144262475919539</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.69163412561502646</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.1370158266198778</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.0759675522554586</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.034552790496422</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.1548781255438376</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.96052676740458742</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.78351154710245074</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>3.3004153263524023E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>2.252810860262023E-2</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>0.11272111962456698</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>7.7777607554648784E-2</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>6.4699169842378529E-2</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>0.10636256563329072</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>0.10065178225027677</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>9.6777623058598883E-2</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>0.10803350098632719</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>8.9852831375546074E-2</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>7.3293877184513634E-2</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.2520574338240651E-2</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.13104147825886844</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.12851698895250163</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.13748607540754992</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.12272179315654419</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.11609889642245613</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.1090508644417824</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>9.7369227473224296E-2</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>8.5814881386908556E-2</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>7.791699620591358E-2</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15461,6 +15483,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15482,13 +15505,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15505,20 +15528,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15529,7 +15552,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15539,7 +15562,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15548,9 +15571,9 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15560,15 +15583,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15578,13 +15601,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15594,13 +15617,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15610,13 +15633,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15630,7 +15653,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15661,7 +15684,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15671,13 +15694,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15685,9 +15708,9 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15695,7 +15718,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15720,7 +15743,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -16492,7 +16515,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16529,7 +16552,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16750,7 +16773,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16979,19 +17002,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17116,7 +17139,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17242,18 +17265,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17265,31 +17288,31 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
-        <v>558008922.80000007</v>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
+        <v>502208030.5200001</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17299,7 +17322,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17308,29 +17331,29 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>9300148713.333334</v>
+        <v>8370133842.0000019</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>6.666666666666667</v>
+        <v>6.0000000000000018</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17343,7 +17366,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17353,13 +17376,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1">
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17367,9 +17390,9 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1">
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17377,13 +17400,13 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1">
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>6.8977230652121717</v>
+        <v>6.2079507586909539</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17399,16 +17422,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17418,7 +17441,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>570918033.4366858</v>
+        <v>513826230.09301728</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17430,7 +17453,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>538601918.336496</v>
+        <v>484741726.50284642</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17440,7 +17463,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>584125786.49757147</v>
+        <v>525713207.84781438</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17452,7 +17475,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>519869870.50335652</v>
+        <v>467882883.45302093</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17462,7 +17485,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>597639090.84726</v>
+        <v>537875181.76253402</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17474,7 +17497,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>501789304.969253</v>
+        <v>451610374.47232771</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17484,7 +17507,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>611465015.18166482</v>
+        <v>550318513.6634984</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17496,7 +17519,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>484337563.81713665</v>
+        <v>435903807.43542308</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17506,7 +17529,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>625610791.7255857</v>
+        <v>563049712.55302715</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17518,7 +17541,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>467492777.15014845</v>
+        <v>420743499.43513364</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18074,11 +18097,11 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>9515300557.2780972</v>
+        <v>8563770501.5502882</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18090,7 +18113,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>7110386108.7030039</v>
+        <v>6399347497.8327036</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18101,7 +18124,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>9622477543.4793949</v>
+        <v>8660229789.1314545</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18111,7 +18134,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18122,7 +18145,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>9622477543.4793949</v>
+        <v>8660229789.1314545</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18152,19 +18175,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>9300148713.3333321</v>
+        <v>8370133842</v>
       </c>
       <c r="C51" s="123">
-        <v>9300148713.3333321</v>
+        <v>8370133842</v>
       </c>
       <c r="D51" s="123">
-        <v>9578243886.814436</v>
+        <v>8620419498.1329937</v>
       </c>
       <c r="E51" s="123">
-        <v>9720006189.0763893</v>
+        <v>8748005570.1687508</v>
       </c>
       <c r="F51" s="123">
-        <v>10009160079.503984</v>
+        <v>9008244071.553587</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18173,19 +18196,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>9300148713.3333282</v>
+        <v>8370133841.9999981</v>
       </c>
       <c r="C52" s="123">
-        <v>9300148713.3333282</v>
+        <v>8370133841.9999981</v>
       </c>
       <c r="D52" s="123">
-        <v>9840692822.8459511</v>
+        <v>8856623540.5613594</v>
       </c>
       <c r="E52" s="123">
-        <v>10130174833.861521</v>
+        <v>9117157350.4753685</v>
       </c>
       <c r="F52" s="123">
-        <v>10751410226.890896</v>
+        <v>9676269204.2018089</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18194,19 +18217,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>9300148713.3333263</v>
+        <v>8370133841.9999962</v>
       </c>
       <c r="C53" s="123">
-        <v>9300148713.3333263</v>
+        <v>8370133841.9999962</v>
       </c>
       <c r="D53" s="123">
-        <v>10196563040.486353</v>
+        <v>9176906736.4377174</v>
       </c>
       <c r="E53" s="123">
-        <v>10700817633.628017</v>
+        <v>9630735870.2652149</v>
       </c>
       <c r="F53" s="123">
-        <v>11840061434.081987</v>
+        <v>10656055290.67379</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18215,19 +18238,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>9300148713.3333282</v>
+        <v>8370133841.9999962</v>
       </c>
       <c r="C54" s="123">
-        <v>9300148713.3333282</v>
+        <v>8370133841.9999962</v>
       </c>
       <c r="D54" s="123">
-        <v>10594291617.257338</v>
+        <v>9534862455.5316048</v>
       </c>
       <c r="E54" s="123">
-        <v>11356054346.993061</v>
+        <v>10220448912.293755</v>
       </c>
       <c r="F54" s="123">
-        <v>13162845840.027014</v>
+        <v>11846561256.024315</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18236,19 +18259,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>9300148713.3333282</v>
+        <v>8370133841.9999952</v>
       </c>
       <c r="C55" s="123">
-        <v>9300148713.3333282</v>
+        <v>8370133841.9999952</v>
       </c>
       <c r="D55" s="123">
-        <v>11000238309.225636</v>
+        <v>9900214478.3030701</v>
       </c>
       <c r="E55" s="123">
-        <v>12043906167.543388</v>
+        <v>10839515550.789051</v>
       </c>
       <c r="F55" s="123">
-        <v>14637014510.896175</v>
+        <v>13173313059.806562</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18257,19 +18280,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>9300148713.3333263</v>
+        <v>8370133841.9999924</v>
       </c>
       <c r="C56" s="123">
-        <v>9300148713.3333263</v>
+        <v>8370133841.9999924</v>
       </c>
       <c r="D56" s="123">
-        <v>11393300053.865107</v>
+        <v>10253970048.478592</v>
       </c>
       <c r="E56" s="123">
-        <v>12729623214.544498</v>
+        <v>11456660893.090048</v>
       </c>
       <c r="F56" s="123">
-        <v>16201823812.197025</v>
+        <v>14581641430.977324</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18282,7 +18305,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18319,23 +18342,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>6.666666666666667</v>
+        <v>6.0000000000000018</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>6.666666666666667</v>
+        <v>6.0000000000000018</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>6.666666666666667</v>
+        <v>6.0000000000000018</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>6.666666666666667</v>
+        <v>6.0000000000000018</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>6.666666666666667</v>
+        <v>6.0000000000000018</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18346,23 +18369,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.6666666666666661</v>
+        <v>6</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666661</v>
+        <v>6</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>6.8660148577928339</v>
+        <v>6.1794133720135518</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>6.9676349548698573</v>
+        <v>6.2708714593828718</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>7.174910414894164</v>
+        <v>6.4574193734047487</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18373,23 +18396,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666634</v>
+        <v>5.9999999999999982</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666634</v>
+        <v>5.9999999999999982</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>7.0541472874425875</v>
+        <v>6.3487325586983312</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>7.2616579555967782</v>
+        <v>6.5354921600370997</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>7.7069808654256136</v>
+        <v>6.9362827788830543</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18400,23 +18423,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666616</v>
+        <v>5.9999999999999973</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666616</v>
+        <v>5.9999999999999973</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>7.3092473068865074</v>
+        <v>6.5783225761978565</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>7.6707143534071225</v>
+        <v>6.9036429180664101</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>8.4873635171785011</v>
+        <v>7.6386271654606528</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18427,23 +18450,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666634</v>
+        <v>5.9999999999999973</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666634</v>
+        <v>5.9999999999999973</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>7.5943528387301535</v>
+        <v>6.8349175548571388</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>8.1404105798238398</v>
+        <v>7.326369521841456</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>9.4355809036012879</v>
+        <v>8.4920228132411619</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18454,23 +18477,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666634</v>
+        <v>5.9999999999999964</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666634</v>
+        <v>5.9999999999999964</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>7.8853493983774952</v>
+        <v>7.0968144585397441</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>8.6334864375350726</v>
+        <v>7.7701377937815668</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>10.492315741081677</v>
+        <v>9.443084166973513</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18480,40 +18503,40 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666616</v>
+        <v>5.9999999999999947</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666616</v>
+        <v>5.9999999999999947</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>8.1671095843380712</v>
+        <v>7.3503986259042611</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>9.1250320160970002</v>
+        <v>8.2125288144872997</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>11.614024901895009</v>
+        <v>10.452622411705509</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18531,7 +18554,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>7.7069808654256136</v>
+        <v>6.9362827788830543</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18553,7 +18576,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.9676349548698573</v>
+        <v>6.2708714593828718</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18576,7 +18599,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>6.8660148577928339</v>
+        <v>6.1794133720135518</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18599,7 +18622,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>6.6666666666666661</v>
+        <v>6</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18622,7 +18645,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>6.6666666666666634</v>
+        <v>5.9999999999999982</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18638,7 +18661,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18690,32 +18713,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="6" width="42.6640625" customWidth="1"/>
-    <col min="8" max="9" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="6" width="42.73046875" customWidth="1"/>
+    <col min="8" max="9" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18727,14 +18750,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18742,7 +18765,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.4</v>
+        <v>0.36000000000000004</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18751,7 +18774,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.36000000000000004</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18763,7 +18786,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18771,12 +18794,12 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.315286704532291</v>
+        <v>13.27528670453229</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18786,11 +18809,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中文传媒(600373.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18811,8 +18834,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18833,8 +18856,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18844,8 +18867,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18856,10 +18879,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>447</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>444</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18870,15 +18893,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-4.5961886297537391E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18889,14 +18912,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.135599908831609</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18913,12 +18936,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.29648179377498129</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18927,38 +18950,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18968,12 +18991,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18983,44 +19006,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19030,55 +19053,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19088,55 +19111,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19146,24 +19169,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19176,7 +19199,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19185,12 +19208,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19205,39 +19228,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19247,55 +19270,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.05</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19305,23 +19328,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19332,7 +19355,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19341,7 +19364,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19350,15 +19373,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19366,19 +19389,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
         <v>2.3134236943577701E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19394,20 +19417,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19417,19 +19440,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19439,14 +19462,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19455,7 +19478,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19464,12 +19487,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19479,11 +19502,11 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
-        <v>0.4</v>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19492,25 +19515,25 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322296</v>
+        <v>0.62127925482890056</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19518,7 +19541,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19532,18 +19555,18 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>6.0942417132402751</v>
+        <v>6.0252106849259528</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.52813732651388556</v>
+        <v>0.53348223521731353</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19551,12 +19574,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19569,11 +19592,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10029030917921822</v>
+        <v>9.6763347097292396E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19581,12 +19604,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19595,11 +19618,11 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.86005014536183588</v>
+        <v>0.77404513082565229</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19607,7 +19630,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19621,30 +19644,30 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>8.582443057830476</v>
+        <v>8.4964380432942921</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.33548180120394178</v>
+        <v>0.34214096537921346</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19655,11 +19678,11 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.069204779784656</v>
+        <v>0.9622843018061904</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19667,7 +19690,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19679,21 +19702,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.913128542800674</v>
+        <v>11.80620806482221</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.7594728220778397E-2</v>
+        <v>8.5873327095470353E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19701,12 +19724,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19715,17 +19738,17 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>1.0179560233797402</v>
+        <v>0.91616042104176609</v>
       </c>
       <c r="D103" s="116"/>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19735,21 +19758,21 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>11.073728055846336</v>
+        <v>10.971932453508362</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.14359457232654926</v>
+        <v>0.15146710684391118</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19757,32 +19780,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
+        <v>322</v>
+      </c>
+      <c r="F110" s="284" t="s">
         <v>325</v>
-      </c>
-      <c r="F110" s="284" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29CD00C-C4FC-4EA8-A6B9-954CE59F33A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF37E352-D6CC-493F-A6E7-8ED323970914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.69</v>
+        <v>10.79</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14912.78846183</v>
+        <v>15052.290692529999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.6763347097292396E-2</v>
+        <v>9.3260656320312663E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.3004153263524023E-2</v>
+        <v>3.269827603216606E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.3676333021515438E-2</v>
+        <v>3.3364226135310482E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.62127925482890056</v>
+        <v>0.62127925482890078</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3676333021515438E-2</v>
+        <v>3.3364226135310482E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3676333021515438E-2</v>
+        <v>3.3364226135310482E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5668849391955109E-2</v>
+        <v>6.5060240963855431E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.3143124415341451E-2</v>
+        <v>6.2557924003707147E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>5.7249766136576244E-2</v>
+        <v>5.6719184430027804E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3004153263524023E-2</v>
+        <v>3.269827603216606E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.252810860262023E-2</v>
+        <v>2.2319321683226159E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11272111962456698</v>
+        <v>0.11167643825640602</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>7.7777607554648784E-2</v>
+        <v>7.7056777086116357E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.4699169842378529E-2</v>
+        <v>6.4099548249770766E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.10636256563329072</v>
+        <v>0.10537681432992381</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10065178225027677</v>
+        <v>9.9718957576965583E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>9.6777623058598883E-2</v>
+        <v>9.5880703475108631E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.10803350098632719</v>
+        <v>0.10703226372046688</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.9852831375546074E-2</v>
+        <v>8.9020089657515067E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.3293877184513634E-2</v>
+        <v>7.2614601214314248E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2520574338240651E-2</v>
+        <v>5.2033822027413593E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13104147825886844</v>
+        <v>0.1298270067272756</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12851698895250163</v>
+        <v>0.12732591398537929</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13748607540754992</v>
+        <v>0.13621187637689611</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12272179315654419</v>
+        <v>0.12158442714026482</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11609889642245613</v>
+        <v>0.11502291035737314</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1090508644417824</v>
+        <v>0.10804019841359165</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7369227473224296E-2</v>
+        <v>9.6466824994325101E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5814881386908556E-2</v>
+        <v>8.5019562745695332E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.791699620591358E-2</v>
+        <v>7.7194873905580746E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.69</v>
+        <v>-10.79</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.69</v>
+        <v>10.79</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.62127925482890056</v>
+        <v>0.62127925482890078</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.69</v>
+        <v>10.79</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.6763347097292396E-2</v>
+        <v>9.3260656320312663E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF37E352-D6CC-493F-A6E7-8ED323970914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C220B08-6C8E-4E29-8E16-C65801EFA5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.79</v>
+        <v>10.27</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>15052.290692529999</v>
+        <v>14326.87909289</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>9.3260656320312663E-2</v>
+        <v>0.11197653523274731</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.269827603216606E-2</v>
+        <v>3.4353884945187131E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.3364226135310482E-2</v>
+        <v>3.5053554040895815E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3364226135310482E-2</v>
+        <v>3.5053554040895815E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3364226135310482E-2</v>
+        <v>3.5053554040895815E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5060240963855431E-2</v>
+        <v>6.8354430379746839E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.2557924003707147E-2</v>
+        <v>6.5725413826679652E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>5.6719184430027804E-2</v>
+        <v>5.9591041869522882E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.269827603216606E-2</v>
+        <v>3.4353884945187131E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.2319321683226159E-2</v>
+        <v>2.3449413920351537E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11167643825640602</v>
+        <v>0.11733094145926203</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>7.7056777086116357E-2</v>
+        <v>8.0958386052501982E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.4099548249770766E-2</v>
+        <v>6.7345094996594593E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.10537681432992381</v>
+        <v>0.11071234923270476</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>9.9718957576965583E-2</v>
+        <v>0.10476801872010308</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>9.5880703475108631E-2</v>
+        <v>0.10073542263840526</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.10703226372046688</v>
+        <v>0.11245161884555381</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>8.9020089657515067E-2</v>
+        <v>9.3527435969287975E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.2614601214314248E-2</v>
+        <v>7.6291289883393454E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2033822027413593E-2</v>
+        <v>5.4668445927535794E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1298270067272756</v>
+        <v>0.13640052605523892</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12732591398537929</v>
+        <v>0.13377279570615799</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13621187637689611</v>
+        <v>0.14310868024408072</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12158442714026482</v>
+        <v>0.12774060066635418</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11502291035737314</v>
+        <v>0.12084685518559456</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10804019841359165</v>
+        <v>0.1135105882066849</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6466824994325101E-2</v>
+        <v>0.1013512211965694</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5019562745695332E-2</v>
+        <v>8.9324350732819136E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7194873905580746E-2</v>
+        <v>8.1103475115989893E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.79</v>
+        <v>-10.27</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.79</v>
+        <v>10.27</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.79</v>
+        <v>10.27</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.3260656320312663E-2</v>
+        <v>0.11197653523274731</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C220B08-6C8E-4E29-8E16-C65801EFA5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE384DE4-F2A9-4FE8-9CB9-E90232F9952D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.27</v>
+        <v>10.28</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14326.87909289</v>
+        <v>14340.82931596</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11197653523274731</v>
+        <v>0.11160452661716125</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4353884945187131E-2</v>
+        <v>3.4320466769170409E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5053554040895815E-2</v>
+        <v>3.5019455252918295E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5053554040895815E-2</v>
+        <v>3.5019455252918295E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5053554040895815E-2</v>
+        <v>3.5019455252918295E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8354430379746839E-2</v>
+        <v>6.8287937743190669E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5725413826679652E-2</v>
+        <v>6.5661478599221793E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>5.9591041869522882E-2</v>
+        <v>5.9533073929961093E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4353884945187131E-2</v>
+        <v>3.4320466769170409E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3449413920351537E-2</v>
+        <v>2.3426603206421232E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11733094145926203</v>
+        <v>0.11721680630220049</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.0958386052501982E-2</v>
+        <v>8.0879632758676601E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.7345094996594593E-2</v>
+        <v>6.7279584203796358E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11071234923270476</v>
+        <v>0.11060465239492975</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10476801872010308</v>
+        <v>0.10466610430500571</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10073542263840526</v>
+        <v>0.10063743098214223</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11245161884555381</v>
+        <v>0.11234223011126826</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.3527435969287975E-2</v>
+        <v>9.3436455973208904E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.6291289883393454E-2</v>
+        <v>7.6217076566386266E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4668445927535794E-2</v>
+        <v>5.46152665054273E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13640052605523892</v>
+        <v>0.13626784071860931</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13377279570615799</v>
+        <v>0.13364266652745552</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14310868024408072</v>
+        <v>0.14296946946563316</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12774060066635418</v>
+        <v>0.12761633938165928</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12084685518559456</v>
+        <v>0.12072929987899378</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1135105882066849</v>
+        <v>0.11340016934656166</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1013512211965694</v>
+        <v>0.10125263051447159</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9324350732819136E-2</v>
+        <v>8.9237459341055703E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1103475115989893E-2</v>
+        <v>8.1024580684943212E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.27</v>
+        <v>-10.28</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.27</v>
+        <v>10.28</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.27</v>
+        <v>10.28</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11197653523274731</v>
+        <v>0.11160452661716125</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE384DE4-F2A9-4FE8-9CB9-E90232F9952D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9E14C7-DF52-4354-98BB-610AF945D168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.28</v>
+        <v>10.08</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14340.82931596</v>
+        <v>14061.82485456</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11160452661716125</v>
+        <v>0.11913975515550601</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4320466769170409E-2</v>
+        <v>3.5001428411415854E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5019455252918295E-2</v>
+        <v>3.5714285714285719E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5019455252918295E-2</v>
+        <v>3.5714285714285719E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5019455252918295E-2</v>
+        <v>3.5714285714285719E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8287937743190669E-2</v>
+        <v>6.9642857142857145E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5661478599221793E-2</v>
+        <v>6.6964285714285712E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>5.9533073929961093E-2</v>
+        <v>6.0714285714285714E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4320466769170409E-2</v>
+        <v>3.5001428411415854E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3426603206421232E-2</v>
+        <v>2.3891416762104191E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11721680630220049</v>
+        <v>0.1195425365859743</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.0879632758676601E-2</v>
+        <v>8.2484387376904306E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.7279584203796358E-2</v>
+        <v>6.8614496588792304E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11060465239492975</v>
+        <v>0.1127991891487974</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10466610430500571</v>
+        <v>0.10674281272375581</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10063743098214223</v>
+        <v>0.10263420540639107</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11234223011126826</v>
+        <v>0.11457124261347595</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.3436455973208904E-2</v>
+        <v>9.5290353909185263E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.6217076566386266E-2</v>
+        <v>7.772932014905265E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.46152665054273E-2</v>
+        <v>5.5698902745614343E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13626784071860931</v>
+        <v>0.1389715677169944</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13364266652745552</v>
+        <v>0.13629430673633358</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14296946946563316</v>
+        <v>0.14580616528836399</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12761633938165928</v>
+        <v>0.13014840960748586</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12072929987899378</v>
+        <v>0.12312472249564048</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11340016934656166</v>
+        <v>0.11565017270661249</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10125263051447159</v>
+        <v>0.10326161127864759</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9237459341055703E-2</v>
+        <v>9.1008043851790926E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1024580684943212E-2</v>
+        <v>8.2632211254088914E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.28</v>
+        <v>-10.08</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.28</v>
+        <v>10.08</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.28</v>
+        <v>10.08</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11160452661716125</v>
+        <v>0.11913975515550601</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9E14C7-DF52-4354-98BB-610AF945D168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A48DF4-4A84-49B4-AF40-E489C1391C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.08</v>
+        <v>10.11</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14061.82485456</v>
+        <v>14103.675523769998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11913975515550601</v>
+        <v>0.11799655385557783</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.5001428411415854E-2</v>
+        <v>3.4897566606040736E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5714285714285719E-2</v>
+        <v>3.5608308605341255E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5714285714285719E-2</v>
+        <v>3.5608308605341255E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5714285714285719E-2</v>
+        <v>3.5608308605341255E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.9642857142857145E-2</v>
+        <v>6.9436201780415444E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.6964285714285712E-2</v>
+        <v>6.6765578635014838E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0714285714285714E-2</v>
+        <v>6.0534124629080123E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.5001428411415854E-2</v>
+        <v>3.4897566606040736E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3891416762104191E-2</v>
+        <v>2.3820522350347206E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.1195425365859743</v>
+        <v>0.11918781095812275</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.2484387376904306E-2</v>
+        <v>8.2239626583501035E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.8614496588792304E-2</v>
+        <v>6.8410892741347817E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.1127991891487974</v>
+        <v>0.11246447345399385</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10674281272375581</v>
+        <v>0.10642606847235002</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10263420540639107</v>
+        <v>0.10232965286809319</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11457124261347595</v>
+        <v>0.11423126859978612</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.5290353909185263E-2</v>
+        <v>9.5007593215092723E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.772932014905265E-2</v>
+        <v>7.7498669347423416E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5698902745614343E-2</v>
+        <v>5.5533624102452286E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1389715677169944</v>
+        <v>0.13855918917777485</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13629430673633358</v>
+        <v>0.13588987259171539</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14580616528836399</v>
+        <v>0.14537350604418486</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13014840960748586</v>
+        <v>0.12976221254633605</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12312472249564048</v>
+        <v>0.12275936723600951</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11565017270661249</v>
+        <v>0.11530699711994599</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10326161127864759</v>
+        <v>0.10295519700185637</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1008043851790926E-2</v>
+        <v>9.0737990309204014E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2632211254088914E-2</v>
+        <v>8.23870118141658E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.08</v>
+        <v>-10.11</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.08</v>
+        <v>10.11</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.08</v>
+        <v>10.11</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11913975515550601</v>
+        <v>0.11799655385557783</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A48DF4-4A84-49B4-AF40-E489C1391C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB5F65D-697E-410A-B1A9-BA4017F4AF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.11</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14103.675523769998</v>
+        <v>14229.2275314</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11799655385557783</v>
+        <v>0.1145944734774933</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4897566606040736E-2</v>
+        <v>3.4589646900693313E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5608308605341255E-2</v>
+        <v>3.529411764705883E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5608308605341255E-2</v>
+        <v>3.529411764705883E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5608308605341255E-2</v>
+        <v>3.529411764705883E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.9436201780415444E-2</v>
+        <v>6.8823529411764714E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.6765578635014838E-2</v>
+        <v>6.6176470588235309E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0534124629080123E-2</v>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4897566606040736E-2</v>
+        <v>3.4589646900693313E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3820522350347206E-2</v>
+        <v>2.3610341270785321E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11918781095812275</v>
+        <v>0.1181361538026099</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.2239626583501035E-2</v>
+        <v>8.1513982819528971E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.8410892741347817E-2</v>
+        <v>6.7807267217159461E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11246447345399385</v>
+        <v>0.11147213986469391</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10642606847235002</v>
+        <v>0.10548701492700575</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10232965286809319</v>
+        <v>0.10142674416631589</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11423126859978612</v>
+        <v>0.11322334564155272</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.5007593215092723E-2</v>
+        <v>9.4169290922018381E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.7498669347423416E-2</v>
+        <v>7.6814857559063809E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5533624102452286E-2</v>
+        <v>5.5043621536842412E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13855918917777485</v>
+        <v>0.13733660809679446</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13588987259171539</v>
+        <v>0.13469084430414144</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14537350604418486</v>
+        <v>0.14409079863791263</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12976221254633605</v>
+        <v>0.12861725184739778</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12275936723600951</v>
+        <v>0.12167619634863294</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11530699711994599</v>
+        <v>0.11428958243947587</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10295519700185637</v>
+        <v>0.10204676879301645</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0737990309204014E-2</v>
+        <v>8.9937360982946329E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.23870118141658E-2</v>
+        <v>8.1660067592276106E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.11</v>
+        <v>-10.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.11</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.11</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11799655385557783</v>
+        <v>0.1145944734774933</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB5F65D-697E-410A-B1A9-BA4017F4AF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D760B06-9D71-4BAA-BA25-6C42D13BC21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.199999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14229.2275314</v>
+        <v>14312.92886982</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1145944734774933</v>
+        <v>0.11234903719576717</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4589646900693313E-2</v>
+        <v>3.4387368263847154E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.529411764705883E-2</v>
+        <v>3.5087719298245619E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.529411764705883E-2</v>
+        <v>3.5087719298245619E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.529411764705883E-2</v>
+        <v>3.5087719298245619E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8823529411764714E-2</v>
+        <v>6.8421052631578952E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.6176470588235309E-2</v>
+        <v>6.5789473684210537E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0000000000000005E-2</v>
+        <v>5.9649122807017542E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4589646900693313E-2</v>
+        <v>3.4387368263847154E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3610341270785321E-2</v>
+        <v>2.3472269099611136E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.1181361538026099</v>
+        <v>0.11744529910200985</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.1513982819528971E-2</v>
+        <v>8.1037292861520019E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.7807267217159461E-2</v>
+        <v>6.7410733490743321E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11147213986469391</v>
+        <v>0.11082025600583605</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10548701492700575</v>
+        <v>0.10487013179877765</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10142674416631589</v>
+        <v>0.1008336053115421</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11322334564155272</v>
+        <v>0.11256122081323953</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.4169290922018381E-2</v>
+        <v>9.3618593314287277E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.6814857559063809E-2</v>
+        <v>7.6365647865735936E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5043621536842412E-2</v>
+        <v>5.4721729013235146E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13733660809679446</v>
+        <v>0.13653347003774888</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13469084430414144</v>
+        <v>0.13390317854797684</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14409079863791263</v>
+        <v>0.14324816238856811</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12861725184739778</v>
+        <v>0.12786510417577557</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12167619634863294</v>
+        <v>0.12096463964483976</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11428958243947587</v>
+        <v>0.11362122230825086</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10204676879301645</v>
+        <v>0.10145000406323273</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9937360982946329E-2</v>
+        <v>8.9411411503513893E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1660067592276106E-2</v>
+        <v>8.1182523337350515E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.199999999999999</v>
+        <v>-10.26</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.199999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.199999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1145944734774933</v>
+        <v>0.11234903719576717</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D760B06-9D71-4BAA-BA25-6C42D13BC21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CA16BA-9445-4DAB-AD29-2380CA7C4840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.26</v>
+        <v>10.17</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14312.92886982</v>
+        <v>14187.37686219</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11234903719576717</v>
+        <v>0.11572394515178419</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4387368263847154E-2</v>
+        <v>3.4691681257332525E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5087719298245619E-2</v>
+        <v>3.5398230088495582E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5087719298245619E-2</v>
+        <v>3.5398230088495582E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5087719298245619E-2</v>
+        <v>3.5398230088495582E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8421052631578952E-2</v>
+        <v>6.9026548672566385E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5789473684210537E-2</v>
+        <v>6.637168141592921E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>5.9649122807017542E-2</v>
+        <v>6.0176991150442477E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4387368263847154E-2</v>
+        <v>3.4691681257332525E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3472269099611136E-2</v>
+        <v>2.3679988295182915E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11744529910200985</v>
+        <v>0.11848463803211612</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.1037292861520019E-2</v>
+        <v>8.1754437046135248E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.7410733490743321E-2</v>
+        <v>6.8007288654378217E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11082025600583605</v>
+        <v>0.11180096623597618</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10487013179877765</v>
+        <v>0.10579818606248363</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.1008336053115421</v>
+        <v>0.10172593810190973</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11256122081323953</v>
+        <v>0.11355733781158679</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.3618593314287277E-2</v>
+        <v>9.4447076440962383E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.6365647865735936E-2</v>
+        <v>7.7041450059238029E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4721729013235146E-2</v>
+        <v>5.5205992101847845E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13653347003774888</v>
+        <v>0.13774173083454311</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13390317854797684</v>
+        <v>0.1350881624289324</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14324816238856811</v>
+        <v>0.14451584524156427</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12786510417577557</v>
+        <v>0.12899665377025146</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12096463964483976</v>
+        <v>0.12203512318151975</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11362122230825086</v>
+        <v>0.11462671985080175</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10145000406323273</v>
+        <v>0.10234779170981001</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9411411503513893E-2</v>
+        <v>9.020266293274852E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1182523337350515E-2</v>
+        <v>8.1900952747415559E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.26</v>
+        <v>-10.17</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.26</v>
+        <v>10.17</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.26</v>
+        <v>10.17</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11234903719576717</v>
+        <v>0.11572394515178419</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CA16BA-9445-4DAB-AD29-2380CA7C4840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BE73D9-684D-4497-BD06-1B44A4F03015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14187.37686219</v>
+        <v>14201.32708526</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11572394515178419</v>
+        <v>0.11534695122345151</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4691681257332525E-2</v>
+        <v>3.4657602984977581E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5398230088495582E-2</v>
+        <v>3.5363457760314347E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5398230088495582E-2</v>
+        <v>3.5363457760314347E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5398230088495582E-2</v>
+        <v>3.5363457760314347E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.9026548672566385E-2</v>
+        <v>6.8958742632612979E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.637168141592921E-2</v>
+        <v>6.63064833005894E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0176991150442477E-2</v>
+        <v>6.0117878192534384E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4691681257332525E-2</v>
+        <v>3.4657602984977581E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3679988295182915E-2</v>
+        <v>2.3656727010020653E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11848463803211612</v>
+        <v>0.11836824840733016</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.1754437046135248E-2</v>
+        <v>8.1674128168879701E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.8007288654378217E-2</v>
+        <v>6.7940483852163697E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11180096623597618</v>
+        <v>0.11169114210411374</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10579818606248363</v>
+        <v>0.10569425857126312</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10172593810190973</v>
+        <v>0.10162601085426543</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11355733781158679</v>
+        <v>0.11344578836383475</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.4447076440962383E-2</v>
+        <v>9.4354299352120571E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.7041450059238029E-2</v>
+        <v>7.6965770835211278E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5205992101847845E-2</v>
+        <v>5.5151762247130899E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13774173083454311</v>
+        <v>0.13760642461564868</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1350881624289324</v>
+        <v>0.13495546285876645</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14451584524156427</v>
+        <v>0.14437388468631718</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12899665377025146</v>
+        <v>0.12886993800033961</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12203512318151975</v>
+        <v>0.1219152458503002</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11462671985080175</v>
+        <v>0.11451411992953378</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10234779170981001</v>
+        <v>0.10224725360400469</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.020266293274852E-2</v>
+        <v>9.0114055208846022E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1900952747415559E-2</v>
+        <v>8.1820499945109648E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.17</v>
+        <v>-10.18</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11572394515178419</v>
+        <v>0.11534695122345151</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BE73D9-684D-4497-BD06-1B44A4F03015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0D97CD-A737-4C74-909B-E2BD3D0A5DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14201.32708526</v>
+        <v>14089.725300699998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11534695122345151</v>
+        <v>0.11837710727015116</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>6.0252106849259528</v>
+        <v>5.8598330354243915</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>8.4964380432942921</v>
+        <v>7.3153467927205327</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4544,7 +4544,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4657602984977581E-2</v>
+        <v>3.4932118652185332E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5363457760314347E-2</v>
+        <v>3.5643564356435647E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.62127925482890078</v>
+        <v>0.61051668952903537</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.4039314300970522</v>
+        <v>5.2493163458953562</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>6.0252106849259528</v>
+        <v>5.8598330354243915</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53348223521731353</v>
+        <v>0.54628703415712532</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.77404513082565229</v>
+        <v>0.70272000000000001</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>7.7223929124686403</v>
+        <v>6.6126267927205324</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>8.4964380432942921</v>
+        <v>7.3153467927205327</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34214096537921346</v>
+        <v>0.43359005803925377</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5363457760314347E-2</v>
+        <v>3.5643564356435647E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5363457760314347E-2</v>
+        <v>3.5643564356435647E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8958742632612979E-2</v>
+        <v>6.9504950495049511E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.63064833005894E-2</v>
+        <v>6.6831683168316836E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0117878192534384E-2</v>
+        <v>6.0594059405940592E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4657602984977581E-2</v>
+        <v>3.4932118652185332E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3656727010020653E-2</v>
+        <v>2.384410702594161E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11836824840733016</v>
+        <v>0.11930581869174466</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.1674128168879701E-2</v>
+        <v>8.2321051956355987E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.7940483852163697E-2</v>
+        <v>6.8478626298517475E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11169114210411374</v>
+        <v>0.11257582441780968</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10569425857126312</v>
+        <v>0.10653144081737215</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10162601085426543</v>
+        <v>0.1024309693560814</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11344578836383475</v>
+        <v>0.11434436886572651</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.4354299352120571E-2</v>
+        <v>9.5101660139068067E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.6965770835211278E-2</v>
+        <v>7.7575400703212949E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5151762247130899E-2</v>
+        <v>5.558860788869234E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13760642461564868</v>
+        <v>0.13869637649379243</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13495546285876645</v>
+        <v>0.13602441702002402</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14437388468631718</v>
+        <v>0.14551744020858504</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12886993800033961</v>
+        <v>0.12989068998450073</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1219152458503002</v>
+        <v>0.12288091116396595</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11451411992953378</v>
+        <v>0.1154211624636291</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10224725360400469</v>
+        <v>0.10305713284047206</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0114055208846022E-2</v>
+        <v>9.0827829903569565E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1820499945109648E-2</v>
+        <v>8.2468583112991711E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.18</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.62127925482890078</v>
+        <v>0.61051668952903537</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19545,7 +19545,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.4039314300970522</v>
+        <v>5.2493163458953562</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>6.0252106849259528</v>
+        <v>5.8598330354243915</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53348223521731353</v>
+        <v>0.54628703415712532</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11534695122345151</v>
+        <v>0.11837710727015116</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.77404513082565229</v>
+        <v>0.70272000000000001</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>7.7223929124686403</v>
+        <v>6.6126267927205324</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>8.4964380432942921</v>
+        <v>7.3153467927205327</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.34214096537921346</v>
+        <v>0.43359005803925377</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0D97CD-A737-4C74-909B-E2BD3D0A5DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C81840A-1DDA-45DC-AD70-4313846CE1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.1</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14089.725300699998</v>
+        <v>14131.575969910002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11837710727015116</v>
+        <v>0.11723698206181421</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4932118652185332E-2</v>
+        <v>3.4828667165554959E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5643564356435647E-2</v>
+        <v>3.5538005923000986E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5643564356435647E-2</v>
+        <v>3.5538005923000986E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5643564356435647E-2</v>
+        <v>3.5538005923000986E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.9504950495049511E-2</v>
+        <v>6.9299111549851924E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.6831683168316836E-2</v>
+        <v>6.6633761105626854E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0594059405940592E-2</v>
+        <v>6.0414610069101669E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4932118652185332E-2</v>
+        <v>3.4828667165554959E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.384410702594161E-2</v>
+        <v>2.3773492691215228E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11930581869174466</v>
+        <v>0.11895249445080167</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.2321051956355987E-2</v>
+        <v>8.2077258120354921E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.8478626298517475E-2</v>
+        <v>6.8275826812934495E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11257582441780968</v>
+        <v>0.11224243105823077</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10653144081737215</v>
+        <v>0.10621594790280933</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.1024309693560814</v>
+        <v>0.10212761998977511</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11434436886572651</v>
+        <v>0.11400573796089215</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.5101660139068067E-2</v>
+        <v>9.4820016525625606E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.7575400703212949E-2</v>
+        <v>7.7345661115740441E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.558860788869234E-2</v>
+        <v>5.5423982198992354E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13869637649379243</v>
+        <v>0.13828562710634781</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13602441702002402</v>
+        <v>0.13562158064187979</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14551744020858504</v>
+        <v>0.1450864902375823</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12989068998450073</v>
+        <v>0.12950601864199973</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12288091116396595</v>
+        <v>0.12251699928490185</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1154211624636291</v>
+        <v>0.11507934263402307</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10305713284047206</v>
+        <v>0.10275192909069769</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0827829903569565E-2</v>
+        <v>9.0558843240479012E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2468583112991711E-2</v>
+        <v>8.2224352363397452E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.1</v>
+        <v>-10.130000000000001</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.1</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.1</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11837710727015116</v>
+        <v>0.11723698206181421</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C81840A-1DDA-45DC-AD70-4313846CE1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5880DB45-E685-4660-B1F2-941CAC98972B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.130000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14131.575969910002</v>
+        <v>14201.32708526</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11723698206181421</v>
+        <v>0.11534695122345151</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4828667165554959E-2</v>
+        <v>3.4657602984977581E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5538005923000986E-2</v>
+        <v>3.5363457760314347E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,24 +13503,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5538005923000986E-2</v>
+        <v>3.5363457760314347E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5538005923000986E-2</v>
+        <v>3.5363457760314347E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.9299111549851924E-2</v>
+        <v>6.8958742632612979E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.6633761105626854E-2</v>
+        <v>6.63064833005894E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0414610069101669E-2</v>
+        <v>6.0117878192534384E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4828667165554959E-2</v>
+        <v>3.4657602984977581E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3773492691215228E-2</v>
+        <v>2.3656727010020653E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11895249445080167</v>
+        <v>0.11836824840733016</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.2077258120354921E-2</v>
+        <v>8.1674128168879701E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.8275826812934495E-2</v>
+        <v>6.7940483852163697E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11224243105823077</v>
+        <v>0.11169114210411374</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10621594790280933</v>
+        <v>0.10569425857126312</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10212761998977511</v>
+        <v>0.10162601085426543</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11400573796089215</v>
+        <v>0.11344578836383475</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.4820016525625606E-2</v>
+        <v>9.4354299352120571E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.7345661115740441E-2</v>
+        <v>7.6965770835211278E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5423982198992354E-2</v>
+        <v>5.5151762247130899E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13828562710634781</v>
+        <v>0.13760642461564868</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13562158064187979</v>
+        <v>0.13495546285876645</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1450864902375823</v>
+        <v>0.14437388468631718</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12950601864199973</v>
+        <v>0.12886993800033961</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12251699928490185</v>
+        <v>0.1219152458503002</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11507934263402307</v>
+        <v>0.11451411992953378</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10275192909069769</v>
+        <v>0.10224725360400469</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0558843240479012E-2</v>
+        <v>9.0114055208846022E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2224352363397452E-2</v>
+        <v>8.1820499945109648E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.130000000000001</v>
+        <v>-10.18</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.130000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.130000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11723698206181421</v>
+        <v>0.11534695122345151</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5880DB45-E685-4660-B1F2-941CAC98972B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AE9FAF-480A-453C-BF2B-0E95A0FCB244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>CN</t>
@@ -4240,13 +4244,13 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4277,7 +4281,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4324,10 +4328,10 @@
         <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4421,7 +4425,7 @@
         <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4429,7 +4433,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4442,7 +4446,7 @@
         <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4450,7 +4454,7 @@
         <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -6627,7 +6631,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12799,7 +12803,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19822,4 +19826,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AE9FAF-480A-453C-BF2B-0E95A0FCB244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D481DD29-C042-4DBF-8AA7-70F1AE143DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2504,7 +2517,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2944,6 +2957,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3147,11 +3166,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3936,9 +3956,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{5DD48AC0-D3C5-4C4A-B79D-DA76CD234918}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4023,6 +4049,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>1395022307</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>10.18</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19829,22 +19938,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1528048E-47DF-4689-9764-0B999420DF44}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D481DD29-C042-4DBF-8AA7-70F1AE143DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40A2FE1-7338-45F4-95FE-652FDF114BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3920,47 +3920,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4449,7 +4449,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>10.18</v>
+        <v>10.28</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14201.32708526</v>
+        <v>14340.82931596</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4507,13 +4507,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4589,14 +4589,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>12.91528670453229</v>
+        <v>11.711712236864567</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11534695122345151</v>
+        <v>7.8003271289299514E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>5.8598330354243915</v>
+        <v>4.3792241541234382</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4638,7 +4638,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>7.3153467927205327</v>
+        <v>5.9845754378081768</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4657,7 +4657,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>11.80620806482221</v>
+        <v>10.363655818472994</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4676,7 +4676,7 @@
         <v>433</v>
       </c>
       <c r="F31" s="312">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>10.971932453508362</v>
+        <v>10.034835914511921</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4713,13 +4713,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4740,13 +4740,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4766,13 +4766,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4801,13 +4801,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4823,13 +4823,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4893,13 +4893,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4915,13 +4915,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4937,22 +4937,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4657602984977581E-2</v>
+        <v>3.4320466769170409E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5363457760314347E-2</v>
+        <v>3.5019455252918295E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -5087,13 +5087,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5146,22 +5146,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.8802399731178632</v>
+        <v>4.7041919784942907</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5198,13 +5198,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5217,13 +5217,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5345,13 +5345,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5390,13 +5390,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>13.64 CNY</v>
+        <v>12.35 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>12.99 CNY</v>
+        <v>11.78 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>12.9 CNY</v>
+        <v>11.7 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>12.73 CNY</v>
+        <v>11.55 CNY</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>12.73 CNY</v>
+        <v>11.55 CNY</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>12.91528670453229</v>
+        <v>11.711712236864567</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5539,13 +5539,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5558,22 +5558,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.61051668952903537</v>
+        <v>0.53758661691746279</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>5.2493163458953562</v>
+        <v>3.8416375372059757</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>5.8598330354243915</v>
+        <v>4.3792241541234382</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54628703415712532</v>
+        <v>0.62608164668364208</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.70272000000000001</v>
+        <v>0.65380063723259008</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.6126267927205324</v>
+        <v>5.3307748005755871</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>7.3153467927205327</v>
+        <v>5.9845754378081768</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.43359005803925377</v>
+        <v>0.48900935091534037</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.9622843018061904</v>
+        <v>0.93618926635390565</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>10.843923763016019</v>
+        <v>9.427466552119089</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>11.80620806482221</v>
+        <v>10.363655818472994</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>8.5873327095470353E-2</v>
+        <v>0.11510327363989881</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>10.055772032466596</v>
+        <v>9.118675493470155</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>10.971932453508362</v>
+        <v>10.034835914511921</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15146710684391118</v>
+        <v>0.14404564603873704</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5906,13 +5906,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5920,13 +5920,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5949,13 +5949,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5963,22 +5963,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6002,6 +6002,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6018,17 +6029,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13616,24 +13616,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5363457760314347E-2</v>
+        <v>3.5019455252918295E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5363457760314347E-2</v>
+        <v>3.5019455252918295E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8958742632612979E-2</v>
+        <v>6.8287937743190669E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.63064833005894E-2</v>
+        <v>6.5661478599221793E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0117878192534384E-2</v>
+        <v>5.9533073929961093E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -14815,50 +14815,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4657602984977581E-2</v>
+        <v>3.4320466769170409E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3656727010020653E-2</v>
+        <v>2.3426603206421232E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11836824840733016</v>
+        <v>0.11721680630220049</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.1674128168879701E-2</v>
+        <v>8.0879632758676601E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.7940483852163697E-2</v>
+        <v>6.7279584203796358E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11169114210411374</v>
+        <v>0.11060465239492975</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10569425857126312</v>
+        <v>0.10466610430500571</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10162601085426543</v>
+        <v>0.10063743098214223</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11344578836383475</v>
+        <v>0.11234223011126826</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.4354299352120571E-2</v>
+        <v>9.3436455973208904E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.6965770835211278E-2</v>
+        <v>7.6217076566386266E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14872,43 +14872,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5151762247130899E-2</v>
+        <v>5.46152665054273E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13760642461564868</v>
+        <v>0.13626784071860931</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13495546285876645</v>
+        <v>0.13364266652745552</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14437388468631718</v>
+        <v>0.14296946946563316</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12886993800033961</v>
+        <v>0.12761633938165928</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1219152458503002</v>
+        <v>0.12072929987899378</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11451411992953378</v>
+        <v>0.11340016934656166</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10224725360400469</v>
+        <v>0.10125263051447159</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0114055208846022E-2</v>
+        <v>8.9237459341055703E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1820499945109648E-2</v>
+        <v>8.1024580684943212E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15690,16 +15690,16 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>8203065933.0124998</v>
+        <v>6562452746.4099998</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15714,8 +15714,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15730,8 +15730,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15746,8 +15746,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>17753993941.386166</v>
+        <v>16113380754.783669</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>12.930473929771464</v>
+        <v>11.723564309325376</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15880,11 +15880,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>475066279.47003394</v>
+        <v>468437447.66347533</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15902,11 +15902,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>458543939.00301653</v>
+        <v>445836642.39159715</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15924,11 +15924,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>442596229.3744846</v>
+        <v>424326263.17657071</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15956,11 +15956,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>427203165.48600757</v>
+        <v>403853699.99095851</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15988,11 +15988,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>412345457.30132753</v>
+        <v>384368881.09496725</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16632,7 +16632,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>8392837603.9706001</v>
+        <v>6714270083.1764803</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16640,11 +16640,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>6271616493.1046057</v>
+        <v>4676882786.3667097</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>8487371563.7394762</v>
+        <v>6803705720.6842785</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16676,7 +16676,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>8487371563.7394762</v>
+        <v>6803705720.6842785</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16706,19 +16706,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>8203065933.0124969</v>
+        <v>6562452746.4099998</v>
       </c>
       <c r="C56" s="123">
-        <v>8203065933.0124969</v>
+        <v>6562452746.4099998</v>
       </c>
       <c r="D56" s="123">
-        <v>8448355886.3277092</v>
+        <v>6770551425.9818649</v>
       </c>
       <c r="E56" s="123">
-        <v>8573395339.7940006</v>
+        <v>6876857671.8395443</v>
       </c>
       <c r="F56" s="123">
-        <v>8828439479.5252323</v>
+        <v>7094149256.700943</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16727,19 +16727,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>8203065933.012495</v>
+        <v>6562452746.4099998</v>
       </c>
       <c r="C57" s="123">
-        <v>8203065933.012495</v>
+        <v>6562452746.4099998</v>
       </c>
       <c r="D57" s="123">
-        <v>8679845295.0109253</v>
+        <v>6976907969.4440937</v>
       </c>
       <c r="E57" s="123">
-        <v>8935178848.911768</v>
+        <v>7199316672.8879862</v>
       </c>
       <c r="F57" s="123">
-        <v>9483130827.5328064</v>
+        <v>7677510651.6329613</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16748,19 +16748,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>8203065933.0124931</v>
+        <v>6562452746.4099998</v>
       </c>
       <c r="C58" s="341">
-        <v>8203065933.0124931</v>
+        <v>6562452746.4099998</v>
       </c>
       <c r="D58" s="123">
-        <v>8993735636.8626118</v>
+        <v>7238179519.1390877</v>
       </c>
       <c r="E58" s="123">
-        <v>9438506339.1455936</v>
+        <v>7618206502.395134</v>
       </c>
       <c r="F58" s="123">
-        <v>10443360379.329018</v>
+        <v>8476405316.1478539</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16779,19 +16779,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>8203065933.0124931</v>
+        <v>6562452746.4100008</v>
       </c>
       <c r="C59" s="341">
-        <v>8203065933.0124931</v>
+        <v>6562452746.4100008</v>
       </c>
       <c r="D59" s="123">
-        <v>9344546558.1996136</v>
+        <v>7510559372.2212534</v>
       </c>
       <c r="E59" s="123">
-        <v>10016448706.21312</v>
+        <v>8066867958.073947</v>
       </c>
       <c r="F59" s="123">
-        <v>11610103840.277256</v>
+        <v>9381860512.5630074</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16810,19 +16810,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>8203065933.0124912</v>
+        <v>6562452746.4100008</v>
       </c>
       <c r="C60" s="341">
-        <v>8203065933.0124912</v>
+        <v>6562452746.4100008</v>
       </c>
       <c r="D60" s="123">
-        <v>9702606152.9596539</v>
+        <v>7769802127.533329</v>
       </c>
       <c r="E60" s="123">
-        <v>10623158771.830408</v>
+        <v>8506068042.9619904</v>
       </c>
       <c r="F60" s="123">
-        <v>12910373672.111689</v>
+        <v>10322806508.590412</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16841,19 +16841,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>8203065933.0124912</v>
+        <v>6562452746.4100008</v>
       </c>
       <c r="C61" s="341">
-        <v>8203065933.0124912</v>
+        <v>6562452746.4100008</v>
       </c>
       <c r="D61" s="123">
-        <v>10049300760.369524</v>
+        <v>8003840303.0804033</v>
       </c>
       <c r="E61" s="123">
-        <v>11227985890.334045</v>
+        <v>8914291920.86516</v>
       </c>
       <c r="F61" s="123">
-        <v>14290591802.684071</v>
+        <v>11254038446.689999</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16933,23 +16933,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16960,23 +16960,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>12.902506149460001</v>
+        <v>11.699798169862193</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>12.992138732995663</v>
+        <v>11.776002145471939</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>13.174963149817861</v>
+        <v>11.931764231691682</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16987,23 +16987,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>12.726673869155672</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>12.726673869155672</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>13.068445724419941</v>
+        <v>11.847721642072468</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>13.251477603279239</v>
+        <v>12.007151855000162</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>13.644268439577344</v>
+        <v>12.349937756233048</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17014,23 +17014,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>12.726673869155672</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>12.726673869155672</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>13.293453124141532</v>
+        <v>12.035010080675905</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>13.612280070528836</v>
+        <v>12.307426501079457</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>14.3325940290521</v>
+        <v>12.922612946089272</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17041,23 +17041,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>12.726673869155672</v>
+        <v>11.550625874532106</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>12.726673869155672</v>
+        <v>11.550625874532106</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>13.544926465877136</v>
+        <v>12.230261333444702</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>14.026569049398569</v>
+        <v>12.629042473402981</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.168955895879394</v>
+        <v>13.571674392541937</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17068,23 +17068,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>12.72667386915567</v>
+        <v>11.550625874532106</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>12.72667386915567</v>
+        <v>11.550625874532106</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>13.801595906188847</v>
+        <v>12.416095462412557</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>14.461479704642512</v>
+        <v>12.943876209526202</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>16.101034060730154</v>
+        <v>14.24617686558906</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17094,23 +17094,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>12.72667386915567</v>
+        <v>11.550625874532106</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>12.72667386915567</v>
+        <v>11.550625874532106</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>14.050118532436622</v>
+        <v>12.583862081177509</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>14.895040598592891</v>
+        <v>13.236505134422075</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>17.090421917574211</v>
+        <v>14.913715967599698</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>13.644268439577344</v>
+        <v>12.349937756233048</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>12.992138732995663</v>
+        <v>11.776002145471939</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>12.902506149460001</v>
+        <v>11.699798169862193</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17236,7 +17236,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>12.726673869155672</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17450,14 +17450,14 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>8370133842.0000019</v>
+        <v>6696107073.6000013</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>6.0000000000000018</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>6.2079507586909539</v>
+        <v>4.976460588939104</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17562,11 +17562,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>484741726.50284642</v>
+        <v>477977888.45862073</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17584,11 +17584,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>467882883.45302093</v>
+        <v>454916783.4269892</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17606,11 +17606,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>451610374.47232771</v>
+        <v>432968312.63665062</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17628,11 +17628,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>435903807.43542308</v>
+        <v>412078794.57697481</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17650,11 +17650,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>420743499.43513364</v>
+        <v>392197137.7210626</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>8563770501.5502882</v>
+        <v>6851016401.2402306</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18222,11 +18222,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>6399347497.8327036</v>
+        <v>4772134614.6561098</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>8660229789.1314545</v>
+        <v>6942273531.476408</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18258,7 +18258,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>8660229789.1314545</v>
+        <v>6942273531.476408</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18288,19 +18288,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>8370133842</v>
+        <v>6696107073.6000023</v>
       </c>
       <c r="C51" s="123">
-        <v>8370133842</v>
+        <v>6696107073.6000023</v>
       </c>
       <c r="D51" s="123">
-        <v>8620419498.1329937</v>
+        <v>6908443999.1573372</v>
       </c>
       <c r="E51" s="123">
-        <v>8748005570.1687508</v>
+        <v>7016915333.3311138</v>
       </c>
       <c r="F51" s="123">
-        <v>9008244071.553587</v>
+        <v>7238632391.6703339</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18309,19 +18309,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>8370133841.9999981</v>
+        <v>6696107073.6000023</v>
       </c>
       <c r="C52" s="123">
-        <v>8370133841.9999981</v>
+        <v>6696107073.6000023</v>
       </c>
       <c r="D52" s="123">
-        <v>8856623540.5613594</v>
+        <v>7119003307.3545628</v>
       </c>
       <c r="E52" s="123">
-        <v>9117157350.4753685</v>
+        <v>7345941702.1758537</v>
       </c>
       <c r="F52" s="123">
-        <v>9676269204.2018089</v>
+        <v>7833874828.3044682</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18330,19 +18330,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>8370133841.9999962</v>
+        <v>6696107073.6000042</v>
       </c>
       <c r="C53" s="123">
-        <v>8370133841.9999962</v>
+        <v>6696107073.6000042</v>
       </c>
       <c r="D53" s="123">
-        <v>9176906736.4377174</v>
+        <v>7385596049.3747101</v>
       </c>
       <c r="E53" s="123">
-        <v>9630735870.2652149</v>
+        <v>7773362859.9062996</v>
       </c>
       <c r="F53" s="123">
-        <v>10656055290.67379</v>
+        <v>8649040197.2354565</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18351,19 +18351,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>8370133841.9999962</v>
+        <v>6696107073.6000051</v>
       </c>
       <c r="C54" s="123">
-        <v>8370133841.9999962</v>
+        <v>6696107073.6000051</v>
       </c>
       <c r="D54" s="123">
-        <v>9534862455.5316048</v>
+        <v>7663523332.2686529</v>
       </c>
       <c r="E54" s="123">
-        <v>10220448912.293755</v>
+        <v>8231161988.237711</v>
       </c>
       <c r="F54" s="123">
-        <v>11846561256.024315</v>
+        <v>9572936365.304657</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18372,19 +18372,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>8370133841.9999952</v>
+        <v>6696107073.6000042</v>
       </c>
       <c r="C55" s="123">
-        <v>8370133841.9999952</v>
+        <v>6696107073.6000042</v>
       </c>
       <c r="D55" s="123">
-        <v>9900214478.3030701</v>
+        <v>7928045960.4238625</v>
       </c>
       <c r="E55" s="123">
-        <v>10839515550.789051</v>
+        <v>8679307050.5779152</v>
       </c>
       <c r="F55" s="123">
-        <v>13173313059.806562</v>
+        <v>10533046157.07748</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18393,19 +18393,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>8370133841.9999924</v>
+        <v>6696107073.6000051</v>
       </c>
       <c r="C56" s="123">
-        <v>8370133841.9999924</v>
+        <v>6696107073.6000051</v>
       </c>
       <c r="D56" s="123">
-        <v>10253970048.478592</v>
+        <v>8166850679.2282019</v>
       </c>
       <c r="E56" s="123">
-        <v>11456660893.090048</v>
+        <v>9095845028.3843422</v>
       </c>
       <c r="F56" s="123">
-        <v>14581641430.977324</v>
+        <v>11483244049.364338</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18455,23 +18455,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>6.0000000000000018</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>6.0000000000000018</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>6.0000000000000018</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>6.0000000000000018</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>6.0000000000000018</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18482,23 +18482,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>6.1794133720135518</v>
+        <v>4.9522104159136839</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>6.2708714593828718</v>
+        <v>5.0299664013409311</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>6.4574193734047487</v>
+        <v>5.1889008192543074</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18509,23 +18509,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>6.3487325586983312</v>
+        <v>5.1031465745261109</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>6.5354921600370997</v>
+        <v>5.2658238261245627</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>6.9362827788830543</v>
+        <v>5.6155910833793339</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18536,23 +18536,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999973</v>
+        <v>4.8000000000000034</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999973</v>
+        <v>4.8000000000000034</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>6.5783225761978565</v>
+        <v>5.2942494269195297</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>6.9036429180664101</v>
+        <v>5.5722140218839522</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>7.6386271654606528</v>
+        <v>6.1999296741248857</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18563,23 +18563,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999973</v>
+        <v>4.8000000000000034</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999973</v>
+        <v>4.8000000000000034</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>6.8349175548571388</v>
+        <v>5.4934772682947877</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>7.326369521841456</v>
+        <v>5.9003801924421202</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>8.4920228132411619</v>
+        <v>6.8622102437137995</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18590,23 +18590,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999964</v>
+        <v>4.8000000000000034</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999964</v>
+        <v>4.8000000000000034</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>7.0968144585397441</v>
+        <v>5.6830961918258867</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>7.7701377937815668</v>
+        <v>6.2216259962486147</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>9.443084166973513</v>
+        <v>7.5504499850821958</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18616,23 +18616,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999947</v>
+        <v>4.8000000000000034</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999947</v>
+        <v>4.8000000000000034</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>7.3503986259042611</v>
+        <v>5.8542796328404529</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>8.2125288144872997</v>
+        <v>6.5202147540887614</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>10.452622411705509</v>
+        <v>8.231584535776415</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18667,7 +18667,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>6.9362827788830543</v>
+        <v>5.6155910833793339</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.2708714593828718</v>
+        <v>5.0299664013409311</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18712,7 +18712,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>6.1794133720135518</v>
+        <v>4.9522104159136839</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18735,7 +18735,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>6</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.9999999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.18</v>
+        <v>-10.28</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>13.27528670453229</v>
+        <v>12.071712236864567</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18922,11 +18922,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中文传媒(600373.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18947,8 +18947,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18969,8 +18969,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18980,8 +18980,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18994,8 +18994,8 @@
       <c r="B11" s="159" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19013,8 +19013,8 @@
         <v>-4.5961886297537391E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19031,8 +19031,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.135599908831609</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19049,8 +19049,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.29648179377498129</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19076,21 +19076,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19098,14 +19098,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.18</v>
+        <v>10.28</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19113,14 +19113,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19140,8 +19140,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19151,8 +19151,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19160,14 +19160,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>12.902506149460001</v>
+        <v>11.699798169862193</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19177,8 +19177,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19198,8 +19198,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19209,8 +19209,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19218,14 +19218,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>12.726673869155675</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19235,8 +19235,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19256,8 +19256,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19267,8 +19267,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19276,14 +19276,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>12.992138732995663</v>
+        <v>11.776002145471939</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -19294,8 +19294,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>12.885266210106266</v>
+        <v>11.685204505918124</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19357,8 +19357,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="370"/>
+      <c r="F49" s="370"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19368,8 +19368,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19377,14 +19377,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>12.726673869155672</v>
+        <v>11.550625874532104</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="370"/>
+      <c r="F51" s="370"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19394,8 +19394,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="370"/>
+      <c r="F52" s="370"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19415,8 +19415,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="370"/>
+      <c r="F55" s="370"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19426,8 +19426,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="370"/>
+      <c r="F56" s="370"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19435,14 +19435,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>13.644268439577344</v>
+        <v>12.349937756233048</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="370"/>
+      <c r="F57" s="370"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19452,8 +19452,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19461,7 +19461,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>12.91528670453229</v>
+        <v>11.711712236864567</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>12.930473929771464</v>
+        <v>11.723564309325376</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.53010312915742175</v>
+        <v>0.58458009875682571</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.61051668952903537</v>
+        <v>0.53758661691746279</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2493163458953562</v>
+        <v>3.8416375372059757</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>5.8598330354243915</v>
+        <v>4.3792241541234382</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.54628703415712532</v>
+        <v>0.62608164668364208</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19696,7 +19696,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.18</v>
+        <v>10.28</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19709,7 +19709,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11534695122345151</v>
+        <v>7.8003271289299514E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19726,7 +19726,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.70272000000000001</v>
+        <v>0.65380063723259008</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.6126267927205324</v>
+        <v>5.3307748005755871</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>7.3153467927205327</v>
+        <v>5.9845754378081768</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.43359005803925377</v>
+        <v>0.48900935091534037</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19795,7 +19795,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.9622843018061904</v>
+        <v>0.93618926635390565</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>10.843923763016019</v>
+        <v>9.427466552119089</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19819,7 +19819,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>11.80620806482221</v>
+        <v>10.363655818472994</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>8.5873327095470353E-2</v>
+        <v>0.11510327363989881</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>10.055772032466596</v>
+        <v>9.118675493470155</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>10.971932453508362</v>
+        <v>10.034835914511921</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19885,7 +19885,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15146710684391118</v>
+        <v>0.14404564603873704</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19942,19 +19942,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="372"/>
+    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="360"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="370" t="s">
+      <c r="B2" s="358" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,45 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40A2FE1-7338-45F4-95FE-652FDF114BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0F5D37-A8C3-447E-BD26-1B5A1097D1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="DDM" sheetId="10" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId3"/>
+    <sheet name="BS" sheetId="3" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId7"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
-    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,20 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="561">
   <si>
     <t>Sales</t>
   </si>
@@ -411,10 +406,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1348,10 +1339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1504,10 +1491,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1525,10 +1508,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1760,71 +1739,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1864,32 +1783,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1987,30 +1880,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2034,58 +1903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2103,23 +1920,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2162,10 +1962,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2284,10 +2080,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2334,133 +2126,1148 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
   <si>
     <t>CN</t>
@@ -3171,7 +3978,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3920,33 +4727,55 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3961,10 +4790,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{5DD48AC0-D3C5-4C4A-B79D-DA76CD234918}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{5EC71C59-AADA-4CA0-87ED-438C3E75AF1F}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4076,7 +4910,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>10.18</v>
+            <v>10.28</v>
           </cell>
         </row>
         <row r="13">
@@ -4101,7 +4935,7 @@
         </row>
         <row r="86">
           <cell r="C86">
-            <v>0.06</v>
+            <v>7.4999999999999997E-2</v>
           </cell>
         </row>
         <row r="92">
@@ -4331,6 +5165,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45797</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>CN</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>中文传媒</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>1395022307</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>600373.SS</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>10.28</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>14340.82931596</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v>Low Growth Asset Play</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>TMT_02</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (CNY) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>11.711712236864567</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>7.8003271289299514E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>600373.SS (CNY)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>4.3792241541234382</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>5.9845754378081768</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>10.363655818472994</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>10.034835914511921</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>805173862.5</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>304213708</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>-304213708</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>30189572.474333331</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-127330087.00000001</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>-97140514.525666684</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>-38841055</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-177008336.99358332</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>335956918.03600812</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>492183955.98074996</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>3.4320466769170409E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>3.5019455252918295E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>1.1337405781301506</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>3.888300021475994E-2</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>4.2520188912675866E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>7.6099586896956867E-2</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>8.3218084848475898E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.30413488760323032</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.30413488760323026</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.6800075256655485</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.6800075256655487</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>4.7041919784942907</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>1685959940.8299999</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.2085541086835108</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>9.2587702159681276E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>2.0939079363495856</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>10570865213.440001</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>7551907966.0066681</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>5.4134675324633843</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>3684979983.197</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.6415204722579393</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>11.550625874532104</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>2.6400638402357823</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.05</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>12.35 CNY</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.03</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>5</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>11.78 CNY</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.02</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>5</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>11.7 CNY</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>5</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>11.55 CNY</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>11.55 CNY</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>11.711712236864567</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>600373.SS</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>0.53758661691746279</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>3.8416375372059757</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>4.3792241541234382</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.62608164668364208</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>0.65380063723259008</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>5.3307748005755871</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>5.9845754378081768</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.48900935091534037</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>0.93618926635390565</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>9.427466552119089</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>10.363655818472994</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>0.11510327363989881</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>0.91616042104176609</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>9.118675493470155</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>10.034835914511921</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.14404564603873704</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4347,24 +6924,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4378,7 +6955,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4387,15 +6964,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C6" s="51">
         <v>1395022307</v>
@@ -4404,7 +6981,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4414,7 +6991,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4427,26 +7004,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="C12" s="50">
         <v>10.28</v>
@@ -4456,17 +7033,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4480,7 +7057,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4494,7 +7071,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="C16" s="50">
         <v>1</v>
@@ -4507,71 +7084,71 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="361" t="s">
-        <v>356</v>
-      </c>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="361"/>
-      <c r="F18" s="361"/>
+      <c r="B18" s="371" t="s">
+        <v>468</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v>Low Growth Asset Play</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>464</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
         <v/>
       </c>
       <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4592,7 +7169,7 @@
         <v>11.711712236864567</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4605,7 +7182,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4616,7 +7193,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4624,7 +7201,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4635,7 +7212,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F29" s="302">
         <v>0.45</v>
@@ -4643,7 +7220,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4654,7 +7231,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F30" s="312">
         <v>0.3</v>
@@ -4662,7 +7239,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4673,7 +7250,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4681,7 +7258,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4692,7 +7269,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4704,7 +7281,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4712,27 +7289,27 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="361" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="361"/>
-      <c r="F36" s="361"/>
+    <row r="36" spans="1:6">
+      <c r="B36" s="371" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
-        <v>336</v>
-      </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4740,17 +7317,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="362" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
+      <c r="B40" s="367" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4766,17 +7343,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="362" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="362"/>
-      <c r="D43" s="362"/>
-      <c r="E43" s="362"/>
-      <c r="F43" s="362"/>
+      <c r="B43" s="367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4789,7 +7366,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4801,17 +7378,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="362" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="362"/>
-      <c r="D47" s="362"/>
-      <c r="E47" s="362"/>
-      <c r="F47" s="362"/>
+      <c r="B47" s="367" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4823,17 +7400,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="362" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="362"/>
-      <c r="D50" s="362"/>
-      <c r="E50" s="362"/>
-      <c r="F50" s="362"/>
+      <c r="B50" s="367" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4848,7 +7425,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4863,7 +7440,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4876,12 +7453,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4893,17 +7470,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="362" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="362"/>
-      <c r="D58" s="362"/>
-      <c r="E58" s="362"/>
-      <c r="F58" s="362"/>
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4915,17 +7492,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="362" t="s">
-        <v>335</v>
-      </c>
-      <c r="C61" s="365"/>
-      <c r="D61" s="365"/>
-      <c r="E61" s="365"/>
-      <c r="F61" s="365"/>
+      <c r="B61" s="367" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4937,26 +7514,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="361" t="s">
-        <v>340</v>
-      </c>
-      <c r="C64" s="361"/>
-      <c r="D64" s="361"/>
-      <c r="E64" s="361"/>
-      <c r="F64" s="361"/>
+      <c r="B64" s="371" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="361" t="s">
-        <v>358</v>
-      </c>
-      <c r="C65" s="361"/>
-      <c r="D65" s="361"/>
-      <c r="E65" s="361"/>
-      <c r="F65" s="361"/>
+      <c r="B65" s="371" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4969,7 +7546,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4982,7 +7559,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -4992,14 +7569,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>3.5019455252918295E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -5008,18 +7585,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -5074,7 +7651,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -5085,33 +7662,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="361" t="s">
-        <v>359</v>
-      </c>
-      <c r="C80" s="361"/>
-      <c r="D80" s="361"/>
-      <c r="E80" s="361"/>
-      <c r="F80" s="361"/>
+      <c r="B80" s="371" t="s">
+        <v>471</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5120,7 +7697,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5129,7 +7706,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5141,31 +7718,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="361" t="s">
-        <v>360</v>
-      </c>
-      <c r="C89" s="361"/>
-      <c r="D89" s="361"/>
-      <c r="E89" s="361"/>
-      <c r="F89" s="361"/>
+      <c r="B89" s="371" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="361" t="s">
-        <v>361</v>
-      </c>
-      <c r="C90" s="361"/>
-      <c r="D90" s="361"/>
-      <c r="E90" s="361"/>
-      <c r="F90" s="361"/>
+      <c r="B90" s="371" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5173,7 +7750,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5186,7 +7763,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5198,36 +7775,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="361" t="s">
-        <v>362</v>
-      </c>
-      <c r="C97" s="361"/>
-      <c r="D97" s="361"/>
-      <c r="E97" s="361"/>
-      <c r="F97" s="361"/>
+      <c r="B97" s="371" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="361" t="s">
-        <v>341</v>
-      </c>
-      <c r="C101" s="361"/>
-      <c r="D101" s="361"/>
-      <c r="E101" s="361"/>
-      <c r="F101" s="361"/>
+      <c r="B101" s="371" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5240,7 +7817,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5253,7 +7830,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5262,7 +7839,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5271,12 +7848,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5289,7 +7866,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5302,7 +7879,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5315,12 +7892,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5333,7 +7910,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5345,17 +7922,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="361" t="s">
-        <v>363</v>
-      </c>
-      <c r="C116" s="361"/>
-      <c r="D116" s="361"/>
-      <c r="E116" s="361"/>
-      <c r="F116" s="361"/>
+      <c r="B116" s="371" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5368,7 +7945,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5381,7 +7958,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5389,30 +7966,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="362" t="s">
-        <v>364</v>
-      </c>
-      <c r="C123" s="362"/>
-      <c r="D123" s="362"/>
-      <c r="E123" s="362"/>
-      <c r="F123" s="362"/>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>473</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5527,7 +8104,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5539,17 +8116,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="366" t="s">
-        <v>367</v>
-      </c>
-      <c r="C134" s="366"/>
-      <c r="D134" s="366"/>
-      <c r="E134" s="366"/>
-      <c r="F134" s="366"/>
+      <c r="B134" s="369" t="s">
+        <v>474</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5558,31 +8135,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="364" t="s">
-        <v>365</v>
-      </c>
-      <c r="C138" s="364"/>
-      <c r="D138" s="364"/>
-      <c r="E138" s="364"/>
-      <c r="F138" s="364"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="361" t="s">
-        <v>366</v>
-      </c>
-      <c r="C139" s="361"/>
-      <c r="D139" s="361"/>
-      <c r="E139" s="361"/>
-      <c r="F139" s="361"/>
+      <c r="B138" s="370" t="s">
+        <v>353</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="B139" s="371" t="s">
+        <v>476</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5591,7 +8168,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5600,7 +8177,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5613,7 +8190,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5626,7 +8203,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5655,7 +8232,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5668,7 +8245,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5681,7 +8258,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5690,12 +8267,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5724,7 +8301,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5737,7 +8314,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5750,7 +8327,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5759,12 +8336,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5793,7 +8370,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5806,7 +8383,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5819,7 +8396,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5828,12 +8405,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5862,7 +8439,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5875,7 +8452,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5888,7 +8465,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5897,7 +8474,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5906,113 +8483,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="368" t="s">
-        <v>373</v>
-      </c>
-      <c r="C179" s="361"/>
-      <c r="D179" s="361"/>
-      <c r="E179" s="361"/>
-      <c r="F179" s="361"/>
+      <c r="B179" s="372" t="s">
+        <v>477</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="365" t="s">
-        <v>377</v>
-      </c>
-      <c r="C182" s="365"/>
-      <c r="D182" s="365"/>
-      <c r="E182" s="365"/>
-      <c r="F182" s="365"/>
+      <c r="B182" s="373" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="362" t="s">
-        <v>378</v>
-      </c>
-      <c r="C188" s="362"/>
-      <c r="D188" s="362"/>
-      <c r="E188" s="362"/>
-      <c r="F188" s="362"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="34.35" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>478</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="367" t="s">
-        <v>379</v>
-      </c>
-      <c r="C191" s="367"/>
-      <c r="D191" s="367"/>
-      <c r="E191" s="367"/>
-      <c r="F191" s="367"/>
+      <c r="B191" s="368" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="367" t="s">
-        <v>380</v>
-      </c>
-      <c r="C192" s="367"/>
-      <c r="D192" s="367"/>
-      <c r="E192" s="367"/>
-      <c r="F192" s="367"/>
+      <c r="B192" s="368" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6029,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6053,7 +8630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6118,7 +8695,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6134,7 +8711,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="106">
         <v>1</v>
@@ -6142,7 +8719,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="351">
         <v>9304036682</v>
@@ -6178,7 +8755,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="351">
         <v>5676944377</v>
@@ -6214,7 +8791,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="351">
         <v>2587076947</v>
@@ -6250,7 +8827,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="352">
         <v>775878829</v>
@@ -6286,7 +8863,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="351">
         <v>218971112</v>
@@ -6316,7 +8893,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6332,7 +8909,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6348,7 +8925,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6364,7 +8941,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="351">
         <v>127330087</v>
@@ -6394,7 +8971,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="351">
         <v>282045305</v>
@@ -6424,7 +9001,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="351">
         <v>399466141</v>
@@ -6460,7 +9037,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="353">
         <v>783228215</v>
@@ -6496,7 +9073,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="351">
         <v>38841055</v>
@@ -6532,13 +9109,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="351">
         <v>304213708</v>
@@ -6568,7 +9145,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="351"/>
       <c r="D20" s="351"/>
@@ -6584,7 +9161,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="351"/>
       <c r="D21" s="351"/>
@@ -6600,7 +9177,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C22" s="351">
         <v>401377348</v>
@@ -6636,7 +9213,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C23" s="351">
         <v>-5702735165</v>
@@ -6672,7 +9249,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C24" s="351">
         <v>-1440890089</v>
@@ -6737,15 +9314,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>465</v>
+        <v>559</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
@@ -6782,7 +9359,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
@@ -6819,7 +9396,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
@@ -6856,7 +9433,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
@@ -6893,7 +9470,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6930,7 +9507,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6946,12 +9523,12 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="333">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -7000,7 +9577,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="333">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7049,7 +9626,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="329">
         <f>IF(C36="","",C36+C37)</f>
@@ -7098,7 +9675,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="333">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7147,7 +9724,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="346">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7196,7 +9773,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C41" s="346">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7245,7 +9822,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="333">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7294,7 +9871,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7343,7 +9920,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7392,7 +9969,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="349">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7441,7 +10018,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="333">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -7490,7 +10067,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="334">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -7539,7 +10116,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="333">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -7588,12 +10165,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="333">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -7642,7 +10219,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="333">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -7691,12 +10268,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7745,7 +10322,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7794,7 +10371,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7843,7 +10420,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7892,13 +10469,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" s="333">
         <f>IF(C$4="","",-C19)</f>
@@ -7947,7 +10524,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="333">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -7996,7 +10573,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="333">
         <f>IF(C$4="","",-C21)</f>
@@ -8045,7 +10622,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8094,7 +10671,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
@@ -8143,7 +10720,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8198,7 +10775,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8297,7 +10874,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8396,7 +10973,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -8412,13 +10989,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
@@ -8467,7 +11044,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -8501,7 +11078,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
@@ -8535,7 +11112,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -8584,7 +11161,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -8656,7 +11233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8676,7 +11253,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="99">
         <v>45657</v>
@@ -8692,7 +11269,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8703,27 +11280,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="19">
         <f>20858204.32+1750682273.49+7611314.85+131065409.1</f>
@@ -8734,7 +11311,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="19">
         <v>10570865213.440001</v>
@@ -8745,7 +11322,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -8755,7 +11332,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -8766,7 +11343,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="19">
         <v>1152244678.0699999</v>
@@ -8776,7 +11353,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8787,7 +11364,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8797,7 +11374,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19">
         <v>5809566736.8500004</v>
@@ -8808,7 +11385,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8818,7 +11395,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8829,7 +11406,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="19">
         <v>382020580.81</v>
@@ -8839,7 +11416,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8850,7 +11427,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="19">
         <v>0</v>
@@ -8862,7 +11439,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="19">
         <f>27904732.88+601371713.32</f>
@@ -8875,7 +11452,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8886,7 +11463,7 @@
         <v>1791918540.4819999</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8904,27 +11481,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>185</v>
-      </c>
       <c r="G14" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H14" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C15" s="19">
         <f>55162498.36</f>
@@ -8934,7 +11511,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8945,7 +11522,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <f>44364412.13+1023569661.78</f>
@@ -8955,7 +11532,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8966,7 +11543,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>666543619.20000005</v>
@@ -8975,7 +11552,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G17" s="19">
         <v>11101623.65</v>
@@ -8986,7 +11563,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8995,7 +11572,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -9006,7 +11583,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="19">
         <f>2110695200.78+216680982.55+108677337.18</f>
@@ -9016,7 +11593,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="19">
         <v>1925789668.97</v>
@@ -9027,7 +11604,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -9036,7 +11613,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -9047,7 +11624,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="19">
         <v>730819471.01999998</v>
@@ -9056,7 +11633,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9067,7 +11644,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="19">
         <v>195810554.43000001</v>
@@ -9079,7 +11656,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19">
         <f>2858698047.61+71365873.11+118340146.3</f>
@@ -9092,7 +11669,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -9103,7 +11680,7 @@
         <v>1412334032.408</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -9116,30 +11693,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H26" s="186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19">
         <v>1601516869.78</v>
       </c>
       <c r="F27" s="187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
@@ -9152,13 +11729,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G28" s="12">
         <v>337582462.13999999</v>
@@ -9167,13 +11744,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="190" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9186,13 +11763,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
@@ -9202,14 +11779,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>1601516869.78</v>
       </c>
       <c r="F31" s="190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
@@ -9219,14 +11796,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>9721988024.8299999</v>
       </c>
       <c r="F32" s="192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
@@ -9239,7 +11816,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="84">
         <v>11323504894.610001</v>
@@ -9252,24 +11829,24 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H34" s="198" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F35" s="199" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G35" s="193">
         <f>C12+C24</f>
@@ -9282,13 +11859,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19">
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9298,13 +11875,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19">
         <v>84443071.049999997</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9314,13 +11891,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19">
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9330,13 +11907,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G39" s="191">
         <f>C7+C17+C19+C20</f>
@@ -9349,14 +11926,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>84443071.049999997</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9369,14 +11946,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>974532871.35000002</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9389,13 +11966,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" s="84">
         <v>1058975942.4</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9408,7 +11985,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -9419,21 +11996,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="F45" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9465,20 +12042,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C49" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D49" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -9492,7 +12069,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9506,19 +12083,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C53" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D53" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" s="253"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9532,7 +12109,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9549,19 +12126,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C57" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D57" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57" s="253"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -9572,7 +12149,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -9586,19 +12163,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D61" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F61" s="253"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9609,12 +12186,12 @@
         <v>1.8889170076983472E-2</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9625,21 +12202,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F65" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9650,12 +12227,12 @@
         <v>7551907966.0066681</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9665,7 +12242,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9675,7 +12252,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9685,7 +12262,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9698,19 +12275,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C72" s="234" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D72" s="182" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F72" s="253"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9721,12 +12298,12 @@
         <v>-754739311.85833323</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9737,12 +12314,12 @@
         <v>14.005981995839356</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9750,12 +12327,12 @@
         <v>3018957247.4333329</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9763,7 +12340,7 @@
         <v>4</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9771,19 +12348,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D78" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" s="253"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9797,7 +12374,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9811,7 +12388,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9825,7 +12402,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9839,7 +12416,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9850,15 +12427,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9875,7 +12452,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9892,7 +12469,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9909,7 +12486,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9931,7 +12508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9957,7 +12534,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -10010,12 +12587,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -10033,7 +12610,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -10047,7 +12624,7 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="327">
         <f>G4</f>
@@ -10104,7 +12681,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="328">
         <f>C25</f>
@@ -10159,7 +12736,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
@@ -10214,7 +12791,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="328">
         <f>C35</f>
@@ -10269,7 +12846,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10326,7 +12903,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="328">
         <f>BS!$G$39*BS!D58</f>
@@ -10381,7 +12958,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" s="328">
         <f>-C4*C78</f>
@@ -10436,7 +13013,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10493,7 +13070,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="328">
         <f>C50</f>
@@ -10548,7 +13125,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10603,7 +13180,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -10658,7 +13235,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10715,7 +13292,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10772,7 +13349,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="328">
         <f>-C4*C85</f>
@@ -10780,7 +13357,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10798,14 +13375,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="328">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10823,7 +13400,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
@@ -10899,12 +13476,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10922,7 +13499,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10943,7 +13520,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
@@ -11000,7 +13577,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="328">
         <f>-C4*C29</f>
@@ -11057,7 +13634,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
@@ -11118,14 +13695,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="63">
         <f>G28</f>
@@ -11133,7 +13710,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11193,7 +13770,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11244,7 +13821,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -11303,21 +13880,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-1811198118</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11367,7 +13944,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="340">
         <f>AVERAGE(G34:J34)</f>
@@ -11375,7 +13952,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11426,7 +14003,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="329">
         <f>C33+C34</f>
@@ -11487,7 +14064,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11610,7 +14187,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -11669,21 +14246,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11737,12 +14314,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -11760,14 +14337,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="328">
         <f>-BS!G31*Normalized_FCF!C54</f>
@@ -11822,7 +14399,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11877,7 +14454,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11934,7 +14511,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
@@ -11993,23 +14570,23 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" s="87">
         <v>0.01</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -12029,14 +14606,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>7.5523791471175328E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12056,7 +14633,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -12115,17 +14692,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12180,7 +14757,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12235,7 +14812,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12290,7 +14867,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12345,13 +14922,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12401,7 +14978,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12460,17 +15037,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12495,7 +15072,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12520,7 +15097,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12545,7 +15122,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12575,12 +15152,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12598,7 +15175,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12619,7 +15196,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -12676,7 +15253,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -12733,7 +15310,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -12790,7 +15367,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12847,7 +15424,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12904,7 +15481,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12912,7 +15489,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>466</v>
+        <v>560</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12963,7 +15540,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -13020,7 +15597,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -13077,7 +15654,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13134,7 +15711,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -13249,7 +15826,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13306,7 +15883,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C85" s="264">
         <v>0</v>
@@ -13332,7 +15909,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -13356,7 +15933,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13417,7 +15994,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13536,7 +16113,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13591,7 +16168,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C93" s="356">
         <v>0.1</v>
@@ -13612,7 +16189,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
@@ -13671,7 +16248,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C96" s="62"/>
       <c r="D96" s="27"/>
@@ -13692,7 +16269,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C97" s="77">
         <f>C4/G4-1</f>
@@ -13749,7 +16326,7 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
@@ -13809,12 +16386,12 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="54"/>
       <c r="D100" s="56"/>
       <c r="E100" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="37"/>
@@ -13832,17 +16409,17 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E101" s="268"/>
       <c r="G101" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="344">
         <f>BS!G32</f>
@@ -13899,7 +16476,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C103" s="345">
         <f>BS!C4</f>
@@ -13956,7 +16533,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="345">
         <f>BS!C6+BS!C7</f>
@@ -14013,7 +16590,7 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C105" s="344">
         <f>BS!G30</f>
@@ -14070,7 +16647,7 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" s="344">
         <f>BS!G27</f>
@@ -14131,14 +16708,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
@@ -14154,7 +16731,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -14211,7 +16788,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C110" s="94">
         <f>C104/C$4</f>
@@ -14268,7 +16845,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C111" s="94">
         <f>BS!$G$38/C$4</f>
@@ -14299,14 +16876,14 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -14358,7 +16935,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
@@ -14414,7 +16991,7 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="55"/>
       <c r="D117" s="55"/>
@@ -14468,7 +17045,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
@@ -14522,7 +17099,7 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C119" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
@@ -14576,7 +17153,7 @@
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="B120" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C120" s="15">
         <f>C102/C106</f>
@@ -14633,7 +17210,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
@@ -14709,12 +17286,12 @@
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C123" s="54"/>
       <c r="D123" s="56"/>
       <c r="E123" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F123" s="56"/>
       <c r="G123" s="37"/>
@@ -14732,7 +17309,7 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C124" s="179"/>
       <c r="D124" s="27"/>
@@ -14811,7 +17388,7 @@
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14867,7 +17444,7 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
@@ -15612,7 +18189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15629,32 +18206,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15665,7 +18242,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15675,7 +18252,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15686,7 +18263,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15696,15 +18273,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15714,13 +18291,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="369"/>
-      <c r="F7" s="369"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15730,13 +18307,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="369"/>
-      <c r="F8" s="369"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15746,13 +18323,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="369"/>
-      <c r="F9" s="369"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15766,7 +18343,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15780,7 +18357,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -15797,7 +18374,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15807,13 +18384,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15823,7 +18400,7 @@
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15833,7 +18410,7 @@
     </row>
     <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -15850,19 +18427,19 @@
     </row>
     <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="128" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="129" t="s">
         <v>107</v>
-      </c>
-      <c r="C20" s="128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="128" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="129" t="s">
-        <v>110</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -16628,7 +19205,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16651,7 +19228,7 @@
     <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
@@ -16665,7 +19242,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16886,7 +19463,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -17115,19 +19692,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D73" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E73" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17252,20 +19829,20 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C80" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="3:3">
@@ -17372,7 +19949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -17389,32 +19966,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
@@ -17425,7 +20002,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17435,7 +20012,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17446,7 +20023,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17456,13 +20033,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369"/>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17479,7 +20056,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17489,13 +20066,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17505,7 +20082,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17515,7 +20092,7 @@
     </row>
     <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
@@ -17532,19 +20109,19 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -18210,7 +20787,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -18233,7 +20810,7 @@
     <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
@@ -18247,7 +20824,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18418,7 +20995,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18637,19 +21214,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D68" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E68" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F68" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18774,20 +21351,20 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C75" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="3:3">
@@ -18823,7 +21400,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -18838,20 +21415,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18863,14 +21440,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18892,14 +21469,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="107">
         <f>DCF!C3</f>
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18912,7 +21489,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18922,11 +21499,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="371" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中文传媒(600373.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="371"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18937,7 +21514,7 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
@@ -18947,8 +21524,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="371"/>
-      <c r="F8" s="371"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18959,7 +21536,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
@@ -18969,8 +21546,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="371"/>
-      <c r="F9" s="371"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18980,8 +21557,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="371"/>
-      <c r="F10" s="371"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18992,10 +21569,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>444</v>
-      </c>
-      <c r="E11" s="371"/>
-      <c r="F11" s="371"/>
+        <v>424</v>
+      </c>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19006,15 +21583,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-4.5961886297537391E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="371"/>
-      <c r="F12" s="371"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19025,14 +21602,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.135599908831609</v>
       </c>
-      <c r="E13" s="371"/>
-      <c r="F13" s="371"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19043,18 +21620,18 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.29648179377498129</v>
       </c>
-      <c r="E14" s="371"/>
-      <c r="F14" s="371"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -19063,38 +21640,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="371" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="372"/>
+      <c r="E18" s="377" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="372"/>
-      <c r="F19" s="372"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="372"/>
-      <c r="F20" s="372"/>
+        <v>298</v>
+      </c>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -19104,12 +21681,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="372"/>
-      <c r="F21" s="372"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -19119,44 +21696,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="372"/>
-      <c r="F22" s="372"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="370"/>
-      <c r="F25" s="370"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="164">
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="370"/>
-      <c r="F26" s="370"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19166,55 +21743,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="370"/>
-      <c r="F27" s="370"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="370"/>
-      <c r="F28" s="370"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="370"/>
-      <c r="F31" s="370"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C32" s="164">
         <v>0</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="370"/>
-      <c r="F32" s="370"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19224,55 +21801,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="370"/>
-      <c r="F33" s="370"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="370"/>
-      <c r="F34" s="370"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="370"/>
-      <c r="F37" s="370"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" s="164">
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="370"/>
-      <c r="F38" s="370"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19282,24 +21859,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="370"/>
-      <c r="F39" s="370"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19312,7 +21889,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19321,12 +21898,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19341,39 +21918,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="370"/>
-      <c r="F49" s="370"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19383,55 +21960,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="370"/>
-      <c r="F51" s="370"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="370"/>
-      <c r="F52" s="370"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="370"/>
-      <c r="F55" s="370"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="164">
         <v>0.05</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="370"/>
-      <c r="F56" s="370"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19441,23 +22018,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="370"/>
-      <c r="F57" s="370"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19468,7 +22045,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19477,7 +22054,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19486,15 +22063,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" s="252" t="s">
         <v>303</v>
-      </c>
-      <c r="E63" s="252" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19502,24 +22079,24 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C65" s="151">
         <v>2.3134236943577701E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
@@ -19530,20 +22107,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19553,19 +22130,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19575,14 +22152,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19591,7 +22168,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19600,12 +22177,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19615,7 +22192,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
@@ -19628,12 +22205,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19642,7 +22219,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19654,7 +22231,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19664,7 +22241,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
@@ -19675,7 +22252,7 @@
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19687,12 +22264,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19705,7 +22282,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19717,12 +22294,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19731,7 +22308,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19743,7 +22320,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19753,7 +22330,7 @@
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
@@ -19764,7 +22341,7 @@
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19773,14 +22350,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19791,7 +22368,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19803,7 +22380,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19815,17 +22392,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>10.363655818472994</v>
       </c>
       <c r="D99" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19837,12 +22414,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19851,7 +22428,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19861,7 +22438,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19871,17 +22448,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>10.034835914511921</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19893,32 +22470,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -19937,24 +22514,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1528048E-47DF-4689-9764-0B999420DF44}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E2F300-6631-4E49-B7C2-4218E921460C}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="360"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="358" t="s">
-        <v>456</v>
-      </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
+      <c r="B2" s="379" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0F5D37-A8C3-447E-BD26-1B5A1097D1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E08B920-BFDD-425D-8451-0E1A35335D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4754,8 +4754,22 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4766,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -4790,11 +4795,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>10.28</v>
+        <v>10.24</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14340.82931596</v>
+        <v>14285.02842368</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.8003271289299514E-2</v>
+        <v>7.9451074657479692E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5577,13 +5577,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5595,13 +5595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5621,13 +5621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5678,13 +5678,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5770,7 +5770,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="373"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4320466769170409E-2</v>
+        <v>3.445453109248748E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5019455252918295E-2</v>
+        <v>3.515625E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5951,13 +5951,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6245,13 +6245,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,13 +6413,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
       <c r="B139" s="371" t="s">
@@ -6761,7 +6761,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
       <c r="C179" s="371"/>
@@ -6804,13 +6804,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,12 +6857,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,15 +6878,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>10.28</v>
+        <v>10.24</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14340.82931596</v>
+        <v>14285.02842368</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.8003271289299514E-2</v>
+        <v>7.9451074657479692E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7299,13 +7299,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7317,13 +7317,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7343,13 +7343,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7378,13 +7378,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7400,13 +7400,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -7470,13 +7470,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7492,7 +7492,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="373"/>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4320466769170409E-2</v>
+        <v>3.445453109248748E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5019455252918295E-2</v>
+        <v>3.515625E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7673,13 +7673,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7967,13 +7967,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,13 +8135,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="371" t="s">
@@ -8483,7 +8483,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
       <c r="C179" s="371"/>
@@ -8526,13 +8526,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,6 +8579,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8595,17 +8606,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,24 +16193,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5019455252918295E-2</v>
+        <v>3.515625E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5019455252918295E-2</v>
+        <v>3.515625E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8287937743190669E-2</v>
+        <v>6.8554687500000003E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5661478599221793E-2</v>
+        <v>6.591796875E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>5.9533073929961093E-2</v>
+        <v>5.9765624999999996E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4320466769170409E-2</v>
+        <v>3.445453109248748E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3426603206421232E-2</v>
+        <v>2.3518113375196315E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11721680630220049</v>
+        <v>0.11767468445181846</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.0879632758676601E-2</v>
+        <v>8.1195568824140169E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.7279584203796358E-2</v>
+        <v>6.7542395079592421E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11060465239492975</v>
+        <v>0.11103670181834743</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10466610430500571</v>
+        <v>0.10507495627494713</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10063743098214223</v>
+        <v>0.10103054594691621</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11234223011126826</v>
+        <v>0.1127810669476404</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.3436455973208904E-2</v>
+        <v>9.3801442129354234E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.6217076566386266E-2</v>
+        <v>7.65147995217237E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.46152665054273E-2</v>
+        <v>5.4828607390214119E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13626784071860931</v>
+        <v>0.13680013697141635</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13364266652745552</v>
+        <v>0.13416470819357837</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14296946946563316</v>
+        <v>0.14352794395573329</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12761633938165928</v>
+        <v>0.12811484070736889</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12072929987899378</v>
+        <v>0.12120089870664609</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11340016934656166</v>
+        <v>0.11384313875807166</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10125263051447159</v>
+        <v>0.10164814860241872</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9237459341055703E-2</v>
+        <v>8.9586043166606691E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1024580684943212E-2</v>
+        <v>8.1341082953243771E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18273,10 +18273,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375" t="s">
+      <c r="E6" s="378" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="375"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -18291,8 +18291,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -18307,8 +18307,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="375"/>
-      <c r="F8" s="375"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -18323,8 +18323,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -20033,8 +20033,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.28</v>
+        <v>-10.24</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21499,11 +21499,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="377" t="str">
+      <c r="E7" s="380" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 中文传媒(600373.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="377"/>
+      <c r="F7" s="380"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -21524,8 +21524,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -21546,8 +21546,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -21557,8 +21557,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="377"/>
-      <c r="F10" s="377"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -21571,8 +21571,8 @@
       <c r="B11" s="159" t="s">
         <v>424</v>
       </c>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
+      <c r="E11" s="380"/>
+      <c r="F11" s="380"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -21590,8 +21590,8 @@
         <v>-4.5961886297537391E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -21608,8 +21608,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.135599908831609</v>
       </c>
-      <c r="E13" s="377"/>
-      <c r="F13" s="377"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -21626,8 +21626,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.29648179377498129</v>
       </c>
-      <c r="E14" s="377"/>
-      <c r="F14" s="377"/>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -21653,21 +21653,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="377" t="s">
+      <c r="E18" s="380" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="378"/>
+      <c r="F18" s="381"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
+      <c r="E20" s="381"/>
+      <c r="F20" s="381"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -21675,14 +21675,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.28</v>
+        <v>10.24</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
+      <c r="E21" s="381"/>
+      <c r="F21" s="381"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -21696,8 +21696,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -21717,8 +21717,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -21728,8 +21728,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="376"/>
+      <c r="E26" s="379"/>
+      <c r="F26" s="379"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -21743,8 +21743,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="376"/>
-      <c r="F27" s="376"/>
+      <c r="E27" s="379"/>
+      <c r="F27" s="379"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -21754,8 +21754,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -21775,8 +21775,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="376"/>
-      <c r="F31" s="376"/>
+      <c r="E31" s="379"/>
+      <c r="F31" s="379"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -21786,8 +21786,8 @@
         <v>0</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="376"/>
-      <c r="F32" s="376"/>
+      <c r="E32" s="379"/>
+      <c r="F32" s="379"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -21801,8 +21801,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="376"/>
-      <c r="F33" s="376"/>
+      <c r="E33" s="379"/>
+      <c r="F33" s="379"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -21812,8 +21812,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="376"/>
-      <c r="F34" s="376"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -21833,8 +21833,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="376"/>
-      <c r="F37" s="376"/>
+      <c r="E37" s="379"/>
+      <c r="F37" s="379"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -21844,8 +21844,8 @@
         <v>0.03</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="376"/>
-      <c r="F38" s="376"/>
+      <c r="E38" s="379"/>
+      <c r="F38" s="379"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -21859,8 +21859,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="376"/>
-      <c r="F39" s="376"/>
+      <c r="E39" s="379"/>
+      <c r="F39" s="379"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -21871,8 +21871,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="376"/>
-      <c r="F40" s="376"/>
+      <c r="E40" s="379"/>
+      <c r="F40" s="379"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -21934,8 +21934,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -21945,8 +21945,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -21960,8 +21960,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="376"/>
-      <c r="F51" s="376"/>
+      <c r="E51" s="379"/>
+      <c r="F51" s="379"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -21971,8 +21971,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="376"/>
-      <c r="F52" s="376"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -21992,8 +21992,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="376"/>
-      <c r="F55" s="376"/>
+      <c r="E55" s="379"/>
+      <c r="F55" s="379"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -22003,8 +22003,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="376"/>
-      <c r="F56" s="376"/>
+      <c r="E56" s="379"/>
+      <c r="F56" s="379"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -22018,8 +22018,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="376"/>
-      <c r="F57" s="376"/>
+      <c r="E57" s="379"/>
+      <c r="F57" s="379"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -22029,8 +22029,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="376"/>
-      <c r="F58" s="376"/>
+      <c r="E58" s="379"/>
+      <c r="F58" s="379"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.28</v>
+        <v>10.24</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>7.8003271289299514E-2</v>
+        <v>7.9451074657479692E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22519,19 +22519,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="381"/>
+    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="369"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="379" t="s">
+      <c r="B2" s="367" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="380"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="368"/>
+      <c r="D2" s="368"/>
+      <c r="E2" s="368"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E08B920-BFDD-425D-8451-0E1A35335D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4183F23D-F205-4FC7-87CC-CAD539342F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4762,15 +4762,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4780,7 +4771,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>10.24</v>
+        <v>10.25</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14285.02842368</v>
+        <v>14298.97864675</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.9451074657479692E-2</v>
+        <v>7.9088402437900385E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.445453109248748E-2</v>
+        <v>3.4420916915811881E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.515625E-2</v>
+        <v>3.5121951219512199E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,15 +6857,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6878,12 +6875,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>10.24</v>
+        <v>10.25</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14285.02842368</v>
+        <v>14298.97864675</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.9451074657479692E-2</v>
+        <v>7.9088402437900385E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.445453109248748E-2</v>
+        <v>3.4420916915811881E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.515625E-2</v>
+        <v>3.5121951219512199E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,17 +8579,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8606,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,24 +16193,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.515625E-2</v>
+        <v>3.5121951219512199E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.515625E-2</v>
+        <v>3.5121951219512199E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8554687500000003E-2</v>
+        <v>6.8487804878048786E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.591796875E-2</v>
+        <v>6.5853658536585369E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>5.9765624999999996E-2</v>
+        <v>5.9707317073170729E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.445453109248748E-2</v>
+        <v>3.4420916915811881E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3518113375196315E-2</v>
+        <v>2.3495168874342463E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11767468445181846</v>
+        <v>0.11755987988162156</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.1195568824140169E-2</v>
+        <v>8.1116353635043451E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.7542395079592421E-2</v>
+        <v>6.7476500060002581E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11103670181834743</v>
+        <v>0.11092837332876856</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10507495627494713</v>
+        <v>0.10497244412248377</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10103054594691621</v>
+        <v>0.10093197956062654</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.1127810669476404</v>
+        <v>0.11267103663842318</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.3801442129354234E-2</v>
+        <v>9.3709928527276817E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.65147995217237E-2</v>
+        <v>7.6440150936824464E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4828607390214119E-2</v>
+        <v>5.4775116065930982E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13680013697141635</v>
+        <v>0.13666667342315156</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13416470819357837</v>
+        <v>0.13403381579534074</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14352794395573329</v>
+        <v>0.14338791669333745</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12811484070736889</v>
+        <v>0.12798985061887388</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12120089870664609</v>
+        <v>0.1210826539274201</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11384313875807166</v>
+        <v>0.11373207228123453</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10164814860241872</v>
+        <v>0.10154897967695295</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9586043166606691E-2</v>
+        <v>8.9498642148883173E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1341082953243771E-2</v>
+        <v>8.126172579914305E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.24</v>
+        <v>-10.25</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.24</v>
+        <v>10.25</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.24</v>
+        <v>10.25</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>7.9451074657479692E-2</v>
+        <v>7.9088402437900385E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4183F23D-F205-4FC7-87CC-CAD539342F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5782FDD7-C12E-4F97-8B24-A66A97B72865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4762,6 +4762,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4771,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>10.25</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>14298.97864675</v>
+        <v>13992.07373921</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.9088402437900385E-2</v>
+        <v>8.7180467568018338E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4420916915811881E-2</v>
+        <v>3.5175912102399981E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5121951219512199E-2</v>
+        <v>3.5892323030907287E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,12 +6857,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,15 +6878,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>10.25</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14298.97864675</v>
+        <v>13992.07373921</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>7.9088402437900385E-2</v>
+        <v>8.7180467568018338E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.4420916915811881E-2</v>
+        <v>3.5175912102399981E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5121951219512199E-2</v>
+        <v>3.5892323030907287E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,6 +8579,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8595,17 +8606,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,24 +16193,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5121951219512199E-2</v>
+        <v>3.5892323030907287E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5121951219512199E-2</v>
+        <v>3.5892323030907287E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.8487804878048786E-2</v>
+        <v>6.9990029910269203E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5853658536585369E-2</v>
+        <v>6.7298105682951151E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>5.9707317073170729E-2</v>
+        <v>6.1016949152542375E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.4420916915811881E-2</v>
+        <v>3.5175912102399981E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.3495168874342463E-2</v>
+        <v>2.4010516546561344E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11755987988162156</v>
+        <v>0.12013846149417956</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.1116353635043451E-2</v>
+        <v>8.2895575748673525E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.7476500060002581E-2</v>
+        <v>6.8956542932704534E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11092837332876856</v>
+        <v>0.11336149816748532</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10497244412248377</v>
+        <v>0.10727493043424313</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10093197956062654</v>
+        <v>0.10314584152506701</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11267103663842318</v>
+        <v>0.1151423853981892</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.3709928527276817E-2</v>
+        <v>9.5765380598662755E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.6440150936824464E-2</v>
+        <v>7.8116804297353015E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4775116065930982E-2</v>
+        <v>5.5976564274754996E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13666667342315156</v>
+        <v>0.13966434721707913</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13403381579534074</v>
+        <v>0.13697373997031331</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14338791669333745</v>
+        <v>0.14653301556397896</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12798985061887388</v>
+        <v>0.13079720526854013</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1210826539274201</v>
+        <v>0.12373850476132164</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11373207228123453</v>
+        <v>0.11622669400624665</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10154897967695295</v>
+        <v>0.10377637504374555</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9498642148883173E-2</v>
+        <v>9.1461723033504735E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.126172579914305E-2</v>
+        <v>8.3044136534518073E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.25</v>
+        <v>-10.029999999999999</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.25</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.25</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>7.9088402437900385E-2</v>
+        <v>8.7180467568018338E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5782FDD7-C12E-4F97-8B24-A66A97B72865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5B981A-CAA6-4562-96F4-09A0EB37A42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4762,15 +4762,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4780,7 +4771,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>10.029999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>13992.07373921</v>
+        <v>13964.17329307</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.7180467568018338E-2</v>
+        <v>8.7928092344854658E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.5175912102399981E-2</v>
+        <v>3.5246193645062117E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5892323030907287E-2</v>
+        <v>3.5964035964035967E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,15 +6857,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6878,12 +6875,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>10.029999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13992.07373921</v>
+        <v>13964.17329307</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.7180467568018338E-2</v>
+        <v>8.7928092344854658E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.5175912102399981E-2</v>
+        <v>3.5246193645062117E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5892323030907287E-2</v>
+        <v>3.5964035964035967E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,17 +8579,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8606,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,24 +16193,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5892323030907287E-2</v>
+        <v>3.5964035964035967E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5892323030907287E-2</v>
+        <v>3.5964035964035967E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.9990029910269203E-2</v>
+        <v>7.0129870129870139E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.7298105682951151E-2</v>
+        <v>6.7432567432567439E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.1016949152542375E-2</v>
+        <v>6.1138861138861141E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.5175912102399981E-2</v>
+        <v>3.5246193645062117E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.4010516546561344E-2</v>
+        <v>2.4058489606594433E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12013846149417956</v>
+        <v>0.12037849838028182</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.2895575748673525E-2</v>
+        <v>8.3061201274644891E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.8956542932704534E-2</v>
+        <v>6.9094318243259387E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11336149816748532</v>
+        <v>0.11358799466732046</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10727493043424313</v>
+        <v>0.10748926595958627</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10314584152506701</v>
+        <v>0.10335192712251969</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.1151423853981892</v>
+        <v>0.11537244011426949</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.5765380598662755E-2</v>
+        <v>9.5956720020438299E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.8116804297353015E-2</v>
+        <v>7.8272881828416657E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5976564274754996E-2</v>
+        <v>5.6088405562017239E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13966434721707913</v>
+        <v>0.13994339686186849</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13697373997031331</v>
+        <v>0.13724741377644781</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14653301556397896</v>
+        <v>0.14682578882184905</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13079720526854013</v>
+        <v>0.13105853834599973</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12373850476132164</v>
+        <v>0.12398573454106454</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11622669400624665</v>
+        <v>0.1164589151730923</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10377637504374555</v>
+        <v>0.10398372044842835</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1461723033504735E-2</v>
+        <v>9.164446373886638E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3044136534518073E-2</v>
+        <v>8.3210058885236388E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.029999999999999</v>
+        <v>-10.01</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.029999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.029999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.7180467568018338E-2</v>
+        <v>8.7928092344854658E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5B981A-CAA6-4562-96F4-09A0EB37A42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F409D8F5-28E5-4B99-85FA-E4CE612F9163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4762,6 +4762,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4771,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>13964.17329307</v>
+        <v>13950.22307</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5349,13 +5349,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.7928092344854658E-2</v>
+        <v>8.830266843905421E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5568,22 +5568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5773,10 +5773,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5792,22 +5792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.5246193645062117E-2</v>
+        <v>3.5281439838707178E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5964035964035967E-2</v>
+        <v>3.6000000000000004E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6001,22 +6001,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6053,13 +6053,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6072,13 +6072,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6200,13 +6200,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,22 +6413,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6761,13 +6761,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6775,13 +6775,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,12 +6857,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,15 +6878,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13964.17329307</v>
+        <v>13950.22307</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7084,13 +7084,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>8.7928092344854658E-2</v>
+        <v>8.830266843905421E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7290,22 +7290,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7495,10 +7495,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7514,22 +7514,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.5246193645062117E-2</v>
+        <v>3.5281439838707178E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.5964035964035967E-2</v>
+        <v>3.6000000000000004E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7723,22 +7723,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7775,13 +7775,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7794,13 +7794,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7922,13 +7922,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,22 +8135,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8483,13 +8483,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8497,13 +8497,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,6 +8579,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8595,17 +8606,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,24 +16193,24 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5964035964035967E-2</v>
+        <v>3.6000000000000004E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5964035964035967E-2</v>
+        <v>3.6000000000000004E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>7.0129870129870139E-2</v>
+        <v>7.0200000000000012E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.7432567432567439E-2</v>
+        <v>6.7500000000000004E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>6.1138861138861141E-2</v>
+        <v>6.1199999999999997E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.5246193645062117E-2</v>
+        <v>3.5281439838707178E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>2.4058489606594433E-2</v>
+        <v>2.4082548096201025E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.12037849838028182</v>
+        <v>0.12049887687866209</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.3061201274644891E-2</v>
+        <v>8.3144262475919536E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.9094318243259387E-2</v>
+        <v>6.9163412561502643E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.11358799466732046</v>
+        <v>0.11370158266198778</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.10748926595958627</v>
+        <v>0.10759675522554586</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.10335192712251969</v>
+        <v>0.1034552790496422</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>0.11537244011426949</v>
+        <v>0.11548781255438376</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>9.5956720020438299E-2</v>
+        <v>9.6052676740458739E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>7.8272881828416657E-2</v>
+        <v>7.8351154710245077E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6088405562017239E-2</v>
+        <v>5.6144493967579256E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13994339686186849</v>
+        <v>0.14008334025873037</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13724741377644781</v>
+        <v>0.13738466119022424</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14682578882184905</v>
+        <v>0.14697261461067088</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13105853834599973</v>
+        <v>0.13118959688434573</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12398573454106454</v>
+        <v>0.1241097202756056</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1164589151730923</v>
+        <v>0.11657537408826539</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10398372044842835</v>
+        <v>0.10408770416887678</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.164446373886638E-2</v>
+        <v>9.1736108202605249E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3210058885236388E-2</v>
+        <v>8.3293268944121618E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-10.01</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.7928092344854658E-2</v>
+        <v>8.830266843905421E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600373.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600373.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F409D8F5-28E5-4B99-85FA-E4CE612F9163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0942757E-747C-4829-892D-9979FE5485EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4762,15 +4762,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapTe